--- a/data/processed/india_wf_inad.xlsx
+++ b/data/processed/india_wf_inad.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://wfp-my.sharepoint.com/personal/gabriel_battcock_wfp_org/Documents/Documents/MIMI_mac/nsso_hces_2023/data/processed/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="25" documentId="13_ncr:40009_{A5C023EF-866A-4065-9832-0D2C463D85C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{45DADDA3-A791-45FC-ADF3-8829D4926BD7}"/>
+  <xr:revisionPtr revIDLastSave="84" documentId="13_ncr:40009_{A5C023EF-866A-4065-9832-0D2C463D85C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{932F5880-E16D-4F1A-A767-91769036347F}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-90" yWindow="0" windowWidth="9780" windowHeight="11370" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="india_wf_inad" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="79">
   <si>
     <t>category</t>
   </si>
@@ -759,9 +760,10 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -12486,4 +12488,3717 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{829C5016-5CDE-4C2B-8E44-9A0CEC325587}">
+  <dimension ref="A1:X50"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="16384" width="8.7265625" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q1" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="R1" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="S1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="T1" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="U1" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="V1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="W1" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="2" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A2" s="2">
+        <v>45.865506961097502</v>
+      </c>
+      <c r="B2" s="2">
+        <v>38.544085940096501</v>
+      </c>
+      <c r="C2" s="2">
+        <v>13.366691255432199</v>
+      </c>
+      <c r="D2" s="2">
+        <v>46.204625678266197</v>
+      </c>
+      <c r="E2" s="2">
+        <v>42.481074779761798</v>
+      </c>
+      <c r="F2" s="2">
+        <v>17.058909047300499</v>
+      </c>
+      <c r="G2" s="2">
+        <v>68.986169096299193</v>
+      </c>
+      <c r="H2" s="2">
+        <v>49.565550286883102</v>
+      </c>
+      <c r="I2" s="2">
+        <v>36.4546004703503</v>
+      </c>
+      <c r="J2" s="2">
+        <v>97.448828726615105</v>
+      </c>
+      <c r="K2" s="2">
+        <v>92.726876459924</v>
+      </c>
+      <c r="L2" s="2">
+        <v>60.442100395179601</v>
+      </c>
+      <c r="M2" s="2">
+        <v>36.061275579399698</v>
+      </c>
+      <c r="N2" s="2">
+        <v>23.6611003798618</v>
+      </c>
+      <c r="O2" s="2">
+        <v>11.2110831475129</v>
+      </c>
+      <c r="P2" s="2">
+        <v>85.384673704236704</v>
+      </c>
+      <c r="Q2" s="2">
+        <v>65.508738687909698</v>
+      </c>
+      <c r="R2" s="2">
+        <v>33.9833682584174</v>
+      </c>
+      <c r="S2" s="2">
+        <v>92.985845725084801</v>
+      </c>
+      <c r="T2" s="2">
+        <v>79.240736769770507</v>
+      </c>
+      <c r="U2" s="2">
+        <v>52.9316460135421</v>
+      </c>
+      <c r="V2" s="2">
+        <v>85.313837451210802</v>
+      </c>
+      <c r="W2" s="2">
+        <v>71.258447229607199</v>
+      </c>
+      <c r="X2" s="2">
+        <v>32.948576223238298</v>
+      </c>
+    </row>
+    <row r="3" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A3" s="2">
+        <v>27.099296678326699</v>
+      </c>
+      <c r="B3" s="2">
+        <v>21.341844836895898</v>
+      </c>
+      <c r="C3" s="2">
+        <v>6.9274258289164301</v>
+      </c>
+      <c r="D3" s="2">
+        <v>14.1148785751669</v>
+      </c>
+      <c r="E3" s="2">
+        <v>11.7546570114216</v>
+      </c>
+      <c r="F3" s="2">
+        <v>4.8620860499209302</v>
+      </c>
+      <c r="G3" s="2">
+        <v>72.161947904869805</v>
+      </c>
+      <c r="H3" s="2">
+        <v>49.082955832389601</v>
+      </c>
+      <c r="I3" s="2">
+        <v>33.577576443941098</v>
+      </c>
+      <c r="J3" s="2">
+        <v>91.688867941084197</v>
+      </c>
+      <c r="K3" s="2">
+        <v>81.046854250786495</v>
+      </c>
+      <c r="L3" s="2">
+        <v>38.9567701602056</v>
+      </c>
+      <c r="M3" s="2">
+        <v>17.7029504390493</v>
+      </c>
+      <c r="N3" s="2">
+        <v>6.6492478319178998</v>
+      </c>
+      <c r="O3" s="2">
+        <v>3.9642753685210201</v>
+      </c>
+      <c r="P3" s="2">
+        <v>87.591836680975803</v>
+      </c>
+      <c r="Q3" s="2">
+        <v>64.1926528595137</v>
+      </c>
+      <c r="R3" s="2">
+        <v>27.349742667591102</v>
+      </c>
+      <c r="S3" s="2">
+        <v>94.151123676332801</v>
+      </c>
+      <c r="T3" s="2">
+        <v>77.504733730434296</v>
+      </c>
+      <c r="U3" s="2">
+        <v>44.3418356959479</v>
+      </c>
+      <c r="V3" s="2">
+        <v>86.444967889397304</v>
+      </c>
+      <c r="W3" s="2">
+        <v>65.265712367269302</v>
+      </c>
+      <c r="X3" s="2">
+        <v>24.143361741586599</v>
+      </c>
+    </row>
+    <row r="4" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A4" s="2">
+        <v>17.049636337717001</v>
+      </c>
+      <c r="B4" s="2">
+        <v>14.1142030073421</v>
+      </c>
+      <c r="C4" s="2">
+        <v>11.6210008106522</v>
+      </c>
+      <c r="D4" s="2">
+        <v>34.999205302839798</v>
+      </c>
+      <c r="E4" s="2">
+        <v>33.079823123446999</v>
+      </c>
+      <c r="F4" s="2">
+        <v>17.094313083920099</v>
+      </c>
+      <c r="G4" s="2">
+        <v>56.043513957307098</v>
+      </c>
+      <c r="H4" s="2">
+        <v>40.572249589491001</v>
+      </c>
+      <c r="I4" s="2">
+        <v>31.8981937602627</v>
+      </c>
+      <c r="J4" s="2">
+        <v>96.275730104300393</v>
+      </c>
+      <c r="K4" s="2">
+        <v>86.142608108098699</v>
+      </c>
+      <c r="L4" s="2">
+        <v>41.032725524308198</v>
+      </c>
+      <c r="M4" s="2">
+        <v>13.5296059082648</v>
+      </c>
+      <c r="N4" s="2">
+        <v>11.0297763898709</v>
+      </c>
+      <c r="O4" s="2">
+        <v>9.9631738098479197</v>
+      </c>
+      <c r="P4" s="2">
+        <v>88.084923863196494</v>
+      </c>
+      <c r="Q4" s="2">
+        <v>62.899372748129998</v>
+      </c>
+      <c r="R4" s="2">
+        <v>30.3810186380407</v>
+      </c>
+      <c r="S4" s="2">
+        <v>91.093759071187606</v>
+      </c>
+      <c r="T4" s="2">
+        <v>68.693505424564194</v>
+      </c>
+      <c r="U4" s="2">
+        <v>50.237413209099103</v>
+      </c>
+      <c r="V4" s="2">
+        <v>78.6301607461033</v>
+      </c>
+      <c r="W4" s="2">
+        <v>52.221286573388198</v>
+      </c>
+      <c r="X4" s="2">
+        <v>25.448854071778701</v>
+      </c>
+    </row>
+    <row r="5" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A5" s="2">
+        <v>23.9903784814251</v>
+      </c>
+      <c r="B5" s="2">
+        <v>20.2109467381561</v>
+      </c>
+      <c r="C5" s="2">
+        <v>14.419379089480699</v>
+      </c>
+      <c r="D5" s="2">
+        <v>14.899698206656501</v>
+      </c>
+      <c r="E5" s="2">
+        <v>12.8158809317934</v>
+      </c>
+      <c r="F5" s="2">
+        <v>8.8103450216560493</v>
+      </c>
+      <c r="G5" s="2">
+        <v>55.127652233914098</v>
+      </c>
+      <c r="H5" s="2">
+        <v>48.425392444367802</v>
+      </c>
+      <c r="I5" s="2">
+        <v>43.373814041745703</v>
+      </c>
+      <c r="J5" s="2">
+        <v>92.433866927760107</v>
+      </c>
+      <c r="K5" s="2">
+        <v>87.298018545721007</v>
+      </c>
+      <c r="L5" s="2">
+        <v>60.502372889638401</v>
+      </c>
+      <c r="M5" s="2">
+        <v>7.4626280101308398</v>
+      </c>
+      <c r="N5" s="2">
+        <v>6.6940592746542702</v>
+      </c>
+      <c r="O5" s="2">
+        <v>6.4839350309088903</v>
+      </c>
+      <c r="P5" s="2">
+        <v>92.026591024708395</v>
+      </c>
+      <c r="Q5" s="2">
+        <v>80.666099130319907</v>
+      </c>
+      <c r="R5" s="2">
+        <v>63.949229957676302</v>
+      </c>
+      <c r="S5" s="2">
+        <v>91.451158336004099</v>
+      </c>
+      <c r="T5" s="2">
+        <v>79.640229909468204</v>
+      </c>
+      <c r="U5" s="2">
+        <v>79.640229909468204</v>
+      </c>
+      <c r="V5" s="2">
+        <v>79.030386302093106</v>
+      </c>
+      <c r="W5" s="2">
+        <v>65.787715231659405</v>
+      </c>
+      <c r="X5" s="2">
+        <v>51.2991808920588</v>
+      </c>
+    </row>
+    <row r="6" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A6" s="2">
+        <v>30.480872526915402</v>
+      </c>
+      <c r="B6" s="2">
+        <v>30.480872526915402</v>
+      </c>
+      <c r="C6" s="2">
+        <v>30.480872526915402</v>
+      </c>
+      <c r="D6" s="2">
+        <v>13.696402379602899</v>
+      </c>
+      <c r="E6" s="2">
+        <v>13.696402379602899</v>
+      </c>
+      <c r="F6" s="2">
+        <v>13.696402379602899</v>
+      </c>
+      <c r="G6" s="2">
+        <v>63.206944444444403</v>
+      </c>
+      <c r="H6" s="2">
+        <v>63.095833333333303</v>
+      </c>
+      <c r="I6" s="2">
+        <v>62.988888888888901</v>
+      </c>
+      <c r="J6" s="2">
+        <v>92.651127705379096</v>
+      </c>
+      <c r="K6" s="2">
+        <v>92.384469174582094</v>
+      </c>
+      <c r="L6" s="2">
+        <v>91.823658262021695</v>
+      </c>
+      <c r="M6" s="2">
+        <v>26.3800132374528</v>
+      </c>
+      <c r="N6" s="2">
+        <v>26.3800132374528</v>
+      </c>
+      <c r="O6" s="2">
+        <v>26.3800132374528</v>
+      </c>
+      <c r="P6" s="2">
+        <v>93.691574431161996</v>
+      </c>
+      <c r="Q6" s="2">
+        <v>93.424915878937597</v>
+      </c>
+      <c r="R6" s="2">
+        <v>93.229604325804104</v>
+      </c>
+      <c r="S6" s="2">
+        <v>92.743437187760307</v>
+      </c>
+      <c r="T6" s="2">
+        <v>92.476778646702897</v>
+      </c>
+      <c r="U6" s="2">
+        <v>92.476778646702897</v>
+      </c>
+      <c r="V6" s="2">
+        <v>86.916038226513194</v>
+      </c>
+      <c r="W6" s="2">
+        <v>86.916038226513194</v>
+      </c>
+      <c r="X6" s="2">
+        <v>86.355227297612203</v>
+      </c>
+    </row>
+    <row r="7" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A7" s="2">
+        <v>18.0519533296088</v>
+      </c>
+      <c r="B7" s="2">
+        <v>14.491746838183399</v>
+      </c>
+      <c r="C7" s="2">
+        <v>7.73848765592078</v>
+      </c>
+      <c r="D7" s="2">
+        <v>26.8571084099326</v>
+      </c>
+      <c r="E7" s="2">
+        <v>23.785303903600202</v>
+      </c>
+      <c r="F7" s="2">
+        <v>12.140516745609499</v>
+      </c>
+      <c r="G7" s="2">
+        <v>54.891099855282199</v>
+      </c>
+      <c r="H7" s="2">
+        <v>42.060781476121598</v>
+      </c>
+      <c r="I7" s="2">
+        <v>35.217076700434198</v>
+      </c>
+      <c r="J7" s="2">
+        <v>96.680226171264707</v>
+      </c>
+      <c r="K7" s="2">
+        <v>91.519300711237705</v>
+      </c>
+      <c r="L7" s="2">
+        <v>60.619665186164802</v>
+      </c>
+      <c r="M7" s="2">
+        <v>8.6885227611932905</v>
+      </c>
+      <c r="N7" s="2">
+        <v>6.2331708171939404</v>
+      </c>
+      <c r="O7" s="2">
+        <v>5.0282291767726699</v>
+      </c>
+      <c r="P7" s="2">
+        <v>85.018172537264306</v>
+      </c>
+      <c r="Q7" s="2">
+        <v>67.412681539619896</v>
+      </c>
+      <c r="R7" s="2">
+        <v>43.221947945129301</v>
+      </c>
+      <c r="S7" s="2">
+        <v>90.689686024033904</v>
+      </c>
+      <c r="T7" s="2">
+        <v>76.928958757814797</v>
+      </c>
+      <c r="U7" s="2">
+        <v>56.921016715575398</v>
+      </c>
+      <c r="V7" s="2">
+        <v>79.239142777099303</v>
+      </c>
+      <c r="W7" s="2">
+        <v>63.733139938792696</v>
+      </c>
+      <c r="X7" s="2">
+        <v>39.703509821210403</v>
+      </c>
+    </row>
+    <row r="8" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A8" s="2">
+        <v>30.488153297890499</v>
+      </c>
+      <c r="B8" s="2">
+        <v>27.063398295416501</v>
+      </c>
+      <c r="C8" s="2">
+        <v>18.73802203192</v>
+      </c>
+      <c r="D8" s="2">
+        <v>26.851595294241299</v>
+      </c>
+      <c r="E8" s="2">
+        <v>25.541490240308701</v>
+      </c>
+      <c r="F8" s="2">
+        <v>17.071126871851501</v>
+      </c>
+      <c r="G8" s="2">
+        <v>50.664958238420702</v>
+      </c>
+      <c r="H8" s="2">
+        <v>45.391419893697801</v>
+      </c>
+      <c r="I8" s="2">
+        <v>41.015375854214099</v>
+      </c>
+      <c r="J8" s="2">
+        <v>92.024964523856198</v>
+      </c>
+      <c r="K8" s="2">
+        <v>87.373299028722698</v>
+      </c>
+      <c r="L8" s="2">
+        <v>58.713374356980303</v>
+      </c>
+      <c r="M8" s="2">
+        <v>7.81337844949336</v>
+      </c>
+      <c r="N8" s="2">
+        <v>6.7938213272004999</v>
+      </c>
+      <c r="O8" s="2">
+        <v>6.3916397749104101</v>
+      </c>
+      <c r="P8" s="2">
+        <v>90.562158146758307</v>
+      </c>
+      <c r="Q8" s="2">
+        <v>79.237135564385596</v>
+      </c>
+      <c r="R8" s="2">
+        <v>63.881803500370999</v>
+      </c>
+      <c r="S8" s="2">
+        <v>87.977807365935902</v>
+      </c>
+      <c r="T8" s="2">
+        <v>76.678524544221304</v>
+      </c>
+      <c r="U8" s="2">
+        <v>76.628453223152107</v>
+      </c>
+      <c r="V8" s="2">
+        <v>72.107469073825797</v>
+      </c>
+      <c r="W8" s="2">
+        <v>62.6626444653105</v>
+      </c>
+      <c r="X8" s="2">
+        <v>47.032600815144797</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A9" s="2">
+        <v>29.417522860738099</v>
+      </c>
+      <c r="B9" s="2">
+        <v>27.5664417912799</v>
+      </c>
+      <c r="C9" s="2">
+        <v>24.681229122018401</v>
+      </c>
+      <c r="D9" s="2">
+        <v>13.9796642049825</v>
+      </c>
+      <c r="E9" s="2">
+        <v>13.032168592700801</v>
+      </c>
+      <c r="F9" s="2">
+        <v>11.0023019802126</v>
+      </c>
+      <c r="G9" s="2">
+        <v>64.908809891808303</v>
+      </c>
+      <c r="H9" s="2">
+        <v>60.819474497681597</v>
+      </c>
+      <c r="I9" s="2">
+        <v>57.961051004636801</v>
+      </c>
+      <c r="J9" s="2">
+        <v>94.344930263573104</v>
+      </c>
+      <c r="K9" s="2">
+        <v>92.588510782510497</v>
+      </c>
+      <c r="L9" s="2">
+        <v>80.480462137840306</v>
+      </c>
+      <c r="M9" s="2">
+        <v>11.5877848856518</v>
+      </c>
+      <c r="N9" s="2">
+        <v>10.362281715605601</v>
+      </c>
+      <c r="O9" s="2">
+        <v>10.0972724257382</v>
+      </c>
+      <c r="P9" s="2">
+        <v>94.439357331565105</v>
+      </c>
+      <c r="Q9" s="2">
+        <v>90.227701551933905</v>
+      </c>
+      <c r="R9" s="2">
+        <v>79.711887044382394</v>
+      </c>
+      <c r="S9" s="2">
+        <v>92.733934530779294</v>
+      </c>
+      <c r="T9" s="2">
+        <v>89.235493766385602</v>
+      </c>
+      <c r="U9" s="2">
+        <v>85.185212926018806</v>
+      </c>
+      <c r="V9" s="2">
+        <v>90.461782783595197</v>
+      </c>
+      <c r="W9" s="2">
+        <v>86.369671585677594</v>
+      </c>
+      <c r="X9" s="2">
+        <v>75.697226562859498</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A10" s="2">
+        <v>36.589333896154002</v>
+      </c>
+      <c r="B10" s="2">
+        <v>30.327345139781102</v>
+      </c>
+      <c r="C10" s="2">
+        <v>18.059497866700099</v>
+      </c>
+      <c r="D10" s="2">
+        <v>36.948103825778702</v>
+      </c>
+      <c r="E10" s="2">
+        <v>34.458996179139902</v>
+      </c>
+      <c r="F10" s="2">
+        <v>20.177736282638001</v>
+      </c>
+      <c r="G10" s="2">
+        <v>34.585158150851598</v>
+      </c>
+      <c r="H10" s="2">
+        <v>28.425714720194701</v>
+      </c>
+      <c r="I10" s="2">
+        <v>24.0894160583942</v>
+      </c>
+      <c r="J10" s="2">
+        <v>98.108100149797707</v>
+      </c>
+      <c r="K10" s="2">
+        <v>95.060610487364102</v>
+      </c>
+      <c r="L10" s="2">
+        <v>50.066844105132397</v>
+      </c>
+      <c r="M10" s="2">
+        <v>9.5459134721647398</v>
+      </c>
+      <c r="N10" s="2">
+        <v>9.0428266907080808</v>
+      </c>
+      <c r="O10" s="2">
+        <v>8.9112555121301096</v>
+      </c>
+      <c r="P10" s="2">
+        <v>86.357557707755205</v>
+      </c>
+      <c r="Q10" s="2">
+        <v>65.230372257593004</v>
+      </c>
+      <c r="R10" s="2">
+        <v>46.1800834983678</v>
+      </c>
+      <c r="S10" s="2">
+        <v>85.268111219979801</v>
+      </c>
+      <c r="T10" s="2">
+        <v>64.489856812501102</v>
+      </c>
+      <c r="U10" s="2">
+        <v>64.489856812501102</v>
+      </c>
+      <c r="V10" s="2">
+        <v>47.6739396747585</v>
+      </c>
+      <c r="W10" s="2">
+        <v>33.417667953220302</v>
+      </c>
+      <c r="X10" s="2">
+        <v>25.571467713561301</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A11" s="2">
+        <v>42.824769906492499</v>
+      </c>
+      <c r="B11" s="2">
+        <v>33.965105770465797</v>
+      </c>
+      <c r="C11" s="2">
+        <v>9.8361716949647207</v>
+      </c>
+      <c r="D11" s="2">
+        <v>47.288167317442898</v>
+      </c>
+      <c r="E11" s="2">
+        <v>43.047868207107001</v>
+      </c>
+      <c r="F11" s="2">
+        <v>14.5246791527507</v>
+      </c>
+      <c r="G11" s="2">
+        <v>59.967086765241</v>
+      </c>
+      <c r="H11" s="2">
+        <v>41.373821573881102</v>
+      </c>
+      <c r="I11" s="2">
+        <v>30.502563593662099</v>
+      </c>
+      <c r="J11" s="2">
+        <v>98.629945625159607</v>
+      </c>
+      <c r="K11" s="2">
+        <v>95.856791517242797</v>
+      </c>
+      <c r="L11" s="2">
+        <v>56.6079084055268</v>
+      </c>
+      <c r="M11" s="2">
+        <v>7.4369118015606199</v>
+      </c>
+      <c r="N11" s="2">
+        <v>3.65167892254191</v>
+      </c>
+      <c r="O11" s="2">
+        <v>2.3047907002926098</v>
+      </c>
+      <c r="P11" s="2">
+        <v>84.401088752188002</v>
+      </c>
+      <c r="Q11" s="2">
+        <v>60.897445963461898</v>
+      </c>
+      <c r="R11" s="2">
+        <v>27.9317654895384</v>
+      </c>
+      <c r="S11" s="2">
+        <v>92.951306307618594</v>
+      </c>
+      <c r="T11" s="2">
+        <v>76.727018110493304</v>
+      </c>
+      <c r="U11" s="2">
+        <v>51.265901037073803</v>
+      </c>
+      <c r="V11" s="2">
+        <v>81.062091851484993</v>
+      </c>
+      <c r="W11" s="2">
+        <v>59.513054569604598</v>
+      </c>
+      <c r="X11" s="2">
+        <v>23.907161956899898</v>
+      </c>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A12" s="2">
+        <v>35.023951334694502</v>
+      </c>
+      <c r="B12" s="2">
+        <v>28.3012286470147</v>
+      </c>
+      <c r="C12" s="2">
+        <v>9.3245638340519701</v>
+      </c>
+      <c r="D12" s="2">
+        <v>31.374218697846601</v>
+      </c>
+      <c r="E12" s="2">
+        <v>26.878430384668999</v>
+      </c>
+      <c r="F12" s="2">
+        <v>9.3819532323066408</v>
+      </c>
+      <c r="G12" s="2">
+        <v>52.165337833905603</v>
+      </c>
+      <c r="H12" s="2">
+        <v>33.1277425362277</v>
+      </c>
+      <c r="I12" s="2">
+        <v>24.2040970726881</v>
+      </c>
+      <c r="J12" s="2">
+        <v>98.835112551632506</v>
+      </c>
+      <c r="K12" s="2">
+        <v>95.409937663455096</v>
+      </c>
+      <c r="L12" s="2">
+        <v>66.912610005141701</v>
+      </c>
+      <c r="M12" s="2">
+        <v>9.5711616024735502</v>
+      </c>
+      <c r="N12" s="2">
+        <v>5.2423778639296499</v>
+      </c>
+      <c r="O12" s="2">
+        <v>2.6011939200511698</v>
+      </c>
+      <c r="P12" s="2">
+        <v>64.138992199606804</v>
+      </c>
+      <c r="Q12" s="2">
+        <v>43.328180291135297</v>
+      </c>
+      <c r="R12" s="2">
+        <v>21.028425617241499</v>
+      </c>
+      <c r="S12" s="2">
+        <v>82.703785410237899</v>
+      </c>
+      <c r="T12" s="2">
+        <v>61.601493516170002</v>
+      </c>
+      <c r="U12" s="2">
+        <v>35.791475359973298</v>
+      </c>
+      <c r="V12" s="2">
+        <v>68.812070671374798</v>
+      </c>
+      <c r="W12" s="2">
+        <v>49.754629911965502</v>
+      </c>
+      <c r="X12" s="2">
+        <v>23.696243106115499</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A13" s="2">
+        <v>45.108726634025302</v>
+      </c>
+      <c r="B13" s="2">
+        <v>38.392851577977297</v>
+      </c>
+      <c r="C13" s="2">
+        <v>15.521351330897</v>
+      </c>
+      <c r="D13" s="2">
+        <v>7.8978610827940603</v>
+      </c>
+      <c r="E13" s="2">
+        <v>6.9027937923159604</v>
+      </c>
+      <c r="F13" s="2">
+        <v>3.6543897997980501</v>
+      </c>
+      <c r="G13" s="2">
+        <v>82.399343031440594</v>
+      </c>
+      <c r="H13" s="2">
+        <v>60.996245893946501</v>
+      </c>
+      <c r="I13" s="2">
+        <v>43.0877522290005</v>
+      </c>
+      <c r="J13" s="2">
+        <v>96.980162316401106</v>
+      </c>
+      <c r="K13" s="2">
+        <v>93.574711850306002</v>
+      </c>
+      <c r="L13" s="2">
+        <v>69.265307871383996</v>
+      </c>
+      <c r="M13" s="2">
+        <v>51.916550175123099</v>
+      </c>
+      <c r="N13" s="2">
+        <v>32.308462401458499</v>
+      </c>
+      <c r="O13" s="2">
+        <v>18.1730722143332</v>
+      </c>
+      <c r="P13" s="2">
+        <v>86.170316485844097</v>
+      </c>
+      <c r="Q13" s="2">
+        <v>70.194175351561498</v>
+      </c>
+      <c r="R13" s="2">
+        <v>32.877515882188298</v>
+      </c>
+      <c r="S13" s="2">
+        <v>90.891037427155695</v>
+      </c>
+      <c r="T13" s="2">
+        <v>82.097542326475505</v>
+      </c>
+      <c r="U13" s="2">
+        <v>41.532323047951401</v>
+      </c>
+      <c r="V13" s="2">
+        <v>94.149302385300899</v>
+      </c>
+      <c r="W13" s="2">
+        <v>88.039938028590697</v>
+      </c>
+      <c r="X13" s="2">
+        <v>36.8878743494666</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A14" s="2">
+        <v>67.942329839569098</v>
+      </c>
+      <c r="B14" s="2">
+        <v>62.324103047434498</v>
+      </c>
+      <c r="C14" s="2">
+        <v>29.741732357401801</v>
+      </c>
+      <c r="D14" s="2">
+        <v>60.1332354297382</v>
+      </c>
+      <c r="E14" s="2">
+        <v>56.742662524985001</v>
+      </c>
+      <c r="F14" s="2">
+        <v>27.868177144400502</v>
+      </c>
+      <c r="G14" s="2">
+        <v>89.987565282268093</v>
+      </c>
+      <c r="H14" s="2">
+        <v>73.594130813230507</v>
+      </c>
+      <c r="I14" s="2">
+        <v>57.435961203680698</v>
+      </c>
+      <c r="J14" s="2">
+        <v>96.594488667522597</v>
+      </c>
+      <c r="K14" s="2">
+        <v>90.384060413119499</v>
+      </c>
+      <c r="L14" s="2">
+        <v>70.570843281477394</v>
+      </c>
+      <c r="M14" s="2">
+        <v>80.733401639219096</v>
+      </c>
+      <c r="N14" s="2">
+        <v>65.806573119574097</v>
+      </c>
+      <c r="O14" s="2">
+        <v>35.642626615605899</v>
+      </c>
+      <c r="P14" s="2">
+        <v>81.042050851866094</v>
+      </c>
+      <c r="Q14" s="2">
+        <v>66.265381716532005</v>
+      </c>
+      <c r="R14" s="2">
+        <v>35.7115054509812</v>
+      </c>
+      <c r="S14" s="2">
+        <v>93.108421002306301</v>
+      </c>
+      <c r="T14" s="2">
+        <v>85.059650066061096</v>
+      </c>
+      <c r="U14" s="2">
+        <v>56.071106602789001</v>
+      </c>
+      <c r="V14" s="2">
+        <v>95.466848726447594</v>
+      </c>
+      <c r="W14" s="2">
+        <v>89.891840053292398</v>
+      </c>
+      <c r="X14" s="2">
+        <v>47.695158363979601</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A15" s="2">
+        <v>74.4191271935548</v>
+      </c>
+      <c r="B15" s="2">
+        <v>69.149655775703707</v>
+      </c>
+      <c r="C15" s="2">
+        <v>22.869268221422601</v>
+      </c>
+      <c r="D15" s="2">
+        <v>61.569383898875998</v>
+      </c>
+      <c r="E15" s="2">
+        <v>57.208121355037697</v>
+      </c>
+      <c r="F15" s="2">
+        <v>25.514928408850501</v>
+      </c>
+      <c r="G15" s="2">
+        <v>95.813658536585393</v>
+      </c>
+      <c r="H15" s="2">
+        <v>76.727154471544694</v>
+      </c>
+      <c r="I15" s="2">
+        <v>54.853658536585399</v>
+      </c>
+      <c r="J15" s="2">
+        <v>96.469832011789805</v>
+      </c>
+      <c r="K15" s="2">
+        <v>89.072052374142899</v>
+      </c>
+      <c r="L15" s="2">
+        <v>67.033351686821007</v>
+      </c>
+      <c r="M15" s="2">
+        <v>86.909743511315099</v>
+      </c>
+      <c r="N15" s="2">
+        <v>66.361144670880194</v>
+      </c>
+      <c r="O15" s="2">
+        <v>27.931353740620501</v>
+      </c>
+      <c r="P15" s="2">
+        <v>75.9819404443422</v>
+      </c>
+      <c r="Q15" s="2">
+        <v>55.539306721265099</v>
+      </c>
+      <c r="R15" s="2">
+        <v>24.520145867394199</v>
+      </c>
+      <c r="S15" s="2">
+        <v>95.975629996066601</v>
+      </c>
+      <c r="T15" s="2">
+        <v>83.080704082700805</v>
+      </c>
+      <c r="U15" s="2">
+        <v>46.773403010746101</v>
+      </c>
+      <c r="V15" s="2">
+        <v>98.713022673795393</v>
+      </c>
+      <c r="W15" s="2">
+        <v>91.951988792614401</v>
+      </c>
+      <c r="X15" s="2">
+        <v>38.090419866474697</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A16" s="2">
+        <v>83.888097020798497</v>
+      </c>
+      <c r="B16" s="2">
+        <v>79.280496594592606</v>
+      </c>
+      <c r="C16" s="2">
+        <v>21.983207360121099</v>
+      </c>
+      <c r="D16" s="2">
+        <v>73.054889558095994</v>
+      </c>
+      <c r="E16" s="2">
+        <v>68.811906816229396</v>
+      </c>
+      <c r="F16" s="2">
+        <v>27.319747747266099</v>
+      </c>
+      <c r="G16" s="2">
+        <v>97.025311203319504</v>
+      </c>
+      <c r="H16" s="2">
+        <v>77.750829875518704</v>
+      </c>
+      <c r="I16" s="2">
+        <v>53.4836099585062</v>
+      </c>
+      <c r="J16" s="2">
+        <v>99.092716590605605</v>
+      </c>
+      <c r="K16" s="2">
+        <v>96.505938348835599</v>
+      </c>
+      <c r="L16" s="2">
+        <v>80.333410768622997</v>
+      </c>
+      <c r="M16" s="2">
+        <v>93.933707686176206</v>
+      </c>
+      <c r="N16" s="2">
+        <v>75.444458665729201</v>
+      </c>
+      <c r="O16" s="2">
+        <v>27.230814124292699</v>
+      </c>
+      <c r="P16" s="2">
+        <v>86.972455113439594</v>
+      </c>
+      <c r="Q16" s="2">
+        <v>65.419411872601501</v>
+      </c>
+      <c r="R16" s="2">
+        <v>23.382128582588901</v>
+      </c>
+      <c r="S16" s="2">
+        <v>99.364479620802499</v>
+      </c>
+      <c r="T16" s="2">
+        <v>94.202752355415399</v>
+      </c>
+      <c r="U16" s="2">
+        <v>52.539836792085602</v>
+      </c>
+      <c r="V16" s="2">
+        <v>99.732253181022003</v>
+      </c>
+      <c r="W16" s="2">
+        <v>96.337414355603798</v>
+      </c>
+      <c r="X16" s="2">
+        <v>34.698657265820202</v>
+      </c>
+    </row>
+    <row r="17" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A17" s="2">
+        <v>81.495878856592697</v>
+      </c>
+      <c r="B17" s="2">
+        <v>70.584896500320397</v>
+      </c>
+      <c r="C17" s="2">
+        <v>7.4573378515157804</v>
+      </c>
+      <c r="D17" s="2">
+        <v>68.795044501762007</v>
+      </c>
+      <c r="E17" s="2">
+        <v>59.750399728601501</v>
+      </c>
+      <c r="F17" s="2">
+        <v>7.7690994082225604</v>
+      </c>
+      <c r="G17" s="2">
+        <v>95.069799777530605</v>
+      </c>
+      <c r="H17" s="2">
+        <v>51.511123470522797</v>
+      </c>
+      <c r="I17" s="2">
+        <v>22.062291434927701</v>
+      </c>
+      <c r="J17" s="2">
+        <v>97.784730376320596</v>
+      </c>
+      <c r="K17" s="2">
+        <v>79.544698300218201</v>
+      </c>
+      <c r="L17" s="2">
+        <v>22.590915235405699</v>
+      </c>
+      <c r="M17" s="2">
+        <v>94.335865944532102</v>
+      </c>
+      <c r="N17" s="2">
+        <v>50.718640368690799</v>
+      </c>
+      <c r="O17" s="2">
+        <v>9.0711673224858593</v>
+      </c>
+      <c r="P17" s="2">
+        <v>89.957045171184006</v>
+      </c>
+      <c r="Q17" s="2">
+        <v>47.4164768536317</v>
+      </c>
+      <c r="R17" s="2">
+        <v>8.5586382921671493</v>
+      </c>
+      <c r="S17" s="2">
+        <v>98.6023306325405</v>
+      </c>
+      <c r="T17" s="2">
+        <v>78.359386203238998</v>
+      </c>
+      <c r="U17" s="2">
+        <v>15.5677149931828</v>
+      </c>
+      <c r="V17" s="2">
+        <v>99.377670799270206</v>
+      </c>
+      <c r="W17" s="2">
+        <v>89.578711960969002</v>
+      </c>
+      <c r="X17" s="2">
+        <v>11.7242933692908</v>
+      </c>
+    </row>
+    <row r="18" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A18" s="2">
+        <v>54.184976237581502</v>
+      </c>
+      <c r="B18" s="2">
+        <v>41.517096556589898</v>
+      </c>
+      <c r="C18" s="2">
+        <v>4.2515299195240397</v>
+      </c>
+      <c r="D18" s="2">
+        <v>44.694170182338198</v>
+      </c>
+      <c r="E18" s="2">
+        <v>37.411416768996403</v>
+      </c>
+      <c r="F18" s="2">
+        <v>4.1404708948723004</v>
+      </c>
+      <c r="G18" s="2">
+        <v>81.835324571883703</v>
+      </c>
+      <c r="H18" s="2">
+        <v>40.786937475109497</v>
+      </c>
+      <c r="I18" s="2">
+        <v>19.950418160095602</v>
+      </c>
+      <c r="J18" s="2">
+        <v>98.034883886606593</v>
+      </c>
+      <c r="K18" s="2">
+        <v>87.505235478963201</v>
+      </c>
+      <c r="L18" s="2">
+        <v>40.431342368554901</v>
+      </c>
+      <c r="M18" s="2">
+        <v>78.946620894472503</v>
+      </c>
+      <c r="N18" s="2">
+        <v>36.516064682979398</v>
+      </c>
+      <c r="O18" s="2">
+        <v>6.4362056415747197</v>
+      </c>
+      <c r="P18" s="2">
+        <v>77.487907835615502</v>
+      </c>
+      <c r="Q18" s="2">
+        <v>33.8069540503026</v>
+      </c>
+      <c r="R18" s="2">
+        <v>6.5027148902868204</v>
+      </c>
+      <c r="S18" s="2">
+        <v>94.166356763257198</v>
+      </c>
+      <c r="T18" s="2">
+        <v>66.390709729915599</v>
+      </c>
+      <c r="U18" s="2">
+        <v>12.2734681968661</v>
+      </c>
+      <c r="V18" s="2">
+        <v>96.946389165887396</v>
+      </c>
+      <c r="W18" s="2">
+        <v>78.114068775703302</v>
+      </c>
+      <c r="X18" s="2">
+        <v>8.4418912534566104</v>
+      </c>
+    </row>
+    <row r="19" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A19" s="2">
+        <v>69.685616582645096</v>
+      </c>
+      <c r="B19" s="2">
+        <v>64.049066599284203</v>
+      </c>
+      <c r="C19" s="2">
+        <v>25.882033234137701</v>
+      </c>
+      <c r="D19" s="2">
+        <v>69.635407994800602</v>
+      </c>
+      <c r="E19" s="2">
+        <v>65.882400091303197</v>
+      </c>
+      <c r="F19" s="2">
+        <v>26.174773849426099</v>
+      </c>
+      <c r="G19" s="2">
+        <v>94.254126440361304</v>
+      </c>
+      <c r="H19" s="2">
+        <v>75.477109934599795</v>
+      </c>
+      <c r="I19" s="2">
+        <v>54.895048271566502</v>
+      </c>
+      <c r="J19" s="2">
+        <v>96.695612897051603</v>
+      </c>
+      <c r="K19" s="2">
+        <v>88.680565315328096</v>
+      </c>
+      <c r="L19" s="2">
+        <v>60.656044602245103</v>
+      </c>
+      <c r="M19" s="2">
+        <v>90.452534179985193</v>
+      </c>
+      <c r="N19" s="2">
+        <v>72.9965642741561</v>
+      </c>
+      <c r="O19" s="2">
+        <v>34.527873249309998</v>
+      </c>
+      <c r="P19" s="2">
+        <v>92.534970765062894</v>
+      </c>
+      <c r="Q19" s="2">
+        <v>73.576783643262402</v>
+      </c>
+      <c r="R19" s="2">
+        <v>34.8291961853526</v>
+      </c>
+      <c r="S19" s="2">
+        <v>98.693898336996</v>
+      </c>
+      <c r="T19" s="2">
+        <v>90.7346543198001</v>
+      </c>
+      <c r="U19" s="2">
+        <v>53.451027419732803</v>
+      </c>
+      <c r="V19" s="2">
+        <v>99.559652087063299</v>
+      </c>
+      <c r="W19" s="2">
+        <v>95.587148532035101</v>
+      </c>
+      <c r="X19" s="2">
+        <v>41.3567514915594</v>
+      </c>
+    </row>
+    <row r="20" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A20" s="2">
+        <v>77.056591975510699</v>
+      </c>
+      <c r="B20" s="2">
+        <v>70.239718420257105</v>
+      </c>
+      <c r="C20" s="2">
+        <v>18.951042380766399</v>
+      </c>
+      <c r="D20" s="2">
+        <v>62.203817835774899</v>
+      </c>
+      <c r="E20" s="2">
+        <v>57.051517948876501</v>
+      </c>
+      <c r="F20" s="2">
+        <v>20.200864557146399</v>
+      </c>
+      <c r="G20" s="2">
+        <v>91.562456058120503</v>
+      </c>
+      <c r="H20" s="2">
+        <v>70.537848605577693</v>
+      </c>
+      <c r="I20" s="2">
+        <v>49.036442465432401</v>
+      </c>
+      <c r="J20" s="2">
+        <v>98.311261867056402</v>
+      </c>
+      <c r="K20" s="2">
+        <v>95.422806097691804</v>
+      </c>
+      <c r="L20" s="2">
+        <v>77.930482128537406</v>
+      </c>
+      <c r="M20" s="2">
+        <v>89.254921254609897</v>
+      </c>
+      <c r="N20" s="2">
+        <v>69.935695887125405</v>
+      </c>
+      <c r="O20" s="2">
+        <v>24.939030802504</v>
+      </c>
+      <c r="P20" s="2">
+        <v>91.266762166223899</v>
+      </c>
+      <c r="Q20" s="2">
+        <v>74.944527365008099</v>
+      </c>
+      <c r="R20" s="2">
+        <v>26.077387516363999</v>
+      </c>
+      <c r="S20" s="2">
+        <v>98.596959724942195</v>
+      </c>
+      <c r="T20" s="2">
+        <v>93.100454779714099</v>
+      </c>
+      <c r="U20" s="2">
+        <v>50.761525886171299</v>
+      </c>
+      <c r="V20" s="2">
+        <v>99.099105785024307</v>
+      </c>
+      <c r="W20" s="2">
+        <v>95.990732352096103</v>
+      </c>
+      <c r="X20" s="2">
+        <v>33.941435032451501</v>
+      </c>
+    </row>
+    <row r="21" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A21" s="2">
+        <v>58.559846869254201</v>
+      </c>
+      <c r="B21" s="2">
+        <v>48.140778536011602</v>
+      </c>
+      <c r="C21" s="2">
+        <v>7.3725740609131902</v>
+      </c>
+      <c r="D21" s="2">
+        <v>54.386963366027302</v>
+      </c>
+      <c r="E21" s="2">
+        <v>48.635974325177799</v>
+      </c>
+      <c r="F21" s="2">
+        <v>10.868841535469199</v>
+      </c>
+      <c r="G21" s="2">
+        <v>76.997792372647496</v>
+      </c>
+      <c r="H21" s="2">
+        <v>48.8839339919422</v>
+      </c>
+      <c r="I21" s="2">
+        <v>31.641260555218299</v>
+      </c>
+      <c r="J21" s="2">
+        <v>97.597878901472399</v>
+      </c>
+      <c r="K21" s="2">
+        <v>89.059348137867005</v>
+      </c>
+      <c r="L21" s="2">
+        <v>41.801326007422702</v>
+      </c>
+      <c r="M21" s="2">
+        <v>56.437898798593203</v>
+      </c>
+      <c r="N21" s="2">
+        <v>29.644251132503001</v>
+      </c>
+      <c r="O21" s="2">
+        <v>9.7714495765645992</v>
+      </c>
+      <c r="P21" s="2">
+        <v>81.052521457330499</v>
+      </c>
+      <c r="Q21" s="2">
+        <v>49.686358580333597</v>
+      </c>
+      <c r="R21" s="2">
+        <v>14.8678083915729</v>
+      </c>
+      <c r="S21" s="2">
+        <v>95.587045940787306</v>
+      </c>
+      <c r="T21" s="2">
+        <v>77.814383392757904</v>
+      </c>
+      <c r="U21" s="2">
+        <v>38.758260989025302</v>
+      </c>
+      <c r="V21" s="2">
+        <v>94.653847911116102</v>
+      </c>
+      <c r="W21" s="2">
+        <v>76.572593301884694</v>
+      </c>
+      <c r="X21" s="2">
+        <v>20.769247468417699</v>
+      </c>
+    </row>
+    <row r="22" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A22" s="2">
+        <v>59.847300879612803</v>
+      </c>
+      <c r="B22" s="2">
+        <v>51.535748137061603</v>
+      </c>
+      <c r="C22" s="2">
+        <v>12.294062004862999</v>
+      </c>
+      <c r="D22" s="2">
+        <v>69.022323752085001</v>
+      </c>
+      <c r="E22" s="2">
+        <v>65.259490067110207</v>
+      </c>
+      <c r="F22" s="2">
+        <v>25.628292844056201</v>
+      </c>
+      <c r="G22" s="2">
+        <v>71.924780150753804</v>
+      </c>
+      <c r="H22" s="2">
+        <v>49.814070351758801</v>
+      </c>
+      <c r="I22" s="2">
+        <v>35.121074120602998</v>
+      </c>
+      <c r="J22" s="2">
+        <v>99.042795791699803</v>
+      </c>
+      <c r="K22" s="2">
+        <v>95.835169708010795</v>
+      </c>
+      <c r="L22" s="2">
+        <v>61.4979379729687</v>
+      </c>
+      <c r="M22" s="2">
+        <v>40.571425320370203</v>
+      </c>
+      <c r="N22" s="2">
+        <v>23.843868950139999</v>
+      </c>
+      <c r="O22" s="2">
+        <v>9.5016712458393702</v>
+      </c>
+      <c r="P22" s="2">
+        <v>80.541867777525198</v>
+      </c>
+      <c r="Q22" s="2">
+        <v>58.335808557029402</v>
+      </c>
+      <c r="R22" s="2">
+        <v>21.611680966383702</v>
+      </c>
+      <c r="S22" s="2">
+        <v>93.819621748318099</v>
+      </c>
+      <c r="T22" s="2">
+        <v>80.401990047521295</v>
+      </c>
+      <c r="U22" s="2">
+        <v>48.452929717694197</v>
+      </c>
+      <c r="V22" s="2">
+        <v>87.716424503120706</v>
+      </c>
+      <c r="W22" s="2">
+        <v>72.934537386236101</v>
+      </c>
+      <c r="X22" s="2">
+        <v>24.267386792951299</v>
+      </c>
+    </row>
+    <row r="23" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A23" s="2">
+        <v>59.062063896912001</v>
+      </c>
+      <c r="B23" s="2">
+        <v>49.544504165486899</v>
+      </c>
+      <c r="C23" s="2">
+        <v>9.9475172253867008</v>
+      </c>
+      <c r="D23" s="2">
+        <v>83.934729419021707</v>
+      </c>
+      <c r="E23" s="2">
+        <v>81.486705489635099</v>
+      </c>
+      <c r="F23" s="2">
+        <v>31.530922685599801</v>
+      </c>
+      <c r="G23" s="2">
+        <v>83.530129755882996</v>
+      </c>
+      <c r="H23" s="2">
+        <v>53.686716516384401</v>
+      </c>
+      <c r="I23" s="2">
+        <v>33.631075434352297</v>
+      </c>
+      <c r="J23" s="2">
+        <v>98.012536198007695</v>
+      </c>
+      <c r="K23" s="2">
+        <v>92.083772131966398</v>
+      </c>
+      <c r="L23" s="2">
+        <v>66.909887139577094</v>
+      </c>
+      <c r="M23" s="2">
+        <v>69.825045647306197</v>
+      </c>
+      <c r="N23" s="2">
+        <v>40.7735611401284</v>
+      </c>
+      <c r="O23" s="2">
+        <v>12.309205729256901</v>
+      </c>
+      <c r="P23" s="2">
+        <v>81.880184651979306</v>
+      </c>
+      <c r="Q23" s="2">
+        <v>57.060991433084503</v>
+      </c>
+      <c r="R23" s="2">
+        <v>17.4935653633028</v>
+      </c>
+      <c r="S23" s="2">
+        <v>96.801430949573799</v>
+      </c>
+      <c r="T23" s="2">
+        <v>85.185962953031293</v>
+      </c>
+      <c r="U23" s="2">
+        <v>33.570591657559497</v>
+      </c>
+      <c r="V23" s="2">
+        <v>96.340780893302295</v>
+      </c>
+      <c r="W23" s="2">
+        <v>84.452828162034905</v>
+      </c>
+      <c r="X23" s="2">
+        <v>20.342022890406199</v>
+      </c>
+    </row>
+    <row r="24" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A24" s="2">
+        <v>49.735156015734503</v>
+      </c>
+      <c r="B24" s="2">
+        <v>39.211795252882297</v>
+      </c>
+      <c r="C24" s="2">
+        <v>8.1541547102353604</v>
+      </c>
+      <c r="D24" s="2">
+        <v>86.096562700670006</v>
+      </c>
+      <c r="E24" s="2">
+        <v>83.143556746302707</v>
+      </c>
+      <c r="F24" s="2">
+        <v>18.094096671703301</v>
+      </c>
+      <c r="G24" s="2">
+        <v>81.217058941862803</v>
+      </c>
+      <c r="H24" s="2">
+        <v>41.187889760611498</v>
+      </c>
+      <c r="I24" s="2">
+        <v>24.586803460068399</v>
+      </c>
+      <c r="J24" s="2">
+        <v>97.613677332326205</v>
+      </c>
+      <c r="K24" s="2">
+        <v>81.878799727423896</v>
+      </c>
+      <c r="L24" s="2">
+        <v>31.9325287650896</v>
+      </c>
+      <c r="M24" s="2">
+        <v>68.495382329566993</v>
+      </c>
+      <c r="N24" s="2">
+        <v>32.527983485187498</v>
+      </c>
+      <c r="O24" s="2">
+        <v>11.7138112748358</v>
+      </c>
+      <c r="P24" s="2">
+        <v>88.684123130744197</v>
+      </c>
+      <c r="Q24" s="2">
+        <v>49.1078302462222</v>
+      </c>
+      <c r="R24" s="2">
+        <v>16.900239935425802</v>
+      </c>
+      <c r="S24" s="2">
+        <v>96.895843732844099</v>
+      </c>
+      <c r="T24" s="2">
+        <v>73.419742032551696</v>
+      </c>
+      <c r="U24" s="2">
+        <v>22.4149815284729</v>
+      </c>
+      <c r="V24" s="2">
+        <v>96.812911635412206</v>
+      </c>
+      <c r="W24" s="2">
+        <v>76.090471347881405</v>
+      </c>
+      <c r="X24" s="2">
+        <v>18.3567059464342</v>
+      </c>
+    </row>
+    <row r="25" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A25" s="2">
+        <v>30.5635144364702</v>
+      </c>
+      <c r="B25" s="2">
+        <v>24.013307662252799</v>
+      </c>
+      <c r="C25" s="2">
+        <v>9.6845761981093208</v>
+      </c>
+      <c r="D25" s="2">
+        <v>55.602550253580802</v>
+      </c>
+      <c r="E25" s="2">
+        <v>52.484429643427603</v>
+      </c>
+      <c r="F25" s="2">
+        <v>24.108725113957099</v>
+      </c>
+      <c r="G25" s="2">
+        <v>48.174484317603799</v>
+      </c>
+      <c r="H25" s="2">
+        <v>35.737637750777097</v>
+      </c>
+      <c r="I25" s="2">
+        <v>28.6344306301215</v>
+      </c>
+      <c r="J25" s="2">
+        <v>98.394011126883498</v>
+      </c>
+      <c r="K25" s="2">
+        <v>95.033484738848799</v>
+      </c>
+      <c r="L25" s="2">
+        <v>55.483488305560002</v>
+      </c>
+      <c r="M25" s="2">
+        <v>7.3029215668763099</v>
+      </c>
+      <c r="N25" s="2">
+        <v>4.5865589285046404</v>
+      </c>
+      <c r="O25" s="2">
+        <v>3.1523221192442201</v>
+      </c>
+      <c r="P25" s="2">
+        <v>86.519182255574705</v>
+      </c>
+      <c r="Q25" s="2">
+        <v>64.016281817796497</v>
+      </c>
+      <c r="R25" s="2">
+        <v>36.774996914402898</v>
+      </c>
+      <c r="S25" s="2">
+        <v>92.460332094001998</v>
+      </c>
+      <c r="T25" s="2">
+        <v>75.589188071429106</v>
+      </c>
+      <c r="U25" s="2">
+        <v>57.593780602480699</v>
+      </c>
+      <c r="V25" s="2">
+        <v>73.488105369355694</v>
+      </c>
+      <c r="W25" s="2">
+        <v>52.290054056872599</v>
+      </c>
+      <c r="X25" s="2">
+        <v>28.1988201924962</v>
+      </c>
+    </row>
+    <row r="26" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A26" s="2">
+        <v>38.150452170686997</v>
+      </c>
+      <c r="B26" s="2">
+        <v>33.857293327589197</v>
+      </c>
+      <c r="C26" s="2">
+        <v>19.468055090253401</v>
+      </c>
+      <c r="D26" s="2">
+        <v>43.448117830764701</v>
+      </c>
+      <c r="E26" s="2">
+        <v>40.465258311982701</v>
+      </c>
+      <c r="F26" s="2">
+        <v>22.5137628700714</v>
+      </c>
+      <c r="G26" s="2">
+        <v>58.972377653432801</v>
+      </c>
+      <c r="H26" s="2">
+        <v>48.635846878053101</v>
+      </c>
+      <c r="I26" s="2">
+        <v>41.7235988986588</v>
+      </c>
+      <c r="J26" s="2">
+        <v>97.968811404335099</v>
+      </c>
+      <c r="K26" s="2">
+        <v>96.343762133942704</v>
+      </c>
+      <c r="L26" s="2">
+        <v>73.224216279405198</v>
+      </c>
+      <c r="M26" s="2">
+        <v>15.726269937040801</v>
+      </c>
+      <c r="N26" s="2">
+        <v>11.055110188838</v>
+      </c>
+      <c r="O26" s="2">
+        <v>8.0272518542022393</v>
+      </c>
+      <c r="P26" s="2">
+        <v>94.193140545189706</v>
+      </c>
+      <c r="Q26" s="2">
+        <v>85.140779336536298</v>
+      </c>
+      <c r="R26" s="2">
+        <v>62.282821470630999</v>
+      </c>
+      <c r="S26" s="2">
+        <v>94.078978259273399</v>
+      </c>
+      <c r="T26" s="2">
+        <v>86.087392050607406</v>
+      </c>
+      <c r="U26" s="2">
+        <v>74.205020534797796</v>
+      </c>
+      <c r="V26" s="2">
+        <v>87.863685627784704</v>
+      </c>
+      <c r="W26" s="2">
+        <v>78.718985470328406</v>
+      </c>
+      <c r="X26" s="2">
+        <v>52.182075681052602</v>
+      </c>
+    </row>
+    <row r="27" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A27" s="2">
+        <v>34.232747334843097</v>
+      </c>
+      <c r="B27" s="2">
+        <v>32.625532418393199</v>
+      </c>
+      <c r="C27" s="2">
+        <v>23.174805121392399</v>
+      </c>
+      <c r="D27" s="2">
+        <v>44.292158257756</v>
+      </c>
+      <c r="E27" s="2">
+        <v>43.257235188287602</v>
+      </c>
+      <c r="F27" s="2">
+        <v>35.7628221442694</v>
+      </c>
+      <c r="G27" s="2">
+        <v>68.483630952380906</v>
+      </c>
+      <c r="H27" s="2">
+        <v>59.904761904761898</v>
+      </c>
+      <c r="I27" s="2">
+        <v>52.132440476190503</v>
+      </c>
+      <c r="J27" s="2">
+        <v>98.646288968526505</v>
+      </c>
+      <c r="K27" s="2">
+        <v>98.646288968526505</v>
+      </c>
+      <c r="L27" s="2">
+        <v>92.606748533293995</v>
+      </c>
+      <c r="M27" s="2">
+        <v>20.546546776758898</v>
+      </c>
+      <c r="N27" s="2">
+        <v>16.283438112812501</v>
+      </c>
+      <c r="O27" s="2">
+        <v>11.3076607543093</v>
+      </c>
+      <c r="P27" s="2">
+        <v>80.409241098377606</v>
+      </c>
+      <c r="Q27" s="2">
+        <v>78.262250174052596</v>
+      </c>
+      <c r="R27" s="2">
+        <v>68.6091806773874</v>
+      </c>
+      <c r="S27" s="2">
+        <v>88.744262760997799</v>
+      </c>
+      <c r="T27" s="2">
+        <v>87.590141817141998</v>
+      </c>
+      <c r="U27" s="2">
+        <v>82.186344234570299</v>
+      </c>
+      <c r="V27" s="2">
+        <v>93.020765358798101</v>
+      </c>
+      <c r="W27" s="2">
+        <v>91.506165232957102</v>
+      </c>
+      <c r="X27" s="2">
+        <v>79.952423680645097</v>
+      </c>
+    </row>
+    <row r="28" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A28" s="2">
+        <v>47.973012218272501</v>
+      </c>
+      <c r="B28" s="2">
+        <v>42.106395877537899</v>
+      </c>
+      <c r="C28" s="2">
+        <v>20.257467499223999</v>
+      </c>
+      <c r="D28" s="2">
+        <v>59.195837981364697</v>
+      </c>
+      <c r="E28" s="2">
+        <v>56.593518771060602</v>
+      </c>
+      <c r="F28" s="2">
+        <v>30.420658918657601</v>
+      </c>
+      <c r="G28" s="2">
+        <v>69.143411023483296</v>
+      </c>
+      <c r="H28" s="2">
+        <v>55.5645239458959</v>
+      </c>
+      <c r="I28" s="2">
+        <v>45.9033352425431</v>
+      </c>
+      <c r="J28" s="2">
+        <v>98.167515772427805</v>
+      </c>
+      <c r="K28" s="2">
+        <v>95.573179295295105</v>
+      </c>
+      <c r="L28" s="2">
+        <v>66.763664917203599</v>
+      </c>
+      <c r="M28" s="2">
+        <v>27.302904734642599</v>
+      </c>
+      <c r="N28" s="2">
+        <v>19.286302669214098</v>
+      </c>
+      <c r="O28" s="2">
+        <v>13.9774435045067</v>
+      </c>
+      <c r="P28" s="2">
+        <v>91.005281790043796</v>
+      </c>
+      <c r="Q28" s="2">
+        <v>78.230108193817898</v>
+      </c>
+      <c r="R28" s="2">
+        <v>52.479994389645597</v>
+      </c>
+      <c r="S28" s="2">
+        <v>96.138243304575894</v>
+      </c>
+      <c r="T28" s="2">
+        <v>88.374466784530796</v>
+      </c>
+      <c r="U28" s="2">
+        <v>74.815455448159398</v>
+      </c>
+      <c r="V28" s="2">
+        <v>92.211375771145697</v>
+      </c>
+      <c r="W28" s="2">
+        <v>81.936000149861897</v>
+      </c>
+      <c r="X28" s="2">
+        <v>50.085219712942397</v>
+      </c>
+    </row>
+    <row r="29" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A29" s="2">
+        <v>52.515054308301004</v>
+      </c>
+      <c r="B29" s="2">
+        <v>42.0828535120922</v>
+      </c>
+      <c r="C29" s="2">
+        <v>8.8689792653009505</v>
+      </c>
+      <c r="D29" s="2">
+        <v>35.417686252823401</v>
+      </c>
+      <c r="E29" s="2">
+        <v>29.979612488504799</v>
+      </c>
+      <c r="F29" s="2">
+        <v>7.5923242106900402</v>
+      </c>
+      <c r="G29" s="2">
+        <v>87.811254050869096</v>
+      </c>
+      <c r="H29" s="2">
+        <v>58.669645487577299</v>
+      </c>
+      <c r="I29" s="2">
+        <v>36.129824216831999</v>
+      </c>
+      <c r="J29" s="2">
+        <v>96.517550476968907</v>
+      </c>
+      <c r="K29" s="2">
+        <v>88.585411534500807</v>
+      </c>
+      <c r="L29" s="2">
+        <v>56.689836660599802</v>
+      </c>
+      <c r="M29" s="2">
+        <v>63.991655783606802</v>
+      </c>
+      <c r="N29" s="2">
+        <v>35.973590384392701</v>
+      </c>
+      <c r="O29" s="2">
+        <v>11.162790916326101</v>
+      </c>
+      <c r="P29" s="2">
+        <v>83.984689762516993</v>
+      </c>
+      <c r="Q29" s="2">
+        <v>59.341527542688503</v>
+      </c>
+      <c r="R29" s="2">
+        <v>17.285038777169099</v>
+      </c>
+      <c r="S29" s="2">
+        <v>95.732270290409105</v>
+      </c>
+      <c r="T29" s="2">
+        <v>81.157113159179602</v>
+      </c>
+      <c r="U29" s="2">
+        <v>33.670401566684198</v>
+      </c>
+      <c r="V29" s="2">
+        <v>96.111102117334298</v>
+      </c>
+      <c r="W29" s="2">
+        <v>86.152170539190095</v>
+      </c>
+      <c r="X29" s="2">
+        <v>23.9585307334773</v>
+      </c>
+    </row>
+    <row r="30" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A30" s="2">
+        <v>41.476911815801699</v>
+      </c>
+      <c r="B30" s="2">
+        <v>33.560741597437499</v>
+      </c>
+      <c r="C30" s="2">
+        <v>13.2237564848757</v>
+      </c>
+      <c r="D30" s="2">
+        <v>46.935037573559903</v>
+      </c>
+      <c r="E30" s="2">
+        <v>42.530043961275098</v>
+      </c>
+      <c r="F30" s="2">
+        <v>15.87186656706</v>
+      </c>
+      <c r="G30" s="2">
+        <v>65.838607594936704</v>
+      </c>
+      <c r="H30" s="2">
+        <v>43.882749107432701</v>
+      </c>
+      <c r="I30" s="2">
+        <v>31.8188899707887</v>
+      </c>
+      <c r="J30" s="2">
+        <v>96.198236726946703</v>
+      </c>
+      <c r="K30" s="2">
+        <v>91.029253651942895</v>
+      </c>
+      <c r="L30" s="2">
+        <v>65.275822005174007</v>
+      </c>
+      <c r="M30" s="2">
+        <v>42.396150606742701</v>
+      </c>
+      <c r="N30" s="2">
+        <v>25.889274968152002</v>
+      </c>
+      <c r="O30" s="2">
+        <v>14.114323392532301</v>
+      </c>
+      <c r="P30" s="2">
+        <v>85.726225590671405</v>
+      </c>
+      <c r="Q30" s="2">
+        <v>67.437227040824098</v>
+      </c>
+      <c r="R30" s="2">
+        <v>30.799351382695399</v>
+      </c>
+      <c r="S30" s="2">
+        <v>92.912645470444005</v>
+      </c>
+      <c r="T30" s="2">
+        <v>80.850652638884796</v>
+      </c>
+      <c r="U30" s="2">
+        <v>45.417903615212403</v>
+      </c>
+      <c r="V30" s="2">
+        <v>90.094787775762796</v>
+      </c>
+      <c r="W30" s="2">
+        <v>77.811946032840197</v>
+      </c>
+      <c r="X30" s="2">
+        <v>33.568944511786697</v>
+      </c>
+    </row>
+    <row r="31" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A31" s="2">
+        <v>24.895570601435502</v>
+      </c>
+      <c r="B31" s="2">
+        <v>19.060329451731899</v>
+      </c>
+      <c r="C31" s="2">
+        <v>7.6943876408749601</v>
+      </c>
+      <c r="D31" s="2">
+        <v>25.028144000077098</v>
+      </c>
+      <c r="E31" s="2">
+        <v>23.637949047950102</v>
+      </c>
+      <c r="F31" s="2">
+        <v>14.175266714224</v>
+      </c>
+      <c r="G31" s="2">
+        <v>58.640648011781998</v>
+      </c>
+      <c r="H31" s="2">
+        <v>37.916053019145799</v>
+      </c>
+      <c r="I31" s="2">
+        <v>27.518409425625901</v>
+      </c>
+      <c r="J31" s="2">
+        <v>90.379956270449895</v>
+      </c>
+      <c r="K31" s="2">
+        <v>81.853692751148202</v>
+      </c>
+      <c r="L31" s="2">
+        <v>56.361139782460498</v>
+      </c>
+      <c r="M31" s="2">
+        <v>44.459737003222898</v>
+      </c>
+      <c r="N31" s="2">
+        <v>23.503110947324402</v>
+      </c>
+      <c r="O31" s="2">
+        <v>10.473106049293699</v>
+      </c>
+      <c r="P31" s="2">
+        <v>84.898884078555895</v>
+      </c>
+      <c r="Q31" s="2">
+        <v>62.383172740726103</v>
+      </c>
+      <c r="R31" s="2">
+        <v>28.950231179453901</v>
+      </c>
+      <c r="S31" s="2">
+        <v>88.882205217452494</v>
+      </c>
+      <c r="T31" s="2">
+        <v>72.410554281898897</v>
+      </c>
+      <c r="U31" s="2">
+        <v>40.081693265360997</v>
+      </c>
+      <c r="V31" s="2">
+        <v>86.283882607540605</v>
+      </c>
+      <c r="W31" s="2">
+        <v>67.642699702157302</v>
+      </c>
+      <c r="X31" s="2">
+        <v>29.300669455867901</v>
+      </c>
+    </row>
+    <row r="32" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A32" s="2">
+        <v>79.387088434965094</v>
+      </c>
+      <c r="B32" s="2">
+        <v>66.693990740509705</v>
+      </c>
+      <c r="C32" s="2">
+        <v>12.395478367136</v>
+      </c>
+      <c r="D32" s="2">
+        <v>45.937063758783601</v>
+      </c>
+      <c r="E32" s="2">
+        <v>40.9378863011448</v>
+      </c>
+      <c r="F32" s="2">
+        <v>16.6632981599289</v>
+      </c>
+      <c r="G32" s="2">
+        <v>74.639209225700199</v>
+      </c>
+      <c r="H32" s="2">
+        <v>41.283360790774303</v>
+      </c>
+      <c r="I32" s="2">
+        <v>22.752883031301501</v>
+      </c>
+      <c r="J32" s="2">
+        <v>99.204813045847601</v>
+      </c>
+      <c r="K32" s="2">
+        <v>97.044299781425295</v>
+      </c>
+      <c r="L32" s="2">
+        <v>69.064134802913998</v>
+      </c>
+      <c r="M32" s="2">
+        <v>97.102770792676907</v>
+      </c>
+      <c r="N32" s="2">
+        <v>74.2372212167475</v>
+      </c>
+      <c r="O32" s="2">
+        <v>18.272849052506601</v>
+      </c>
+      <c r="P32" s="2">
+        <v>96.983478649143706</v>
+      </c>
+      <c r="Q32" s="2">
+        <v>78.025428309343695</v>
+      </c>
+      <c r="R32" s="2">
+        <v>18.032196658570001</v>
+      </c>
+      <c r="S32" s="2">
+        <v>98.372776197974204</v>
+      </c>
+      <c r="T32" s="2">
+        <v>88.657093839335502</v>
+      </c>
+      <c r="U32" s="2">
+        <v>29.247444244506401</v>
+      </c>
+      <c r="V32" s="2">
+        <v>98.307254746680798</v>
+      </c>
+      <c r="W32" s="2">
+        <v>87.069916100669303</v>
+      </c>
+      <c r="X32" s="2">
+        <v>18.089915631157002</v>
+      </c>
+    </row>
+    <row r="33" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A33" s="2">
+        <v>65.114671344893907</v>
+      </c>
+      <c r="B33" s="2">
+        <v>59.521535337370302</v>
+      </c>
+      <c r="C33" s="2">
+        <v>20.101395974552702</v>
+      </c>
+      <c r="D33" s="2">
+        <v>29.357020543876899</v>
+      </c>
+      <c r="E33" s="2">
+        <v>27.387926271214099</v>
+      </c>
+      <c r="F33" s="2">
+        <v>13.0965249564158</v>
+      </c>
+      <c r="G33" s="2">
+        <v>80.296059782608694</v>
+      </c>
+      <c r="H33" s="2">
+        <v>60.9964673913044</v>
+      </c>
+      <c r="I33" s="2">
+        <v>45.906657608695703</v>
+      </c>
+      <c r="J33" s="2">
+        <v>97.295648375869703</v>
+      </c>
+      <c r="K33" s="2">
+        <v>94.359829125511794</v>
+      </c>
+      <c r="L33" s="2">
+        <v>77.2710269461206</v>
+      </c>
+      <c r="M33" s="2">
+        <v>84.308420878718906</v>
+      </c>
+      <c r="N33" s="2">
+        <v>72.309028871183799</v>
+      </c>
+      <c r="O33" s="2">
+        <v>37.161140678125903</v>
+      </c>
+      <c r="P33" s="2">
+        <v>95.477951366618498</v>
+      </c>
+      <c r="Q33" s="2">
+        <v>86.065141747461894</v>
+      </c>
+      <c r="R33" s="2">
+        <v>44.1022100328303</v>
+      </c>
+      <c r="S33" s="2">
+        <v>96.696080822846994</v>
+      </c>
+      <c r="T33" s="2">
+        <v>89.765516360966203</v>
+      </c>
+      <c r="U33" s="2">
+        <v>65.840301466933795</v>
+      </c>
+      <c r="V33" s="2">
+        <v>97.234065728353002</v>
+      </c>
+      <c r="W33" s="2">
+        <v>92.189738582726093</v>
+      </c>
+      <c r="X33" s="2">
+        <v>50.615961980600602</v>
+      </c>
+    </row>
+    <row r="34" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A34" s="2">
+        <v>44.922591014458597</v>
+      </c>
+      <c r="B34" s="2">
+        <v>38.306615845923801</v>
+      </c>
+      <c r="C34" s="2">
+        <v>11.2636927556467</v>
+      </c>
+      <c r="D34" s="2">
+        <v>35.032789770848503</v>
+      </c>
+      <c r="E34" s="2">
+        <v>31.4348628780109</v>
+      </c>
+      <c r="F34" s="2">
+        <v>12.2475044075737</v>
+      </c>
+      <c r="G34" s="2">
+        <v>78.972873082287293</v>
+      </c>
+      <c r="H34" s="2">
+        <v>57.073430962343103</v>
+      </c>
+      <c r="I34" s="2">
+        <v>40.370571827057198</v>
+      </c>
+      <c r="J34" s="2">
+        <v>96.195606885758096</v>
+      </c>
+      <c r="K34" s="2">
+        <v>89.752155017613305</v>
+      </c>
+      <c r="L34" s="2">
+        <v>65.166140106773298</v>
+      </c>
+      <c r="M34" s="2">
+        <v>73.2174376520165</v>
+      </c>
+      <c r="N34" s="2">
+        <v>54.281022516269502</v>
+      </c>
+      <c r="O34" s="2">
+        <v>21.448625463383099</v>
+      </c>
+      <c r="P34" s="2">
+        <v>92.767197996085798</v>
+      </c>
+      <c r="Q34" s="2">
+        <v>79.797359838469106</v>
+      </c>
+      <c r="R34" s="2">
+        <v>33.750575524063798</v>
+      </c>
+      <c r="S34" s="2">
+        <v>94.154359581393607</v>
+      </c>
+      <c r="T34" s="2">
+        <v>85.283332847810797</v>
+      </c>
+      <c r="U34" s="2">
+        <v>55.335228146828598</v>
+      </c>
+      <c r="V34" s="2">
+        <v>94.241472495584901</v>
+      </c>
+      <c r="W34" s="2">
+        <v>86.114896805671293</v>
+      </c>
+      <c r="X34" s="2">
+        <v>38.518862373373899</v>
+      </c>
+    </row>
+    <row r="35" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A35" s="2">
+        <v>50.368073926776297</v>
+      </c>
+      <c r="B35" s="2">
+        <v>48.129516606979898</v>
+      </c>
+      <c r="C35" s="2">
+        <v>36.132422711253902</v>
+      </c>
+      <c r="D35" s="2">
+        <v>13.0024407609643</v>
+      </c>
+      <c r="E35" s="2">
+        <v>12.2286015031997</v>
+      </c>
+      <c r="F35" s="2">
+        <v>10.321669528146501</v>
+      </c>
+      <c r="G35" s="2">
+        <v>83.507504690431503</v>
+      </c>
+      <c r="H35" s="2">
+        <v>77.521575984990605</v>
+      </c>
+      <c r="I35" s="2">
+        <v>71.779549718574103</v>
+      </c>
+      <c r="J35" s="2">
+        <v>94.519655734180205</v>
+      </c>
+      <c r="K35" s="2">
+        <v>92.199583198579504</v>
+      </c>
+      <c r="L35" s="2">
+        <v>84.516829323441897</v>
+      </c>
+      <c r="M35" s="2">
+        <v>72.237996095930995</v>
+      </c>
+      <c r="N35" s="2">
+        <v>65.263626982126297</v>
+      </c>
+      <c r="O35" s="2">
+        <v>55.0519303374546</v>
+      </c>
+      <c r="P35" s="2">
+        <v>91.903574224848896</v>
+      </c>
+      <c r="Q35" s="2">
+        <v>86.636942052635902</v>
+      </c>
+      <c r="R35" s="2">
+        <v>72.739875210991499</v>
+      </c>
+      <c r="S35" s="2">
+        <v>96.361068527274995</v>
+      </c>
+      <c r="T35" s="2">
+        <v>94.078454017960595</v>
+      </c>
+      <c r="U35" s="2">
+        <v>84.567626234581894</v>
+      </c>
+      <c r="V35" s="2">
+        <v>97.584460377514304</v>
+      </c>
+      <c r="W35" s="2">
+        <v>95.281680019464702</v>
+      </c>
+      <c r="X35" s="2">
+        <v>81.033943970601399</v>
+      </c>
+    </row>
+    <row r="36" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A36" s="2">
+        <v>61.515128103959</v>
+      </c>
+      <c r="B36" s="2">
+        <v>55.086541677329798</v>
+      </c>
+      <c r="C36" s="2">
+        <v>23.309910122455399</v>
+      </c>
+      <c r="D36" s="2">
+        <v>26.021565567336701</v>
+      </c>
+      <c r="E36" s="2">
+        <v>23.7265939145129</v>
+      </c>
+      <c r="F36" s="2">
+        <v>10.357708624233</v>
+      </c>
+      <c r="G36" s="2">
+        <v>83.324596774193594</v>
+      </c>
+      <c r="H36" s="2">
+        <v>63.6401209677419</v>
+      </c>
+      <c r="I36" s="2">
+        <v>48.2822580645161</v>
+      </c>
+      <c r="J36" s="2">
+        <v>98.644828826423705</v>
+      </c>
+      <c r="K36" s="2">
+        <v>95.102566878496503</v>
+      </c>
+      <c r="L36" s="2">
+        <v>73.008099926318593</v>
+      </c>
+      <c r="M36" s="2">
+        <v>71.055073401554395</v>
+      </c>
+      <c r="N36" s="2">
+        <v>56.2430482806245</v>
+      </c>
+      <c r="O36" s="2">
+        <v>32.408510566420901</v>
+      </c>
+      <c r="P36" s="2">
+        <v>86.718201868680396</v>
+      </c>
+      <c r="Q36" s="2">
+        <v>73.126755425359605</v>
+      </c>
+      <c r="R36" s="2">
+        <v>38.933393819787703</v>
+      </c>
+      <c r="S36" s="2">
+        <v>96.149169020274996</v>
+      </c>
+      <c r="T36" s="2">
+        <v>86.918674170264694</v>
+      </c>
+      <c r="U36" s="2">
+        <v>61.059231245834198</v>
+      </c>
+      <c r="V36" s="2">
+        <v>95.761265459593702</v>
+      </c>
+      <c r="W36" s="2">
+        <v>87.760091225972502</v>
+      </c>
+      <c r="X36" s="2">
+        <v>49.309881521772198</v>
+      </c>
+    </row>
+    <row r="37" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A37" s="2">
+        <v>66.446882062849099</v>
+      </c>
+      <c r="B37" s="2">
+        <v>58.408117778523099</v>
+      </c>
+      <c r="C37" s="2">
+        <v>23.7214804255558</v>
+      </c>
+      <c r="D37" s="2">
+        <v>43.996118250678798</v>
+      </c>
+      <c r="E37" s="2">
+        <v>39.099519129580798</v>
+      </c>
+      <c r="F37" s="2">
+        <v>17.272160722326898</v>
+      </c>
+      <c r="G37" s="2">
+        <v>89.521932424422005</v>
+      </c>
+      <c r="H37" s="2">
+        <v>64.904712507409599</v>
+      </c>
+      <c r="I37" s="2">
+        <v>46.781713100177797</v>
+      </c>
+      <c r="J37" s="2">
+        <v>97.149214747166994</v>
+      </c>
+      <c r="K37" s="2">
+        <v>91.660574310248606</v>
+      </c>
+      <c r="L37" s="2">
+        <v>65.216005913564601</v>
+      </c>
+      <c r="M37" s="2">
+        <v>69.830550559817198</v>
+      </c>
+      <c r="N37" s="2">
+        <v>47.193840758077101</v>
+      </c>
+      <c r="O37" s="2">
+        <v>26.128872927512099</v>
+      </c>
+      <c r="P37" s="2">
+        <v>86.0427005372797</v>
+      </c>
+      <c r="Q37" s="2">
+        <v>65.730862704582805</v>
+      </c>
+      <c r="R37" s="2">
+        <v>34.6685273963258</v>
+      </c>
+      <c r="S37" s="2">
+        <v>96.421534405657397</v>
+      </c>
+      <c r="T37" s="2">
+        <v>86.068843857547805</v>
+      </c>
+      <c r="U37" s="2">
+        <v>49.646879596925899</v>
+      </c>
+      <c r="V37" s="2">
+        <v>96.419099088410604</v>
+      </c>
+      <c r="W37" s="2">
+        <v>88.4184363009946</v>
+      </c>
+      <c r="X37" s="2">
+        <v>42.206836097034703</v>
+      </c>
+    </row>
+    <row r="38" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A38" s="2">
+        <v>53.105433072572303</v>
+      </c>
+      <c r="B38" s="2">
+        <v>43.212096535551098</v>
+      </c>
+      <c r="C38" s="2">
+        <v>2.0826519482416899</v>
+      </c>
+      <c r="D38" s="2">
+        <v>6.72660645988657</v>
+      </c>
+      <c r="E38" s="2">
+        <v>4.0853620107786597</v>
+      </c>
+      <c r="F38" s="2">
+        <v>1.2283652722992799</v>
+      </c>
+      <c r="G38" s="2">
+        <v>80.044506258692607</v>
+      </c>
+      <c r="H38" s="2">
+        <v>47.802503477051502</v>
+      </c>
+      <c r="I38" s="2">
+        <v>26.1766342141864</v>
+      </c>
+      <c r="J38" s="2">
+        <v>92.765062264851593</v>
+      </c>
+      <c r="K38" s="2">
+        <v>77.577555726684395</v>
+      </c>
+      <c r="L38" s="2">
+        <v>17.6568747205324</v>
+      </c>
+      <c r="M38" s="2">
+        <v>24.697797983807298</v>
+      </c>
+      <c r="N38" s="2">
+        <v>4.2957742194010002</v>
+      </c>
+      <c r="O38" s="2">
+        <v>1.11660670462676</v>
+      </c>
+      <c r="P38" s="2">
+        <v>89.426122090613603</v>
+      </c>
+      <c r="Q38" s="2">
+        <v>61.908973391981803</v>
+      </c>
+      <c r="R38" s="2">
+        <v>5.6355642779051296</v>
+      </c>
+      <c r="S38" s="2">
+        <v>94.168819292707695</v>
+      </c>
+      <c r="T38" s="2">
+        <v>73.563614274517505</v>
+      </c>
+      <c r="U38" s="2">
+        <v>35.807017895168997</v>
+      </c>
+      <c r="V38" s="2">
+        <v>90.156524284806906</v>
+      </c>
+      <c r="W38" s="2">
+        <v>66.663240264187806</v>
+      </c>
+      <c r="X38" s="2">
+        <v>5.0140727295788601</v>
+      </c>
+    </row>
+    <row r="39" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A39" s="2">
+        <v>59.217514992679902</v>
+      </c>
+      <c r="B39" s="2">
+        <v>49.868908156602203</v>
+      </c>
+      <c r="C39" s="2">
+        <v>10.992651655980399</v>
+      </c>
+      <c r="D39" s="2">
+        <v>62.804496541770099</v>
+      </c>
+      <c r="E39" s="2">
+        <v>58.166347289607899</v>
+      </c>
+      <c r="F39" s="2">
+        <v>19.288898341644501</v>
+      </c>
+      <c r="G39" s="2">
+        <v>73.583481843441604</v>
+      </c>
+      <c r="H39" s="2">
+        <v>49.3910702309093</v>
+      </c>
+      <c r="I39" s="2">
+        <v>32.414640222286103</v>
+      </c>
+      <c r="J39" s="2">
+        <v>99.226257417116599</v>
+      </c>
+      <c r="K39" s="2">
+        <v>95.851944335628801</v>
+      </c>
+      <c r="L39" s="2">
+        <v>58.018563540110101</v>
+      </c>
+      <c r="M39" s="2">
+        <v>35.320925638865297</v>
+      </c>
+      <c r="N39" s="2">
+        <v>21.857373523879399</v>
+      </c>
+      <c r="O39" s="2">
+        <v>7.4754963279553399</v>
+      </c>
+      <c r="P39" s="2">
+        <v>86.954468054954901</v>
+      </c>
+      <c r="Q39" s="2">
+        <v>63.707511720246998</v>
+      </c>
+      <c r="R39" s="2">
+        <v>24.011619763678802</v>
+      </c>
+      <c r="S39" s="2">
+        <v>95.548202351000398</v>
+      </c>
+      <c r="T39" s="2">
+        <v>81.179996568203194</v>
+      </c>
+      <c r="U39" s="2">
+        <v>49.744713624437203</v>
+      </c>
+      <c r="V39" s="2">
+        <v>87.684156963806103</v>
+      </c>
+      <c r="W39" s="2">
+        <v>70.747231775892701</v>
+      </c>
+      <c r="X39" s="2">
+        <v>23.346574246422101</v>
+      </c>
+    </row>
+    <row r="40" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A40" s="2">
+        <v>49.464948603291099</v>
+      </c>
+      <c r="B40" s="2">
+        <v>40.324886981791003</v>
+      </c>
+      <c r="C40" s="2">
+        <v>9.7825232112329505</v>
+      </c>
+      <c r="D40" s="2">
+        <v>53.500950575787499</v>
+      </c>
+      <c r="E40" s="2">
+        <v>48.798957491962099</v>
+      </c>
+      <c r="F40" s="2">
+        <v>15.314953705557301</v>
+      </c>
+      <c r="G40" s="2">
+        <v>69.839769813462794</v>
+      </c>
+      <c r="H40" s="2">
+        <v>47.053220849889399</v>
+      </c>
+      <c r="I40" s="2">
+        <v>31.702362543796099</v>
+      </c>
+      <c r="J40" s="2">
+        <v>98.433939069847497</v>
+      </c>
+      <c r="K40" s="2">
+        <v>93.708596441130197</v>
+      </c>
+      <c r="L40" s="2">
+        <v>53.8670250230006</v>
+      </c>
+      <c r="M40" s="2">
+        <v>34.704767117387597</v>
+      </c>
+      <c r="N40" s="2">
+        <v>20.523024508295801</v>
+      </c>
+      <c r="O40" s="2">
+        <v>7.1554201590723201</v>
+      </c>
+      <c r="P40" s="2">
+        <v>84.926220239159306</v>
+      </c>
+      <c r="Q40" s="2">
+        <v>60.697596289565901</v>
+      </c>
+      <c r="R40" s="2">
+        <v>24.629248775973899</v>
+      </c>
+      <c r="S40" s="2">
+        <v>94.378607471764695</v>
+      </c>
+      <c r="T40" s="2">
+        <v>78.1689282907723</v>
+      </c>
+      <c r="U40" s="2">
+        <v>47.660564681100297</v>
+      </c>
+      <c r="V40" s="2">
+        <v>85.238586126630906</v>
+      </c>
+      <c r="W40" s="2">
+        <v>67.631703097643907</v>
+      </c>
+      <c r="X40" s="2">
+        <v>23.451892388853299</v>
+      </c>
+    </row>
+    <row r="41" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A41" s="2">
+        <v>44.7229735569978</v>
+      </c>
+      <c r="B41" s="2">
+        <v>36.682348457032099</v>
+      </c>
+      <c r="C41" s="2">
+        <v>11.363691405275301</v>
+      </c>
+      <c r="D41" s="2">
+        <v>44.7027703902437</v>
+      </c>
+      <c r="E41" s="2">
+        <v>40.487447287696</v>
+      </c>
+      <c r="F41" s="2">
+        <v>14.4724467847531</v>
+      </c>
+      <c r="G41" s="2">
+        <v>69.572640914390604</v>
+      </c>
+      <c r="H41" s="2">
+        <v>48.362698063800899</v>
+      </c>
+      <c r="I41" s="2">
+        <v>34.023203807412202</v>
+      </c>
+      <c r="J41" s="2">
+        <v>97.700644913638797</v>
+      </c>
+      <c r="K41" s="2">
+        <v>92.050887706355397</v>
+      </c>
+      <c r="L41" s="2">
+        <v>56.275951361723997</v>
+      </c>
+      <c r="M41" s="2">
+        <v>37.374423080361801</v>
+      </c>
+      <c r="N41" s="2">
+        <v>23.170735316121601</v>
+      </c>
+      <c r="O41" s="2">
+        <v>9.1692732814813205</v>
+      </c>
+      <c r="P41" s="2">
+        <v>85.086411724990796</v>
+      </c>
+      <c r="Q41" s="2">
+        <v>63.264899779658002</v>
+      </c>
+      <c r="R41" s="2">
+        <v>29.497889716203598</v>
+      </c>
+      <c r="S41" s="2">
+        <v>93.505284760439295</v>
+      </c>
+      <c r="T41" s="2">
+        <v>78.259336874846397</v>
+      </c>
+      <c r="U41" s="2">
+        <v>49.790401315674202</v>
+      </c>
+      <c r="V41" s="2">
+        <v>85.265112675765295</v>
+      </c>
+      <c r="W41" s="2">
+        <v>70.090388251818098</v>
+      </c>
+      <c r="X41" s="2">
+        <v>28.655703471531101</v>
+      </c>
+    </row>
+    <row r="42" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A42" s="2">
+        <v>39.093923732180002</v>
+      </c>
+      <c r="B42" s="2">
+        <v>32.592134390479302</v>
+      </c>
+      <c r="C42" s="2">
+        <v>13.4191190635628</v>
+      </c>
+      <c r="D42" s="2">
+        <v>35.877051072802701</v>
+      </c>
+      <c r="E42" s="2">
+        <v>32.573741517195103</v>
+      </c>
+      <c r="F42" s="2">
+        <v>14.673671647881401</v>
+      </c>
+      <c r="G42" s="2">
+        <v>68.211532280933895</v>
+      </c>
+      <c r="H42" s="2">
+        <v>49.932318744682902</v>
+      </c>
+      <c r="I42" s="2">
+        <v>37.761603176103598</v>
+      </c>
+      <c r="J42" s="2">
+        <v>97.001844389341898</v>
+      </c>
+      <c r="K42" s="2">
+        <v>91.228170187870703</v>
+      </c>
+      <c r="L42" s="2">
+        <v>61.413855378955098</v>
+      </c>
+      <c r="M42" s="2">
+        <v>37.551200294222703</v>
+      </c>
+      <c r="N42" s="2">
+        <v>25.196746830410898</v>
+      </c>
+      <c r="O42" s="2">
+        <v>12.088165307262299</v>
+      </c>
+      <c r="P42" s="2">
+        <v>85.058582602833397</v>
+      </c>
+      <c r="Q42" s="2">
+        <v>66.615483973033705</v>
+      </c>
+      <c r="R42" s="2">
+        <v>37.169835896364098</v>
+      </c>
+      <c r="S42" s="2">
+        <v>92.371291274467694</v>
+      </c>
+      <c r="T42" s="2">
+        <v>78.667839448079206</v>
+      </c>
+      <c r="U42" s="2">
+        <v>53.140620632885401</v>
+      </c>
+      <c r="V42" s="2">
+        <v>84.831367707022494</v>
+      </c>
+      <c r="W42" s="2">
+        <v>72.382036196261893</v>
+      </c>
+      <c r="X42" s="2">
+        <v>36.507484237500599</v>
+      </c>
+    </row>
+    <row r="43" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A43" s="2">
+        <v>33.481690118397204</v>
+      </c>
+      <c r="B43" s="2">
+        <v>30.669191046814198</v>
+      </c>
+      <c r="C43" s="2">
+        <v>22.507317024054501</v>
+      </c>
+      <c r="D43" s="2">
+        <v>29.713575869215401</v>
+      </c>
+      <c r="E43" s="2">
+        <v>28.3321038829781</v>
+      </c>
+      <c r="F43" s="2">
+        <v>21.567060723356899</v>
+      </c>
+      <c r="G43" s="2">
+        <v>63.791097843860499</v>
+      </c>
+      <c r="H43" s="2">
+        <v>53.006806860098102</v>
+      </c>
+      <c r="I43" s="2">
+        <v>46.183595086891998</v>
+      </c>
+      <c r="J43" s="2">
+        <v>94.311637289934794</v>
+      </c>
+      <c r="K43" s="2">
+        <v>90.026053661453503</v>
+      </c>
+      <c r="L43" s="2">
+        <v>74.416038265924001</v>
+      </c>
+      <c r="M43" s="2">
+        <v>35.522820142897501</v>
+      </c>
+      <c r="N43" s="2">
+        <v>28.380511949660001</v>
+      </c>
+      <c r="O43" s="2">
+        <v>21.761055288951301</v>
+      </c>
+      <c r="P43" s="2">
+        <v>84.609969476586798</v>
+      </c>
+      <c r="Q43" s="2">
+        <v>74.476254432976702</v>
+      </c>
+      <c r="R43" s="2">
+        <v>58.543986552875403</v>
+      </c>
+      <c r="S43" s="2">
+        <v>88.292365925678794</v>
+      </c>
+      <c r="T43" s="2">
+        <v>79.701212732457705</v>
+      </c>
+      <c r="U43" s="2">
+        <v>66.069007639635302</v>
+      </c>
+      <c r="V43" s="2">
+        <v>82.998957992339001</v>
+      </c>
+      <c r="W43" s="2">
+        <v>76.087285821074701</v>
+      </c>
+      <c r="X43" s="2">
+        <v>56.6078196169981</v>
+      </c>
+    </row>
+    <row r="44" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A44" s="2">
+        <v>47.098018188697601</v>
+      </c>
+      <c r="B44" s="2">
+        <v>38.445682254966002</v>
+      </c>
+      <c r="C44" s="2">
+        <v>9.1711948110684798</v>
+      </c>
+      <c r="D44" s="2">
+        <v>50.503002122069098</v>
+      </c>
+      <c r="E44" s="2">
+        <v>46.0994769043728</v>
+      </c>
+      <c r="F44" s="2">
+        <v>15.341040025186899</v>
+      </c>
+      <c r="G44" s="2">
+        <v>69.3039418416801</v>
+      </c>
+      <c r="H44" s="2">
+        <v>45.672665589660703</v>
+      </c>
+      <c r="I44" s="2">
+        <v>29.945751211631698</v>
+      </c>
+      <c r="J44" s="2">
+        <v>97.981818172716601</v>
+      </c>
+      <c r="K44" s="2">
+        <v>92.612974295540596</v>
+      </c>
+      <c r="L44" s="2">
+        <v>54.268269724312397</v>
+      </c>
+      <c r="M44" s="2">
+        <v>35.402096524006197</v>
+      </c>
+      <c r="N44" s="2">
+        <v>21.103361847899599</v>
+      </c>
+      <c r="O44" s="2">
+        <v>7.4466570681439297</v>
+      </c>
+      <c r="P44" s="2">
+        <v>83.685239728834702</v>
+      </c>
+      <c r="Q44" s="2">
+        <v>59.695161379344803</v>
+      </c>
+      <c r="R44" s="2">
+        <v>24.118165226592801</v>
+      </c>
+      <c r="S44" s="2">
+        <v>93.054638178440896</v>
+      </c>
+      <c r="T44" s="2">
+        <v>76.381739327310399</v>
+      </c>
+      <c r="U44" s="2">
+        <v>45.3901175577355</v>
+      </c>
+      <c r="V44" s="2">
+        <v>84.143947588173006</v>
+      </c>
+      <c r="W44" s="2">
+        <v>67.134382533379096</v>
+      </c>
+      <c r="X44" s="2">
+        <v>23.197317184334</v>
+      </c>
+    </row>
+    <row r="45" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A45" s="2">
+        <v>43.179013973835502</v>
+      </c>
+      <c r="B45" s="2">
+        <v>38.758575506001598</v>
+      </c>
+      <c r="C45" s="2">
+        <v>22.5115746788378</v>
+      </c>
+      <c r="D45" s="2">
+        <v>36.835495870869501</v>
+      </c>
+      <c r="E45" s="2">
+        <v>34.594078479701999</v>
+      </c>
+      <c r="F45" s="2">
+        <v>20.8033316381049</v>
+      </c>
+      <c r="G45" s="2">
+        <v>68.523699356731697</v>
+      </c>
+      <c r="H45" s="2">
+        <v>55.231049919121197</v>
+      </c>
+      <c r="I45" s="2">
+        <v>45.9272373321296</v>
+      </c>
+      <c r="J45" s="2">
+        <v>96.287076745620197</v>
+      </c>
+      <c r="K45" s="2">
+        <v>92.975147911974105</v>
+      </c>
+      <c r="L45" s="2">
+        <v>73.899139719903701</v>
+      </c>
+      <c r="M45" s="2">
+        <v>37.4980818256277</v>
+      </c>
+      <c r="N45" s="2">
+        <v>29.236178453455501</v>
+      </c>
+      <c r="O45" s="2">
+        <v>19.416366470516301</v>
+      </c>
+      <c r="P45" s="2">
+        <v>89.088914110757898</v>
+      </c>
+      <c r="Q45" s="2">
+        <v>78.180537224399998</v>
+      </c>
+      <c r="R45" s="2">
+        <v>55.486456414101497</v>
+      </c>
+      <c r="S45" s="2">
+        <v>92.835899476221101</v>
+      </c>
+      <c r="T45" s="2">
+        <v>85.472465994353598</v>
+      </c>
+      <c r="U45" s="2">
+        <v>69.369843044525297</v>
+      </c>
+      <c r="V45" s="2">
+        <v>87.863835550295406</v>
+      </c>
+      <c r="W45" s="2">
+        <v>80.247631377637404</v>
+      </c>
+      <c r="X45" s="2">
+        <v>54.2033017560994</v>
+      </c>
+    </row>
+    <row r="46" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A46" s="2">
+        <v>60.662018779778201</v>
+      </c>
+      <c r="B46" s="2">
+        <v>51.7663073291451</v>
+      </c>
+      <c r="C46" s="2">
+        <v>13.134300829705101</v>
+      </c>
+      <c r="D46" s="2">
+        <v>61.848835574464204</v>
+      </c>
+      <c r="E46" s="2">
+        <v>57.425224298286402</v>
+      </c>
+      <c r="F46" s="2">
+        <v>20.304321181432101</v>
+      </c>
+      <c r="G46" s="2">
+        <v>74.051509415163906</v>
+      </c>
+      <c r="H46" s="2">
+        <v>51.311348012354301</v>
+      </c>
+      <c r="I46" s="2">
+        <v>35.101623991232401</v>
+      </c>
+      <c r="J46" s="2">
+        <v>99.1624699389847</v>
+      </c>
+      <c r="K46" s="2">
+        <v>96.093588027638305</v>
+      </c>
+      <c r="L46" s="2">
+        <v>60.930510058852498</v>
+      </c>
+      <c r="M46" s="2">
+        <v>36.490441528131498</v>
+      </c>
+      <c r="N46" s="2">
+        <v>23.643177985169601</v>
+      </c>
+      <c r="O46" s="2">
+        <v>8.9840288355954403</v>
+      </c>
+      <c r="P46" s="2">
+        <v>88.229933794043902</v>
+      </c>
+      <c r="Q46" s="2">
+        <v>66.835521137223097</v>
+      </c>
+      <c r="R46" s="2">
+        <v>27.9011461245675</v>
+      </c>
+      <c r="S46" s="2">
+        <v>96.066513930695805</v>
+      </c>
+      <c r="T46" s="2">
+        <v>83.132917741518796</v>
+      </c>
+      <c r="U46" s="2">
+        <v>53.580066953304801</v>
+      </c>
+      <c r="V46" s="2">
+        <v>88.787007110590807</v>
+      </c>
+      <c r="W46" s="2">
+        <v>73.323723522819506</v>
+      </c>
+      <c r="X46" s="2">
+        <v>27.198192483210601</v>
+      </c>
+    </row>
+    <row r="47" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A47" s="2">
+        <v>50.758135380014302</v>
+      </c>
+      <c r="B47" s="2">
+        <v>41.977422637078703</v>
+      </c>
+      <c r="C47" s="2">
+        <v>11.6761670746066</v>
+      </c>
+      <c r="D47" s="2">
+        <v>53.3006867163379</v>
+      </c>
+      <c r="E47" s="2">
+        <v>48.930406884767301</v>
+      </c>
+      <c r="F47" s="2">
+        <v>16.460735395315499</v>
+      </c>
+      <c r="G47" s="2">
+        <v>70.511178822342103</v>
+      </c>
+      <c r="H47" s="2">
+        <v>49.162791600357103</v>
+      </c>
+      <c r="I47" s="2">
+        <v>34.515894888017698</v>
+      </c>
+      <c r="J47" s="2">
+        <v>98.452712977337001</v>
+      </c>
+      <c r="K47" s="2">
+        <v>94.246115073535805</v>
+      </c>
+      <c r="L47" s="2">
+        <v>56.692821164711802</v>
+      </c>
+      <c r="M47" s="2">
+        <v>35.310751284636503</v>
+      </c>
+      <c r="N47" s="2">
+        <v>21.9736696961007</v>
+      </c>
+      <c r="O47" s="2">
+        <v>8.6625428040171499</v>
+      </c>
+      <c r="P47" s="2">
+        <v>86.279786015978601</v>
+      </c>
+      <c r="Q47" s="2">
+        <v>63.782914800375103</v>
+      </c>
+      <c r="R47" s="2">
+        <v>28.159285329782499</v>
+      </c>
+      <c r="S47" s="2">
+        <v>94.8609635622783</v>
+      </c>
+      <c r="T47" s="2">
+        <v>80.064657588230304</v>
+      </c>
+      <c r="U47" s="2">
+        <v>51.089223711026698</v>
+      </c>
+      <c r="V47" s="2">
+        <v>86.630494579239695</v>
+      </c>
+      <c r="W47" s="2">
+        <v>70.202798236918198</v>
+      </c>
+      <c r="X47" s="2">
+        <v>27.2535874883907</v>
+      </c>
+    </row>
+    <row r="48" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A48" s="2">
+        <v>44.845505735511999</v>
+      </c>
+      <c r="B48" s="2">
+        <v>37.032709893165702</v>
+      </c>
+      <c r="C48" s="2">
+        <v>11.9768428125293</v>
+      </c>
+      <c r="D48" s="2">
+        <v>45.321179481851303</v>
+      </c>
+      <c r="E48" s="2">
+        <v>41.190238702278499</v>
+      </c>
+      <c r="F48" s="2">
+        <v>15.194847042716599</v>
+      </c>
+      <c r="G48" s="2">
+        <v>69.068025966901303</v>
+      </c>
+      <c r="H48" s="2">
+        <v>49.019767760811902</v>
+      </c>
+      <c r="I48" s="2">
+        <v>35.655572826186301</v>
+      </c>
+      <c r="J48" s="2">
+        <v>97.870197977834295</v>
+      </c>
+      <c r="K48" s="2">
+        <v>92.641873589753402</v>
+      </c>
+      <c r="L48" s="2">
+        <v>57.936123149733596</v>
+      </c>
+      <c r="M48" s="2">
+        <v>36.029700771274499</v>
+      </c>
+      <c r="N48" s="2">
+        <v>22.696028479727701</v>
+      </c>
+      <c r="O48" s="2">
+        <v>9.7869126126835209</v>
+      </c>
+      <c r="P48" s="2">
+        <v>85.323904999972498</v>
+      </c>
+      <c r="Q48" s="2">
+        <v>64.256457862022003</v>
+      </c>
+      <c r="R48" s="2">
+        <v>31.744657585308101</v>
+      </c>
+      <c r="S48" s="2">
+        <v>93.621334364230606</v>
+      </c>
+      <c r="T48" s="2">
+        <v>79.055369056435794</v>
+      </c>
+      <c r="U48" s="2">
+        <v>51.276356442402601</v>
+      </c>
+      <c r="V48" s="2">
+        <v>85.388846700465507</v>
+      </c>
+      <c r="W48" s="2">
+        <v>70.455865170922706</v>
+      </c>
+      <c r="X48" s="2">
+        <v>30.906376507638701</v>
+      </c>
+    </row>
+    <row r="49" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A49" s="2">
+        <v>39.514416757856203</v>
+      </c>
+      <c r="B49" s="2">
+        <v>32.618490499006597</v>
+      </c>
+      <c r="C49" s="2">
+        <v>12.4068673351959</v>
+      </c>
+      <c r="D49" s="2">
+        <v>38.786335077087401</v>
+      </c>
+      <c r="E49" s="2">
+        <v>35.2692375018935</v>
+      </c>
+      <c r="F49" s="2">
+        <v>14.65612214683</v>
+      </c>
+      <c r="G49" s="2">
+        <v>67.541162110321096</v>
+      </c>
+      <c r="H49" s="2">
+        <v>48.943696355569301</v>
+      </c>
+      <c r="I49" s="2">
+        <v>36.598957626954501</v>
+      </c>
+      <c r="J49" s="2">
+        <v>96.997190438635201</v>
+      </c>
+      <c r="K49" s="2">
+        <v>91.4885271849666</v>
+      </c>
+      <c r="L49" s="2">
+        <v>60.380736463596399</v>
+      </c>
+      <c r="M49" s="2">
+        <v>36.421935027911999</v>
+      </c>
+      <c r="N49" s="2">
+        <v>23.346472325946898</v>
+      </c>
+      <c r="O49" s="2">
+        <v>10.925855386756901</v>
+      </c>
+      <c r="P49" s="2">
+        <v>84.895728576541302</v>
+      </c>
+      <c r="Q49" s="2">
+        <v>65.134134374736604</v>
+      </c>
+      <c r="R49" s="2">
+        <v>35.435900723066901</v>
+      </c>
+      <c r="S49" s="2">
+        <v>92.245706421712697</v>
+      </c>
+      <c r="T49" s="2">
+        <v>78.270464664610003</v>
+      </c>
+      <c r="U49" s="2">
+        <v>52.241692894209898</v>
+      </c>
+      <c r="V49" s="2">
+        <v>84.509268302847303</v>
+      </c>
+      <c r="W49" s="2">
+        <v>71.190808665756805</v>
+      </c>
+      <c r="X49" s="2">
+        <v>34.387270176051999</v>
+      </c>
+    </row>
+    <row r="50" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A50" s="2">
+        <v>33.9283908943274</v>
+      </c>
+      <c r="B50" s="2">
+        <v>29.642584736951701</v>
+      </c>
+      <c r="C50" s="2">
+        <v>17.568280376891099</v>
+      </c>
+      <c r="D50" s="2">
+        <v>32.174282743260001</v>
+      </c>
+      <c r="E50" s="2">
+        <v>29.9745436488897</v>
+      </c>
+      <c r="F50" s="2">
+        <v>18.7026517406502</v>
+      </c>
+      <c r="G50" s="2">
+        <v>64.036817214026001</v>
+      </c>
+      <c r="H50" s="2">
+        <v>49.4728769807624</v>
+      </c>
+      <c r="I50" s="2">
+        <v>40.2990597855784</v>
+      </c>
+      <c r="J50" s="2">
+        <v>94.820163084359294</v>
+      </c>
+      <c r="K50" s="2">
+        <v>89.268155488747098</v>
+      </c>
+      <c r="L50" s="2">
+        <v>66.245729164514898</v>
+      </c>
+      <c r="M50" s="2">
+        <v>36.071511549170602</v>
+      </c>
+      <c r="N50" s="2">
+        <v>26.608285552077799</v>
+      </c>
+      <c r="O50" s="2">
+        <v>17.563106213157699</v>
+      </c>
+      <c r="P50" s="2">
+        <v>82.300858646263706</v>
+      </c>
+      <c r="Q50" s="2">
+        <v>67.550087493015795</v>
+      </c>
+      <c r="R50" s="2">
+        <v>46.421515480837499</v>
+      </c>
+      <c r="S50" s="2">
+        <v>88.247622599346897</v>
+      </c>
+      <c r="T50" s="2">
+        <v>75.803703084439903</v>
+      </c>
+      <c r="U50" s="2">
+        <v>56.449002388354998</v>
+      </c>
+      <c r="V50" s="2">
+        <v>81.375857194549297</v>
+      </c>
+      <c r="W50" s="2">
+        <v>71.185691419358804</v>
+      </c>
+      <c r="X50" s="2">
+        <v>44.7545215974719</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/data/processed/india_wf_inad.xlsx
+++ b/data/processed/india_wf_inad.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://wfp-my.sharepoint.com/personal/gabriel_battcock_wfp_org/Documents/Documents/MIMI_mac/nsso_hces_2023/data/processed/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="124" documentId="13_ncr:40009_{A5C023EF-866A-4065-9832-0D2C463D85C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2E962673-6A55-4852-A13B-BD58662C281D}"/>
+  <xr:revisionPtr revIDLastSave="177" documentId="13_ncr:40009_{A5C023EF-866A-4065-9832-0D2C463D85C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{90634E41-57DA-482F-9CD8-CC85D0401597}"/>
   <bookViews>
-    <workbookView xWindow="-165" yWindow="-165" windowWidth="25530" windowHeight="15360" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-570" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="india_wf_inad" sheetId="1" r:id="rId1"/>
@@ -860,9 +860,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -900,7 +900,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1006,7 +1006,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1148,7 +1148,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1157,9 +1157,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:BN55"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:66" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
         <v>0</v>
       </c>
@@ -1353,7 +1353,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="2" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1518,55 +1518,55 @@
         <v>93(30)</v>
       </c>
       <c r="BC2" s="1" t="str">
-        <f>ROUND(G2,0)&amp;"("&amp;ROUND((G2-U2)/G2*100,0)&amp;")"</f>
+        <f t="shared" ref="BC2:BC33" si="0">ROUND(G2,0)&amp;"("&amp;ROUND((G2-U2)/G2*100,0)&amp;")"</f>
         <v>36(-18)</v>
       </c>
       <c r="BD2" s="1" t="str">
-        <f>ROUND(I2,0)&amp;"("&amp;ROUND((I2-W2)/I2*100,0)&amp;")"</f>
+        <f t="shared" ref="BD2:BD33" si="1">ROUND(I2,0)&amp;"("&amp;ROUND((I2-W2)/I2*100,0)&amp;")"</f>
         <v>100(76)</v>
       </c>
       <c r="BE2" s="1" t="str">
-        <f>ROUND(K2,0)&amp;"("&amp;ROUND((K2-Y2)/K2*100,0)&amp;")"</f>
+        <f t="shared" ref="BE2:BE33" si="2">ROUND(K2,0)&amp;"("&amp;ROUND((K2-Y2)/K2*100,0)&amp;")"</f>
         <v>85(-17)</v>
       </c>
       <c r="BF2" s="1" t="str">
-        <f>ROUND(O2,0)&amp;"("&amp;ROUND((O2-AC2)/O2*100,0)&amp;")"</f>
+        <f t="shared" ref="BF2:BF33" si="3">ROUND(O2,0)&amp;"("&amp;ROUND((O2-AC2)/O2*100,0)&amp;")"</f>
         <v>97(19)</v>
       </c>
       <c r="BG2" s="1" t="str">
-        <f>ROUND(C2,0)&amp;"("&amp;ROUND((C2-AE2)/C2*100,0)&amp;")"</f>
+        <f t="shared" ref="BG2:BG33" si="4">ROUND(C2,0)&amp;"("&amp;ROUND((C2-AE2)/C2*100,0)&amp;")"</f>
         <v>46(-102)</v>
       </c>
       <c r="BH2" s="1" t="str">
-        <f>ROUND(E2,0)&amp;"("&amp;ROUND((E2-AG2)/E2*100,1)&amp;")"</f>
+        <f t="shared" ref="BH2:BH33" si="5">ROUND(E2,0)&amp;"("&amp;ROUND((E2-AG2)/E2*100,1)&amp;")"</f>
         <v>46(-54.2)</v>
       </c>
       <c r="BI2" s="1" t="str">
-        <f>ROUND(AS2,0)&amp;"("&amp;ROUND((AS2-AU2)/AS2*100,0)&amp;")"</f>
+        <f t="shared" ref="BI2:BI33" si="6">ROUND(AS2,0)&amp;"("&amp;ROUND((AS2-AU2)/AS2*100,0)&amp;")"</f>
         <v>53(-14)</v>
       </c>
       <c r="BJ2" s="1" t="str">
-        <f>ROUND(M2,0)&amp;"("&amp;ROUND((M2-AO2)/M2*100,0)&amp;")"</f>
+        <f t="shared" ref="BJ2:BJ33" si="7">ROUND(M2,0)&amp;"("&amp;ROUND((M2-AO2)/M2*100,0)&amp;")"</f>
         <v>93(-7)</v>
       </c>
       <c r="BK2" s="1" t="str">
-        <f>ROUND(G2,0)&amp;"("&amp;ROUND((G2-AI2)/G2*100,0)&amp;")"</f>
+        <f t="shared" ref="BK2:BK33" si="8">ROUND(G2,0)&amp;"("&amp;ROUND((G2-AI2)/G2*100,0)&amp;")"</f>
         <v>36(63)</v>
       </c>
       <c r="BL2" s="1" t="str">
-        <f>ROUND(I2,0)&amp;"("&amp;ROUND((I2-AK2)/I2*100,0)&amp;")"</f>
+        <f t="shared" ref="BL2:BL33" si="9">ROUND(I2,0)&amp;"("&amp;ROUND((I2-AK2)/I2*100,0)&amp;")"</f>
         <v>100(85)</v>
       </c>
       <c r="BM2" s="1" t="str">
-        <f>ROUND(K2,0)&amp;"("&amp;ROUND((K2-AM2)/K2*100,0)&amp;")"</f>
+        <f t="shared" ref="BM2:BM33" si="10">ROUND(K2,0)&amp;"("&amp;ROUND((K2-AM2)/K2*100,0)&amp;")"</f>
         <v>85(87)</v>
       </c>
       <c r="BN2" s="1" t="str">
-        <f>ROUND(O2,0)&amp;"("&amp;ROUND((O2-AQ2)/O2*100,0)&amp;")"</f>
+        <f t="shared" ref="BN2:BN33" si="11">ROUND(O2,0)&amp;"("&amp;ROUND((O2-AQ2)/O2*100,0)&amp;")"</f>
         <v>97(65)</v>
       </c>
     </row>
-    <row r="3" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1727,59 +1727,59 @@
         <v>33.577576443941098</v>
       </c>
       <c r="BB3" s="1" t="str">
-        <f>ROUND(M3,0)&amp;"("&amp;ROUND((M3-AA3)/M3*100,0)&amp;")"</f>
+        <f t="shared" ref="BB2:BB33" si="12">ROUND(M3,0)&amp;"("&amp;ROUND((M3-AA3)/M3*100,0)&amp;")"</f>
         <v>94(32)</v>
       </c>
       <c r="BC3" s="1" t="str">
-        <f>ROUND(G3,0)&amp;"("&amp;ROUND((G3-U3)/G3*100,0)&amp;")"</f>
+        <f t="shared" si="0"/>
         <v>18(34)</v>
       </c>
       <c r="BD3" s="1" t="str">
-        <f>ROUND(I3,0)&amp;"("&amp;ROUND((I3-W3)/I3*100,0)&amp;")"</f>
+        <f t="shared" si="1"/>
         <v>100(93)</v>
       </c>
       <c r="BE3" s="1" t="str">
-        <f>ROUND(K3,0)&amp;"("&amp;ROUND((K3-Y3)/K3*100,0)&amp;")"</f>
+        <f t="shared" si="2"/>
         <v>88(-14)</v>
       </c>
       <c r="BF3" s="1" t="str">
-        <f>ROUND(O3,0)&amp;"("&amp;ROUND((O3-AC3)/O3*100,0)&amp;")"</f>
+        <f t="shared" si="3"/>
         <v>92(15)</v>
       </c>
       <c r="BG3" s="1" t="str">
-        <f>ROUND(C3,0)&amp;"("&amp;ROUND((C3-AE3)/C3*100,0)&amp;")"</f>
+        <f t="shared" si="4"/>
         <v>27(-199)</v>
       </c>
       <c r="BH3" s="1" t="str">
-        <f>ROUND(E3,0)&amp;"("&amp;ROUND((E3-AG3)/E3*100,1)&amp;")"</f>
+        <f t="shared" si="5"/>
         <v>14(-362.4)</v>
       </c>
       <c r="BI3" s="1" t="str">
-        <f>ROUND(AS3,0)&amp;"("&amp;ROUND((AS3-AU3)/AS3*100,0)&amp;")"</f>
+        <f t="shared" si="6"/>
         <v>44(12)</v>
       </c>
       <c r="BJ3" s="1" t="str">
-        <f>ROUND(M3,0)&amp;"("&amp;ROUND((M3-AO3)/M3*100,0)&amp;")"</f>
+        <f t="shared" si="7"/>
         <v>94(-6)</v>
       </c>
       <c r="BK3" s="1" t="str">
-        <f>ROUND(G3,0)&amp;"("&amp;ROUND((G3-AI3)/G3*100,0)&amp;")"</f>
+        <f t="shared" si="8"/>
         <v>18(61)</v>
       </c>
       <c r="BL3" s="1" t="str">
-        <f>ROUND(I3,0)&amp;"("&amp;ROUND((I3-AK3)/I3*100,0)&amp;")"</f>
+        <f t="shared" si="9"/>
         <v>100(96)</v>
       </c>
       <c r="BM3" s="1" t="str">
-        <f>ROUND(K3,0)&amp;"("&amp;ROUND((K3-AM3)/K3*100,0)&amp;")"</f>
+        <f t="shared" si="10"/>
         <v>88(95)</v>
       </c>
       <c r="BN3" s="1" t="str">
-        <f>ROUND(O3,0)&amp;"("&amp;ROUND((O3-AQ3)/O3*100,0)&amp;")"</f>
+        <f t="shared" si="11"/>
         <v>92(70)</v>
       </c>
     </row>
-    <row r="4" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1940,59 +1940,59 @@
         <v>31.8981937602627</v>
       </c>
       <c r="BB4" s="1" t="str">
-        <f>ROUND(M4,0)&amp;"("&amp;ROUND((M4-AA4)/M4*100,0)&amp;")"</f>
+        <f t="shared" si="12"/>
         <v>91(31)</v>
       </c>
       <c r="BC4" s="1" t="str">
-        <f>ROUND(G4,0)&amp;"("&amp;ROUND((G4-U4)/G4*100,0)&amp;")"</f>
+        <f t="shared" si="0"/>
         <v>14(-144)</v>
       </c>
       <c r="BD4" s="1" t="str">
-        <f>ROUND(I4,0)&amp;"("&amp;ROUND((I4-W4)/I4*100,0)&amp;")"</f>
+        <f t="shared" si="1"/>
         <v>100(89)</v>
       </c>
       <c r="BE4" s="1" t="str">
-        <f>ROUND(K4,0)&amp;"("&amp;ROUND((K4-Y4)/K4*100,0)&amp;")"</f>
+        <f t="shared" si="2"/>
         <v>88(-13)</v>
       </c>
       <c r="BF4" s="1" t="str">
-        <f>ROUND(O4,0)&amp;"("&amp;ROUND((O4-AC4)/O4*100,0)&amp;")"</f>
+        <f t="shared" si="3"/>
         <v>96(29)</v>
       </c>
       <c r="BG4" s="1" t="str">
-        <f>ROUND(C4,0)&amp;"("&amp;ROUND((C4-AE4)/C4*100,0)&amp;")"</f>
+        <f t="shared" si="4"/>
         <v>17(-405)</v>
       </c>
       <c r="BH4" s="1" t="str">
-        <f>ROUND(E4,0)&amp;"("&amp;ROUND((E4-AG4)/E4*100,1)&amp;")"</f>
+        <f t="shared" si="5"/>
         <v>35(-49.2)</v>
       </c>
       <c r="BI4" s="1" t="str">
-        <f>ROUND(AS4,0)&amp;"("&amp;ROUND((AS4-AU4)/AS4*100,0)&amp;")"</f>
+        <f t="shared" si="6"/>
         <v>50(18)</v>
       </c>
       <c r="BJ4" s="1" t="str">
-        <f>ROUND(M4,0)&amp;"("&amp;ROUND((M4-AO4)/M4*100,0)&amp;")"</f>
+        <f t="shared" si="7"/>
         <v>91(-9)</v>
       </c>
       <c r="BK4" s="1" t="str">
-        <f>ROUND(G4,0)&amp;"("&amp;ROUND((G4-AI4)/G4*100,0)&amp;")"</f>
+        <f t="shared" si="8"/>
         <v>14(14)</v>
       </c>
       <c r="BL4" s="1" t="str">
-        <f>ROUND(I4,0)&amp;"("&amp;ROUND((I4-AK4)/I4*100,0)&amp;")"</f>
+        <f t="shared" si="9"/>
         <v>100(86)</v>
       </c>
       <c r="BM4" s="1" t="str">
-        <f>ROUND(K4,0)&amp;"("&amp;ROUND((K4-AM4)/K4*100,0)&amp;")"</f>
+        <f t="shared" si="10"/>
         <v>88(89)</v>
       </c>
       <c r="BN4" s="1" t="str">
-        <f>ROUND(O4,0)&amp;"("&amp;ROUND((O4-AQ4)/O4*100,0)&amp;")"</f>
+        <f t="shared" si="11"/>
         <v>96(68)</v>
       </c>
     </row>
-    <row r="5" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -2153,59 +2153,59 @@
         <v>43.373814041745703</v>
       </c>
       <c r="BB5" s="1" t="str">
-        <f>ROUND(M5,0)&amp;"("&amp;ROUND((M5-AA5)/M5*100,0)&amp;")"</f>
+        <f t="shared" si="12"/>
         <v>91(12)</v>
       </c>
       <c r="BC5" s="1" t="str">
-        <f>ROUND(G5,0)&amp;"("&amp;ROUND((G5-U5)/G5*100,0)&amp;")"</f>
+        <f t="shared" si="0"/>
         <v>7(-72)</v>
       </c>
       <c r="BD5" s="1" t="str">
-        <f>ROUND(I5,0)&amp;"("&amp;ROUND((I5-W5)/I5*100,0)&amp;")"</f>
+        <f t="shared" si="1"/>
         <v>100(93)</v>
       </c>
       <c r="BE5" s="1" t="str">
-        <f>ROUND(K5,0)&amp;"("&amp;ROUND((K5-Y5)/K5*100,0)&amp;")"</f>
+        <f t="shared" si="2"/>
         <v>92(-8)</v>
       </c>
       <c r="BF5" s="1" t="str">
-        <f>ROUND(O5,0)&amp;"("&amp;ROUND((O5-AC5)/O5*100,0)&amp;")"</f>
+        <f t="shared" si="3"/>
         <v>92(14)</v>
       </c>
       <c r="BG5" s="1" t="str">
-        <f>ROUND(C5,0)&amp;"("&amp;ROUND((C5-AE5)/C5*100,0)&amp;")"</f>
+        <f t="shared" si="4"/>
         <v>24(-264)</v>
       </c>
       <c r="BH5" s="1" t="str">
-        <f>ROUND(E5,0)&amp;"("&amp;ROUND((E5-AG5)/E5*100,1)&amp;")"</f>
+        <f t="shared" si="5"/>
         <v>15(-341.5)</v>
       </c>
       <c r="BI5" s="1" t="str">
-        <f>ROUND(AS5,0)&amp;"("&amp;ROUND((AS5-AU5)/AS5*100,0)&amp;")"</f>
+        <f t="shared" si="6"/>
         <v>80(24)</v>
       </c>
       <c r="BJ5" s="1" t="str">
-        <f>ROUND(M5,0)&amp;"("&amp;ROUND((M5-AO5)/M5*100,0)&amp;")"</f>
+        <f t="shared" si="7"/>
         <v>91(-8)</v>
       </c>
       <c r="BK5" s="1" t="str">
-        <f>ROUND(G5,0)&amp;"("&amp;ROUND((G5-AI5)/G5*100,0)&amp;")"</f>
+        <f t="shared" si="8"/>
         <v>7(-93)</v>
       </c>
       <c r="BL5" s="1" t="str">
-        <f>ROUND(I5,0)&amp;"("&amp;ROUND((I5-AK5)/I5*100,0)&amp;")"</f>
+        <f t="shared" si="9"/>
         <v>100(92)</v>
       </c>
       <c r="BM5" s="1" t="str">
-        <f>ROUND(K5,0)&amp;"("&amp;ROUND((K5-AM5)/K5*100,0)&amp;")"</f>
+        <f t="shared" si="10"/>
         <v>92(93)</v>
       </c>
       <c r="BN5" s="1" t="str">
-        <f>ROUND(O5,0)&amp;"("&amp;ROUND((O5-AQ5)/O5*100,0)&amp;")"</f>
+        <f t="shared" si="11"/>
         <v>92(31)</v>
       </c>
     </row>
-    <row r="6" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -2366,59 +2366,59 @@
         <v>62.988888888888901</v>
       </c>
       <c r="BB6" s="1" t="str">
-        <f>ROUND(M6,0)&amp;"("&amp;ROUND((M6-AA6)/M6*100,0)&amp;")"</f>
+        <f t="shared" si="12"/>
         <v>93(-1)</v>
       </c>
       <c r="BC6" s="1" t="str">
-        <f>ROUND(G6,0)&amp;"("&amp;ROUND((G6-U6)/G6*100,0)&amp;")"</f>
+        <f t="shared" si="0"/>
         <v>26(48)</v>
       </c>
       <c r="BD6" s="1" t="str">
-        <f>ROUND(I6,0)&amp;"("&amp;ROUND((I6-W6)/I6*100,0)&amp;")"</f>
+        <f t="shared" si="1"/>
         <v>100(74)</v>
       </c>
       <c r="BE6" s="1" t="str">
-        <f>ROUND(K6,0)&amp;"("&amp;ROUND((K6-Y6)/K6*100,0)&amp;")"</f>
+        <f t="shared" si="2"/>
         <v>94(-7)</v>
       </c>
       <c r="BF6" s="1" t="str">
-        <f>ROUND(O6,0)&amp;"("&amp;ROUND((O6-AC6)/O6*100,0)&amp;")"</f>
+        <f t="shared" si="3"/>
         <v>93(0)</v>
       </c>
       <c r="BG6" s="1" t="str">
-        <f>ROUND(C6,0)&amp;"("&amp;ROUND((C6-AE6)/C6*100,0)&amp;")"</f>
+        <f t="shared" si="4"/>
         <v>30(-203)</v>
       </c>
       <c r="BH6" s="1" t="str">
-        <f>ROUND(E6,0)&amp;"("&amp;ROUND((E6-AG6)/E6*100,1)&amp;")"</f>
+        <f t="shared" si="5"/>
         <v>14(-534.6)</v>
       </c>
       <c r="BI6" s="1" t="str">
-        <f>ROUND(AS6,0)&amp;"("&amp;ROUND((AS6-AU6)/AS6*100,0)&amp;")"</f>
+        <f t="shared" si="6"/>
         <v>92(1)</v>
       </c>
       <c r="BJ6" s="1" t="str">
-        <f>ROUND(M6,0)&amp;"("&amp;ROUND((M6-AO6)/M6*100,0)&amp;")"</f>
+        <f t="shared" si="7"/>
         <v>93(-8)</v>
       </c>
       <c r="BK6" s="1" t="str">
-        <f>ROUND(G6,0)&amp;"("&amp;ROUND((G6-AI6)/G6*100,0)&amp;")"</f>
+        <f t="shared" si="8"/>
         <v>26(-16)</v>
       </c>
       <c r="BL6" s="1" t="str">
-        <f>ROUND(I6,0)&amp;"("&amp;ROUND((I6-AK6)/I6*100,0)&amp;")"</f>
+        <f t="shared" si="9"/>
         <v>100(86)</v>
       </c>
       <c r="BM6" s="1" t="str">
-        <f>ROUND(K6,0)&amp;"("&amp;ROUND((K6-AM6)/K6*100,0)&amp;")"</f>
+        <f t="shared" si="10"/>
         <v>94(72)</v>
       </c>
       <c r="BN6" s="1" t="str">
-        <f>ROUND(O6,0)&amp;"("&amp;ROUND((O6-AQ6)/O6*100,0)&amp;")"</f>
+        <f t="shared" si="11"/>
         <v>93(-1)</v>
       </c>
     </row>
-    <row r="7" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -2579,59 +2579,59 @@
         <v>35.217076700434198</v>
       </c>
       <c r="BB7" s="1" t="str">
-        <f>ROUND(M7,0)&amp;"("&amp;ROUND((M7-AA7)/M7*100,0)&amp;")"</f>
+        <f t="shared" si="12"/>
         <v>91(26)</v>
       </c>
       <c r="BC7" s="1" t="str">
-        <f>ROUND(G7,0)&amp;"("&amp;ROUND((G7-U7)/G7*100,0)&amp;")"</f>
+        <f t="shared" si="0"/>
         <v>9(-174)</v>
       </c>
       <c r="BD7" s="1" t="str">
-        <f>ROUND(I7,0)&amp;"("&amp;ROUND((I7-W7)/I7*100,0)&amp;")"</f>
+        <f t="shared" si="1"/>
         <v>100(94)</v>
       </c>
       <c r="BE7" s="1" t="str">
-        <f>ROUND(K7,0)&amp;"("&amp;ROUND((K7-Y7)/K7*100,0)&amp;")"</f>
+        <f t="shared" si="2"/>
         <v>85(-18)</v>
       </c>
       <c r="BF7" s="1" t="str">
-        <f>ROUND(O7,0)&amp;"("&amp;ROUND((O7-AC7)/O7*100,0)&amp;")"</f>
+        <f t="shared" si="3"/>
         <v>97(20)</v>
       </c>
       <c r="BG7" s="1" t="str">
-        <f>ROUND(C7,0)&amp;"("&amp;ROUND((C7-AE7)/C7*100,0)&amp;")"</f>
+        <f t="shared" si="4"/>
         <v>18(-407)</v>
       </c>
       <c r="BH7" s="1" t="str">
-        <f>ROUND(E7,0)&amp;"("&amp;ROUND((E7-AG7)/E7*100,1)&amp;")"</f>
+        <f t="shared" si="5"/>
         <v>27(-137.3)</v>
       </c>
       <c r="BI7" s="1" t="str">
-        <f>ROUND(AS7,0)&amp;"("&amp;ROUND((AS7-AU7)/AS7*100,0)&amp;")"</f>
+        <f t="shared" si="6"/>
         <v>57(-6)</v>
       </c>
       <c r="BJ7" s="1" t="str">
-        <f>ROUND(M7,0)&amp;"("&amp;ROUND((M7-AO7)/M7*100,0)&amp;")"</f>
+        <f t="shared" si="7"/>
         <v>91(-10)</v>
       </c>
       <c r="BK7" s="1" t="str">
-        <f>ROUND(G7,0)&amp;"("&amp;ROUND((G7-AI7)/G7*100,0)&amp;")"</f>
+        <f t="shared" si="8"/>
         <v>9(11)</v>
       </c>
       <c r="BL7" s="1" t="str">
-        <f>ROUND(I7,0)&amp;"("&amp;ROUND((I7-AK7)/I7*100,0)&amp;")"</f>
+        <f t="shared" si="9"/>
         <v>100(88)</v>
       </c>
       <c r="BM7" s="1" t="str">
-        <f>ROUND(K7,0)&amp;"("&amp;ROUND((K7-AM7)/K7*100,0)&amp;")"</f>
+        <f t="shared" si="10"/>
         <v>85(94)</v>
       </c>
       <c r="BN7" s="1" t="str">
-        <f>ROUND(O7,0)&amp;"("&amp;ROUND((O7-AQ7)/O7*100,0)&amp;")"</f>
+        <f t="shared" si="11"/>
         <v>97(55)</v>
       </c>
     </row>
-    <row r="8" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -2792,59 +2792,59 @@
         <v>41.015375854214099</v>
       </c>
       <c r="BB8" s="1" t="str">
-        <f>ROUND(M8,0)&amp;"("&amp;ROUND((M8-AA8)/M8*100,0)&amp;")"</f>
+        <f t="shared" si="12"/>
         <v>88(10)</v>
       </c>
       <c r="BC8" s="1" t="str">
-        <f>ROUND(G8,0)&amp;"("&amp;ROUND((G8-U8)/G8*100,0)&amp;")"</f>
+        <f t="shared" si="0"/>
         <v>8(-227)</v>
       </c>
       <c r="BD8" s="1" t="str">
-        <f>ROUND(I8,0)&amp;"("&amp;ROUND((I8-W8)/I8*100,0)&amp;")"</f>
+        <f t="shared" si="1"/>
         <v>100(93)</v>
       </c>
       <c r="BE8" s="1" t="str">
-        <f>ROUND(K8,0)&amp;"("&amp;ROUND((K8-Y8)/K8*100,0)&amp;")"</f>
+        <f t="shared" si="2"/>
         <v>91(-10)</v>
       </c>
       <c r="BF8" s="1" t="str">
-        <f>ROUND(O8,0)&amp;"("&amp;ROUND((O8-AC8)/O8*100,0)&amp;")"</f>
+        <f t="shared" si="3"/>
         <v>92(17)</v>
       </c>
       <c r="BG8" s="1" t="str">
-        <f>ROUND(C8,0)&amp;"("&amp;ROUND((C8-AE8)/C8*100,0)&amp;")"</f>
+        <f t="shared" si="4"/>
         <v>30(-187)</v>
       </c>
       <c r="BH8" s="1" t="str">
-        <f>ROUND(E8,0)&amp;"("&amp;ROUND((E8-AG8)/E8*100,1)&amp;")"</f>
+        <f t="shared" si="5"/>
         <v>27(-133.4)</v>
       </c>
       <c r="BI8" s="1" t="str">
-        <f>ROUND(AS8,0)&amp;"("&amp;ROUND((AS8-AU8)/AS8*100,0)&amp;")"</f>
+        <f t="shared" si="6"/>
         <v>77(23)</v>
       </c>
       <c r="BJ8" s="1" t="str">
-        <f>ROUND(M8,0)&amp;"("&amp;ROUND((M8-AO8)/M8*100,0)&amp;")"</f>
+        <f t="shared" si="7"/>
         <v>88(-12)</v>
       </c>
       <c r="BK8" s="1" t="str">
-        <f>ROUND(G8,0)&amp;"("&amp;ROUND((G8-AI8)/G8*100,0)&amp;")"</f>
+        <f t="shared" si="8"/>
         <v>8(-140)</v>
       </c>
       <c r="BL8" s="1" t="str">
-        <f>ROUND(I8,0)&amp;"("&amp;ROUND((I8-AK8)/I8*100,0)&amp;")"</f>
+        <f t="shared" si="9"/>
         <v>100(85)</v>
       </c>
       <c r="BM8" s="1" t="str">
-        <f>ROUND(K8,0)&amp;"("&amp;ROUND((K8-AM8)/K8*100,0)&amp;")"</f>
+        <f t="shared" si="10"/>
         <v>91(93)</v>
       </c>
       <c r="BN8" s="1" t="str">
-        <f>ROUND(O8,0)&amp;"("&amp;ROUND((O8-AQ8)/O8*100,0)&amp;")"</f>
+        <f t="shared" si="11"/>
         <v>92(31)</v>
       </c>
     </row>
-    <row r="9" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
@@ -3005,59 +3005,59 @@
         <v>57.961051004636801</v>
       </c>
       <c r="BB9" s="1" t="str">
-        <f>ROUND(M9,0)&amp;"("&amp;ROUND((M9-AA9)/M9*100,0)&amp;")"</f>
+        <f t="shared" si="12"/>
         <v>93(3)</v>
       </c>
       <c r="BC9" s="1" t="str">
-        <f>ROUND(G9,0)&amp;"("&amp;ROUND((G9-U9)/G9*100,0)&amp;")"</f>
+        <f t="shared" si="0"/>
         <v>12(-12)</v>
       </c>
       <c r="BD9" s="1" t="str">
-        <f>ROUND(I9,0)&amp;"("&amp;ROUND((I9-W9)/I9*100,0)&amp;")"</f>
+        <f t="shared" si="1"/>
         <v>100(90)</v>
       </c>
       <c r="BE9" s="1" t="str">
-        <f>ROUND(K9,0)&amp;"("&amp;ROUND((K9-Y9)/K9*100,0)&amp;")"</f>
+        <f t="shared" si="2"/>
         <v>94(-6)</v>
       </c>
       <c r="BF9" s="1" t="str">
-        <f>ROUND(O9,0)&amp;"("&amp;ROUND((O9-AC9)/O9*100,0)&amp;")"</f>
+        <f t="shared" si="3"/>
         <v>94(5)</v>
       </c>
       <c r="BG9" s="1" t="str">
-        <f>ROUND(C9,0)&amp;"("&amp;ROUND((C9-AE9)/C9*100,0)&amp;")"</f>
+        <f t="shared" si="4"/>
         <v>29(-215)</v>
       </c>
       <c r="BH9" s="1" t="str">
-        <f>ROUND(E9,0)&amp;"("&amp;ROUND((E9-AG9)/E9*100,1)&amp;")"</f>
+        <f t="shared" si="5"/>
         <v>14(-517.8)</v>
       </c>
       <c r="BI9" s="1" t="str">
-        <f>ROUND(AS9,0)&amp;"("&amp;ROUND((AS9-AU9)/AS9*100,0)&amp;")"</f>
+        <f t="shared" si="6"/>
         <v>85(6)</v>
       </c>
       <c r="BJ9" s="1" t="str">
-        <f>ROUND(M9,0)&amp;"("&amp;ROUND((M9-AO9)/M9*100,0)&amp;")"</f>
+        <f t="shared" si="7"/>
         <v>93(-8)</v>
       </c>
       <c r="BK9" s="1" t="str">
-        <f>ROUND(G9,0)&amp;"("&amp;ROUND((G9-AI9)/G9*100,0)&amp;")"</f>
+        <f t="shared" si="8"/>
         <v>12(-113)</v>
       </c>
       <c r="BL9" s="1" t="str">
-        <f>ROUND(I9,0)&amp;"("&amp;ROUND((I9-AK9)/I9*100,0)&amp;")"</f>
+        <f t="shared" si="9"/>
         <v>100(89)</v>
       </c>
       <c r="BM9" s="1" t="str">
-        <f>ROUND(K9,0)&amp;"("&amp;ROUND((K9-AM9)/K9*100,0)&amp;")"</f>
+        <f t="shared" si="10"/>
         <v>94(89)</v>
       </c>
       <c r="BN9" s="1" t="str">
-        <f>ROUND(O9,0)&amp;"("&amp;ROUND((O9-AQ9)/O9*100,0)&amp;")"</f>
+        <f t="shared" si="11"/>
         <v>94(16)</v>
       </c>
     </row>
-    <row r="10" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
@@ -3218,59 +3218,59 @@
         <v>24.0894160583942</v>
       </c>
       <c r="BB10" s="1" t="str">
-        <f>ROUND(M10,0)&amp;"("&amp;ROUND((M10-AA10)/M10*100,0)&amp;")"</f>
+        <f t="shared" si="12"/>
         <v>85(23)</v>
       </c>
       <c r="BC10" s="1" t="str">
-        <f>ROUND(G10,0)&amp;"("&amp;ROUND((G10-U10)/G10*100,0)&amp;")"</f>
+        <f t="shared" si="0"/>
         <v>10(-261)</v>
       </c>
       <c r="BD10" s="1" t="str">
-        <f>ROUND(I10,0)&amp;"("&amp;ROUND((I10-W10)/I10*100,0)&amp;")"</f>
+        <f t="shared" si="1"/>
         <v>100(91)</v>
       </c>
       <c r="BE10" s="1" t="str">
-        <f>ROUND(K10,0)&amp;"("&amp;ROUND((K10-Y10)/K10*100,0)&amp;")"</f>
+        <f t="shared" si="2"/>
         <v>86(-14)</v>
       </c>
       <c r="BF10" s="1" t="str">
-        <f>ROUND(O10,0)&amp;"("&amp;ROUND((O10-AC10)/O10*100,0)&amp;")"</f>
+        <f t="shared" si="3"/>
         <v>98(34)</v>
       </c>
       <c r="BG10" s="1" t="str">
-        <f>ROUND(C10,0)&amp;"("&amp;ROUND((C10-AE10)/C10*100,0)&amp;")"</f>
+        <f t="shared" si="4"/>
         <v>37(-160)</v>
       </c>
       <c r="BH10" s="1" t="str">
-        <f>ROUND(E10,0)&amp;"("&amp;ROUND((E10-AG10)/E10*100,1)&amp;")"</f>
+        <f t="shared" si="5"/>
         <v>37(9.6)</v>
       </c>
       <c r="BI10" s="1" t="str">
-        <f>ROUND(AS10,0)&amp;"("&amp;ROUND((AS10-AU10)/AS10*100,0)&amp;")"</f>
+        <f t="shared" si="6"/>
         <v>64(22)</v>
       </c>
       <c r="BJ10" s="1" t="str">
-        <f>ROUND(M10,0)&amp;"("&amp;ROUND((M10-AO10)/M10*100,0)&amp;")"</f>
+        <f t="shared" si="7"/>
         <v>85(-13)</v>
       </c>
       <c r="BK10" s="1" t="str">
-        <f>ROUND(G10,0)&amp;"("&amp;ROUND((G10-AI10)/G10*100,0)&amp;")"</f>
+        <f t="shared" si="8"/>
         <v>10(-89)</v>
       </c>
       <c r="BL10" s="1" t="str">
-        <f>ROUND(I10,0)&amp;"("&amp;ROUND((I10-AK10)/I10*100,0)&amp;")"</f>
+        <f t="shared" si="9"/>
         <v>100(83)</v>
       </c>
       <c r="BM10" s="1" t="str">
-        <f>ROUND(K10,0)&amp;"("&amp;ROUND((K10-AM10)/K10*100,0)&amp;")"</f>
+        <f t="shared" si="10"/>
         <v>86(90)</v>
       </c>
       <c r="BN10" s="1" t="str">
-        <f>ROUND(O10,0)&amp;"("&amp;ROUND((O10-AQ10)/O10*100,0)&amp;")"</f>
+        <f t="shared" si="11"/>
         <v>98(53)</v>
       </c>
     </row>
-    <row r="11" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
@@ -3431,59 +3431,59 @@
         <v>30.502563593662099</v>
       </c>
       <c r="BB11" s="1" t="str">
-        <f>ROUND(M11,0)&amp;"("&amp;ROUND((M11-AA11)/M11*100,0)&amp;")"</f>
+        <f t="shared" si="12"/>
         <v>93(34)</v>
       </c>
       <c r="BC11" s="1" t="str">
-        <f>ROUND(G11,0)&amp;"("&amp;ROUND((G11-U11)/G11*100,0)&amp;")"</f>
+        <f t="shared" si="0"/>
         <v>7(-479)</v>
       </c>
       <c r="BD11" s="1" t="str">
-        <f>ROUND(I11,0)&amp;"("&amp;ROUND((I11-W11)/I11*100,0)&amp;")"</f>
+        <f t="shared" si="1"/>
         <v>100(96)</v>
       </c>
       <c r="BE11" s="1" t="str">
-        <f>ROUND(K11,0)&amp;"("&amp;ROUND((K11-Y11)/K11*100,0)&amp;")"</f>
+        <f t="shared" si="2"/>
         <v>84(-18)</v>
       </c>
       <c r="BF11" s="1" t="str">
-        <f>ROUND(O11,0)&amp;"("&amp;ROUND((O11-AC11)/O11*100,0)&amp;")"</f>
+        <f t="shared" si="3"/>
         <v>99(22)</v>
       </c>
       <c r="BG11" s="1" t="str">
-        <f>ROUND(C11,0)&amp;"("&amp;ROUND((C11-AE11)/C11*100,0)&amp;")"</f>
+        <f t="shared" si="4"/>
         <v>43(-124)</v>
       </c>
       <c r="BH11" s="1" t="str">
-        <f>ROUND(E11,0)&amp;"("&amp;ROUND((E11-AG11)/E11*100,1)&amp;")"</f>
+        <f t="shared" si="5"/>
         <v>47(-25.9)</v>
       </c>
       <c r="BI11" s="1" t="str">
-        <f>ROUND(AS11,0)&amp;"("&amp;ROUND((AS11-AU11)/AS11*100,0)&amp;")"</f>
+        <f t="shared" si="6"/>
         <v>51(-10)</v>
       </c>
       <c r="BJ11" s="1" t="str">
-        <f>ROUND(M11,0)&amp;"("&amp;ROUND((M11-AO11)/M11*100,0)&amp;")"</f>
+        <f t="shared" si="7"/>
         <v>93(-7)</v>
       </c>
       <c r="BK11" s="1" t="str">
-        <f>ROUND(G11,0)&amp;"("&amp;ROUND((G11-AI11)/G11*100,0)&amp;")"</f>
+        <f t="shared" si="8"/>
         <v>7(-32)</v>
       </c>
       <c r="BL11" s="1" t="str">
-        <f>ROUND(I11,0)&amp;"("&amp;ROUND((I11-AK11)/I11*100,0)&amp;")"</f>
+        <f t="shared" si="9"/>
         <v>100(88)</v>
       </c>
       <c r="BM11" s="1" t="str">
-        <f>ROUND(K11,0)&amp;"("&amp;ROUND((K11-AM11)/K11*100,0)&amp;")"</f>
+        <f t="shared" si="10"/>
         <v>84(97)</v>
       </c>
       <c r="BN11" s="1" t="str">
-        <f>ROUND(O11,0)&amp;"("&amp;ROUND((O11-AQ11)/O11*100,0)&amp;")"</f>
+        <f t="shared" si="11"/>
         <v>99(72)</v>
       </c>
     </row>
-    <row r="12" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
@@ -3644,59 +3644,59 @@
         <v>24.2040970726881</v>
       </c>
       <c r="BB12" s="1" t="str">
-        <f>ROUND(M12,0)&amp;"("&amp;ROUND((M12-AA12)/M12*100,0)&amp;")"</f>
+        <f t="shared" si="12"/>
         <v>83(48)</v>
       </c>
       <c r="BC12" s="1" t="str">
-        <f>ROUND(G12,0)&amp;"("&amp;ROUND((G12-U12)/G12*100,0)&amp;")"</f>
+        <f t="shared" si="0"/>
         <v>10(-181)</v>
       </c>
       <c r="BD12" s="1" t="str">
-        <f>ROUND(I12,0)&amp;"("&amp;ROUND((I12-W12)/I12*100,0)&amp;")"</f>
+        <f t="shared" si="1"/>
         <v>100(95)</v>
       </c>
       <c r="BE12" s="1" t="str">
-        <f>ROUND(K12,0)&amp;"("&amp;ROUND((K12-Y12)/K12*100,0)&amp;")"</f>
+        <f t="shared" si="2"/>
         <v>64(-56)</v>
       </c>
       <c r="BF12" s="1" t="str">
-        <f>ROUND(O12,0)&amp;"("&amp;ROUND((O12-AC12)/O12*100,0)&amp;")"</f>
+        <f t="shared" si="3"/>
         <v>99(38)</v>
       </c>
       <c r="BG12" s="1" t="str">
-        <f>ROUND(C12,0)&amp;"("&amp;ROUND((C12-AE12)/C12*100,0)&amp;")"</f>
+        <f t="shared" si="4"/>
         <v>35(-172)</v>
       </c>
       <c r="BH12" s="1" t="str">
-        <f>ROUND(E12,0)&amp;"("&amp;ROUND((E12-AG12)/E12*100,1)&amp;")"</f>
+        <f t="shared" si="5"/>
         <v>31(-58.6)</v>
       </c>
       <c r="BI12" s="1" t="str">
-        <f>ROUND(AS12,0)&amp;"("&amp;ROUND((AS12-AU12)/AS12*100,0)&amp;")"</f>
+        <f t="shared" si="6"/>
         <v>36(-87)</v>
       </c>
       <c r="BJ12" s="1" t="str">
-        <f>ROUND(M12,0)&amp;"("&amp;ROUND((M12-AO12)/M12*100,0)&amp;")"</f>
+        <f t="shared" si="7"/>
         <v>83(-21)</v>
       </c>
       <c r="BK12" s="1" t="str">
-        <f>ROUND(G12,0)&amp;"("&amp;ROUND((G12-AI12)/G12*100,0)&amp;")"</f>
+        <f t="shared" si="8"/>
         <v>10(3)</v>
       </c>
       <c r="BL12" s="1" t="str">
-        <f>ROUND(I12,0)&amp;"("&amp;ROUND((I12-AK12)/I12*100,0)&amp;")"</f>
+        <f t="shared" si="9"/>
         <v>100(91)</v>
       </c>
       <c r="BM12" s="1" t="str">
-        <f>ROUND(K12,0)&amp;"("&amp;ROUND((K12-AM12)/K12*100,0)&amp;")"</f>
+        <f t="shared" si="10"/>
         <v>64(96)</v>
       </c>
       <c r="BN12" s="1" t="str">
-        <f>ROUND(O12,0)&amp;"("&amp;ROUND((O12-AQ12)/O12*100,0)&amp;")"</f>
+        <f t="shared" si="11"/>
         <v>99(79)</v>
       </c>
     </row>
-    <row r="13" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
@@ -3857,59 +3857,59 @@
         <v>43.0877522290005</v>
       </c>
       <c r="BB13" s="1" t="str">
-        <f>ROUND(M13,0)&amp;"("&amp;ROUND((M13-AA13)/M13*100,0)&amp;")"</f>
+        <f t="shared" si="12"/>
         <v>91(23)</v>
       </c>
       <c r="BC13" s="1" t="str">
-        <f>ROUND(G13,0)&amp;"("&amp;ROUND((G13-U13)/G13*100,0)&amp;")"</f>
+        <f t="shared" si="0"/>
         <v>52(87)</v>
       </c>
       <c r="BD13" s="1" t="str">
-        <f>ROUND(I13,0)&amp;"("&amp;ROUND((I13-W13)/I13*100,0)&amp;")"</f>
+        <f t="shared" si="1"/>
         <v>100(68)</v>
       </c>
       <c r="BE13" s="1" t="str">
-        <f>ROUND(K13,0)&amp;"("&amp;ROUND((K13-Y13)/K13*100,0)&amp;")"</f>
+        <f t="shared" si="2"/>
         <v>86(-16)</v>
       </c>
       <c r="BF13" s="1" t="str">
-        <f>ROUND(O13,0)&amp;"("&amp;ROUND((O13-AC13)/O13*100,0)&amp;")"</f>
+        <f t="shared" si="3"/>
         <v>97(15)</v>
       </c>
       <c r="BG13" s="1" t="str">
-        <f>ROUND(C13,0)&amp;"("&amp;ROUND((C13-AE13)/C13*100,0)&amp;")"</f>
+        <f t="shared" si="4"/>
         <v>45(-107)</v>
       </c>
       <c r="BH13" s="1" t="str">
-        <f>ROUND(E13,0)&amp;"("&amp;ROUND((E13-AG13)/E13*100,1)&amp;")"</f>
+        <f t="shared" si="5"/>
         <v>8(-1014.7)</v>
       </c>
       <c r="BI13" s="1" t="str">
-        <f>ROUND(AS13,0)&amp;"("&amp;ROUND((AS13-AU13)/AS13*100,0)&amp;")"</f>
+        <f t="shared" si="6"/>
         <v>42(-67)</v>
       </c>
       <c r="BJ13" s="1" t="str">
-        <f>ROUND(M13,0)&amp;"("&amp;ROUND((M13-AO13)/M13*100,0)&amp;")"</f>
+        <f t="shared" si="7"/>
         <v>91(-10)</v>
       </c>
       <c r="BK13" s="1" t="str">
-        <f>ROUND(G13,0)&amp;"("&amp;ROUND((G13-AI13)/G13*100,0)&amp;")"</f>
+        <f t="shared" si="8"/>
         <v>52(70)</v>
       </c>
       <c r="BL13" s="1" t="str">
-        <f>ROUND(I13,0)&amp;"("&amp;ROUND((I13-AK13)/I13*100,0)&amp;")"</f>
+        <f t="shared" si="9"/>
         <v>100(96)</v>
       </c>
       <c r="BM13" s="1" t="str">
-        <f>ROUND(K13,0)&amp;"("&amp;ROUND((K13-AM13)/K13*100,0)&amp;")"</f>
+        <f t="shared" si="10"/>
         <v>86(79)</v>
       </c>
       <c r="BN13" s="1" t="str">
-        <f>ROUND(O13,0)&amp;"("&amp;ROUND((O13-AQ13)/O13*100,0)&amp;")"</f>
+        <f t="shared" si="11"/>
         <v>97(66)</v>
       </c>
     </row>
-    <row r="14" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
@@ -4070,59 +4070,59 @@
         <v>57.435961203680698</v>
       </c>
       <c r="BB14" s="1" t="str">
-        <f>ROUND(M14,0)&amp;"("&amp;ROUND((M14-AA14)/M14*100,0)&amp;")"</f>
+        <f t="shared" si="12"/>
         <v>93(29)</v>
       </c>
       <c r="BC14" s="1" t="str">
-        <f>ROUND(G14,0)&amp;"("&amp;ROUND((G14-U14)/G14*100,0)&amp;")"</f>
+        <f t="shared" si="0"/>
         <v>81(30)</v>
       </c>
       <c r="BD14" s="1" t="str">
-        <f>ROUND(I14,0)&amp;"("&amp;ROUND((I14-W14)/I14*100,0)&amp;")"</f>
+        <f t="shared" si="1"/>
         <v>100(34)</v>
       </c>
       <c r="BE14" s="1" t="str">
-        <f>ROUND(K14,0)&amp;"("&amp;ROUND((K14-Y14)/K14*100,0)&amp;")"</f>
+        <f t="shared" si="2"/>
         <v>81(-23)</v>
       </c>
       <c r="BF14" s="1" t="str">
-        <f>ROUND(O14,0)&amp;"("&amp;ROUND((O14-AC14)/O14*100,0)&amp;")"</f>
+        <f t="shared" si="3"/>
         <v>97(12)</v>
       </c>
       <c r="BG14" s="1" t="str">
-        <f>ROUND(C14,0)&amp;"("&amp;ROUND((C14-AE14)/C14*100,0)&amp;")"</f>
+        <f t="shared" si="4"/>
         <v>68(-33)</v>
       </c>
       <c r="BH14" s="1" t="str">
-        <f>ROUND(E14,0)&amp;"("&amp;ROUND((E14-AG14)/E14*100,1)&amp;")"</f>
+        <f t="shared" si="5"/>
         <v>60(-49.5)</v>
       </c>
       <c r="BI14" s="1" t="str">
-        <f>ROUND(AS14,0)&amp;"("&amp;ROUND((AS14-AU14)/AS14*100,0)&amp;")"</f>
+        <f t="shared" si="6"/>
         <v>56(-26)</v>
       </c>
       <c r="BJ14" s="1" t="str">
-        <f>ROUND(M14,0)&amp;"("&amp;ROUND((M14-AO14)/M14*100,0)&amp;")"</f>
+        <f t="shared" si="7"/>
         <v>93(-7)</v>
       </c>
       <c r="BK14" s="1" t="str">
-        <f>ROUND(G14,0)&amp;"("&amp;ROUND((G14-AI14)/G14*100,0)&amp;")"</f>
+        <f t="shared" si="8"/>
         <v>81(63)</v>
       </c>
       <c r="BL14" s="1" t="str">
-        <f>ROUND(I14,0)&amp;"("&amp;ROUND((I14-AK14)/I14*100,0)&amp;")"</f>
+        <f t="shared" si="9"/>
         <v>100(72)</v>
       </c>
       <c r="BM14" s="1" t="str">
-        <f>ROUND(K14,0)&amp;"("&amp;ROUND((K14-AM14)/K14*100,0)&amp;")"</f>
+        <f t="shared" si="10"/>
         <v>81(56)</v>
       </c>
       <c r="BN14" s="1" t="str">
-        <f>ROUND(O14,0)&amp;"("&amp;ROUND((O14-AQ14)/O14*100,0)&amp;")"</f>
+        <f t="shared" si="11"/>
         <v>97(63)</v>
       </c>
     </row>
-    <row r="15" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
@@ -4283,59 +4283,59 @@
         <v>54.853658536585399</v>
       </c>
       <c r="BB15" s="1" t="str">
-        <f>ROUND(M15,0)&amp;"("&amp;ROUND((M15-AA15)/M15*100,0)&amp;")"</f>
+        <f t="shared" si="12"/>
         <v>96(42)</v>
       </c>
       <c r="BC15" s="1" t="str">
-        <f>ROUND(G15,0)&amp;"("&amp;ROUND((G15-U15)/G15*100,0)&amp;")"</f>
+        <f t="shared" si="0"/>
         <v>87(34)</v>
       </c>
       <c r="BD15" s="1" t="str">
-        <f>ROUND(I15,0)&amp;"("&amp;ROUND((I15-W15)/I15*100,0)&amp;")"</f>
+        <f t="shared" si="1"/>
         <v>100(34)</v>
       </c>
       <c r="BE15" s="1" t="str">
-        <f>ROUND(K15,0)&amp;"("&amp;ROUND((K15-Y15)/K15*100,0)&amp;")"</f>
+        <f t="shared" si="2"/>
         <v>76(-32)</v>
       </c>
       <c r="BF15" s="1" t="str">
-        <f>ROUND(O15,0)&amp;"("&amp;ROUND((O15-AC15)/O15*100,0)&amp;")"</f>
+        <f t="shared" si="3"/>
         <v>96(14)</v>
       </c>
       <c r="BG15" s="1" t="str">
-        <f>ROUND(C15,0)&amp;"("&amp;ROUND((C15-AE15)/C15*100,0)&amp;")"</f>
+        <f t="shared" si="4"/>
         <v>74(-20)</v>
       </c>
       <c r="BH15" s="1" t="str">
-        <f>ROUND(E15,0)&amp;"("&amp;ROUND((E15-AG15)/E15*100,1)&amp;")"</f>
+        <f t="shared" si="5"/>
         <v>62(-49.3)</v>
       </c>
       <c r="BI15" s="1" t="str">
-        <f>ROUND(AS15,0)&amp;"("&amp;ROUND((AS15-AU15)/AS15*100,0)&amp;")"</f>
+        <f t="shared" si="6"/>
         <v>47(-43)</v>
       </c>
       <c r="BJ15" s="1" t="str">
-        <f>ROUND(M15,0)&amp;"("&amp;ROUND((M15-AO15)/M15*100,0)&amp;")"</f>
+        <f t="shared" si="7"/>
         <v>96(-4)</v>
       </c>
       <c r="BK15" s="1" t="str">
-        <f>ROUND(G15,0)&amp;"("&amp;ROUND((G15-AI15)/G15*100,0)&amp;")"</f>
+        <f t="shared" si="8"/>
         <v>87(74)</v>
       </c>
       <c r="BL15" s="1" t="str">
-        <f>ROUND(I15,0)&amp;"("&amp;ROUND((I15-AK15)/I15*100,0)&amp;")"</f>
+        <f t="shared" si="9"/>
         <v>100(74)</v>
       </c>
       <c r="BM15" s="1" t="str">
-        <f>ROUND(K15,0)&amp;"("&amp;ROUND((K15-AM15)/K15*100,0)&amp;")"</f>
+        <f t="shared" si="10"/>
         <v>76(63)</v>
       </c>
       <c r="BN15" s="1" t="str">
-        <f>ROUND(O15,0)&amp;"("&amp;ROUND((O15-AQ15)/O15*100,0)&amp;")"</f>
+        <f t="shared" si="11"/>
         <v>96(75)</v>
       </c>
     </row>
-    <row r="16" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
@@ -4496,59 +4496,59 @@
         <v>53.4836099585062</v>
       </c>
       <c r="BB16" s="1" t="str">
-        <f>ROUND(M16,0)&amp;"("&amp;ROUND((M16-AA16)/M16*100,0)&amp;")"</f>
+        <f t="shared" si="12"/>
         <v>99(34)</v>
       </c>
       <c r="BC16" s="1" t="str">
-        <f>ROUND(G16,0)&amp;"("&amp;ROUND((G16-U16)/G16*100,0)&amp;")"</f>
+        <f t="shared" si="0"/>
         <v>94(27)</v>
       </c>
       <c r="BD16" s="1" t="str">
-        <f>ROUND(I16,0)&amp;"("&amp;ROUND((I16-W16)/I16*100,0)&amp;")"</f>
+        <f t="shared" si="1"/>
         <v>100(25)</v>
       </c>
       <c r="BE16" s="1" t="str">
-        <f>ROUND(K16,0)&amp;"("&amp;ROUND((K16-Y16)/K16*100,0)&amp;")"</f>
+        <f t="shared" si="2"/>
         <v>87(-15)</v>
       </c>
       <c r="BF16" s="1" t="str">
-        <f>ROUND(O16,0)&amp;"("&amp;ROUND((O16-AC16)/O16*100,0)&amp;")"</f>
+        <f t="shared" si="3"/>
         <v>99(5)</v>
       </c>
       <c r="BG16" s="1" t="str">
-        <f>ROUND(C16,0)&amp;"("&amp;ROUND((C16-AE16)/C16*100,0)&amp;")"</f>
+        <f t="shared" si="4"/>
         <v>84(-15)</v>
       </c>
       <c r="BH16" s="1" t="str">
-        <f>ROUND(E16,0)&amp;"("&amp;ROUND((E16-AG16)/E16*100,1)&amp;")"</f>
+        <f t="shared" si="5"/>
         <v>73(-31.9)</v>
       </c>
       <c r="BI16" s="1" t="str">
-        <f>ROUND(AS16,0)&amp;"("&amp;ROUND((AS16-AU16)/AS16*100,0)&amp;")"</f>
+        <f t="shared" si="6"/>
         <v>53(-53)</v>
       </c>
       <c r="BJ16" s="1" t="str">
-        <f>ROUND(M16,0)&amp;"("&amp;ROUND((M16-AO16)/M16*100,0)&amp;")"</f>
+        <f t="shared" si="7"/>
         <v>99(-1)</v>
       </c>
       <c r="BK16" s="1" t="str">
-        <f>ROUND(G16,0)&amp;"("&amp;ROUND((G16-AI16)/G16*100,0)&amp;")"</f>
+        <f t="shared" si="8"/>
         <v>94(77)</v>
       </c>
       <c r="BL16" s="1" t="str">
-        <f>ROUND(I16,0)&amp;"("&amp;ROUND((I16-AK16)/I16*100,0)&amp;")"</f>
+        <f t="shared" si="9"/>
         <v>100(73)</v>
       </c>
       <c r="BM16" s="1" t="str">
-        <f>ROUND(K16,0)&amp;"("&amp;ROUND((K16-AM16)/K16*100,0)&amp;")"</f>
+        <f t="shared" si="10"/>
         <v>87(69)</v>
       </c>
       <c r="BN16" s="1" t="str">
-        <f>ROUND(O16,0)&amp;"("&amp;ROUND((O16-AQ16)/O16*100,0)&amp;")"</f>
+        <f t="shared" si="11"/>
         <v>99(76)</v>
       </c>
     </row>
-    <row r="17" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>16</v>
       </c>
@@ -4709,59 +4709,59 @@
         <v>22.062291434927701</v>
       </c>
       <c r="BB17" s="1" t="str">
-        <f>ROUND(M17,0)&amp;"("&amp;ROUND((M17-AA17)/M17*100,0)&amp;")"</f>
+        <f t="shared" si="12"/>
         <v>99(52)</v>
       </c>
       <c r="BC17" s="1" t="str">
-        <f>ROUND(G17,0)&amp;"("&amp;ROUND((G17-U17)/G17*100,0)&amp;")"</f>
+        <f t="shared" si="0"/>
         <v>94(37)</v>
       </c>
       <c r="BD17" s="1" t="str">
-        <f>ROUND(I17,0)&amp;"("&amp;ROUND((I17-W17)/I17*100,0)&amp;")"</f>
+        <f t="shared" si="1"/>
         <v>100(49)</v>
       </c>
       <c r="BE17" s="1" t="str">
-        <f>ROUND(K17,0)&amp;"("&amp;ROUND((K17-Y17)/K17*100,0)&amp;")"</f>
+        <f t="shared" si="2"/>
         <v>90(-11)</v>
       </c>
       <c r="BF17" s="1" t="str">
-        <f>ROUND(O17,0)&amp;"("&amp;ROUND((O17-AC17)/O17*100,0)&amp;")"</f>
+        <f t="shared" si="3"/>
         <v>98(20)</v>
       </c>
       <c r="BG17" s="1" t="str">
-        <f>ROUND(C17,0)&amp;"("&amp;ROUND((C17-AE17)/C17*100,0)&amp;")"</f>
+        <f t="shared" si="4"/>
         <v>81(2)</v>
       </c>
       <c r="BH17" s="1" t="str">
-        <f>ROUND(E17,0)&amp;"("&amp;ROUND((E17-AG17)/E17*100,1)&amp;")"</f>
+        <f t="shared" si="5"/>
         <v>69(-30.2)</v>
       </c>
       <c r="BI17" s="1" t="str">
-        <f>ROUND(AS17,0)&amp;"("&amp;ROUND((AS17-AU17)/AS17*100,0)&amp;")"</f>
+        <f t="shared" si="6"/>
         <v>16(-45)</v>
       </c>
       <c r="BJ17" s="1" t="str">
-        <f>ROUND(M17,0)&amp;"("&amp;ROUND((M17-AO17)/M17*100,0)&amp;")"</f>
+        <f t="shared" si="7"/>
         <v>99(-1)</v>
       </c>
       <c r="BK17" s="1" t="str">
-        <f>ROUND(G17,0)&amp;"("&amp;ROUND((G17-AI17)/G17*100,0)&amp;")"</f>
+        <f t="shared" si="8"/>
         <v>94(92)</v>
       </c>
       <c r="BL17" s="1" t="str">
-        <f>ROUND(I17,0)&amp;"("&amp;ROUND((I17-AK17)/I17*100,0)&amp;")"</f>
+        <f t="shared" si="9"/>
         <v>100(92)</v>
       </c>
       <c r="BM17" s="1" t="str">
-        <f>ROUND(K17,0)&amp;"("&amp;ROUND((K17-AM17)/K17*100,0)&amp;")"</f>
+        <f t="shared" si="10"/>
         <v>90(90)</v>
       </c>
       <c r="BN17" s="1" t="str">
-        <f>ROUND(O17,0)&amp;"("&amp;ROUND((O17-AQ17)/O17*100,0)&amp;")"</f>
+        <f t="shared" si="11"/>
         <v>98(91)</v>
       </c>
     </row>
-    <row r="18" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>17</v>
       </c>
@@ -4922,59 +4922,59 @@
         <v>19.950418160095602</v>
       </c>
       <c r="BB18" s="1" t="str">
-        <f>ROUND(M18,0)&amp;"("&amp;ROUND((M18-AA18)/M18*100,0)&amp;")"</f>
+        <f t="shared" si="12"/>
         <v>94(64)</v>
       </c>
       <c r="BC18" s="1" t="str">
-        <f>ROUND(G18,0)&amp;"("&amp;ROUND((G18-U18)/G18*100,0)&amp;")"</f>
+        <f t="shared" si="0"/>
         <v>79(53)</v>
       </c>
       <c r="BD18" s="1" t="str">
-        <f>ROUND(I18,0)&amp;"("&amp;ROUND((I18-W18)/I18*100,0)&amp;")"</f>
+        <f t="shared" si="1"/>
         <v>100(63)</v>
       </c>
       <c r="BE18" s="1" t="str">
-        <f>ROUND(K18,0)&amp;"("&amp;ROUND((K18-Y18)/K18*100,0)&amp;")"</f>
+        <f t="shared" si="2"/>
         <v>77(-29)</v>
       </c>
       <c r="BF18" s="1" t="str">
-        <f>ROUND(O18,0)&amp;"("&amp;ROUND((O18-AC18)/O18*100,0)&amp;")"</f>
+        <f t="shared" si="3"/>
         <v>98(32)</v>
       </c>
       <c r="BG18" s="1" t="str">
-        <f>ROUND(C18,0)&amp;"("&amp;ROUND((C18-AE18)/C18*100,0)&amp;")"</f>
+        <f t="shared" si="4"/>
         <v>54(-61)</v>
       </c>
       <c r="BH18" s="1" t="str">
-        <f>ROUND(E18,0)&amp;"("&amp;ROUND((E18-AG18)/E18*100,1)&amp;")"</f>
+        <f t="shared" si="5"/>
         <v>45(-74.8)</v>
       </c>
       <c r="BI18" s="1" t="str">
-        <f>ROUND(AS18,0)&amp;"("&amp;ROUND((AS18-AU18)/AS18*100,0)&amp;")"</f>
+        <f t="shared" si="6"/>
         <v>12(-229)</v>
       </c>
       <c r="BJ18" s="1" t="str">
-        <f>ROUND(M18,0)&amp;"("&amp;ROUND((M18-AO18)/M18*100,0)&amp;")"</f>
+        <f t="shared" si="7"/>
         <v>94(-6)</v>
       </c>
       <c r="BK18" s="1" t="str">
-        <f>ROUND(G18,0)&amp;"("&amp;ROUND((G18-AI18)/G18*100,0)&amp;")"</f>
+        <f t="shared" si="8"/>
         <v>79(95)</v>
       </c>
       <c r="BL18" s="1" t="str">
-        <f>ROUND(I18,0)&amp;"("&amp;ROUND((I18-AK18)/I18*100,0)&amp;")"</f>
+        <f t="shared" si="9"/>
         <v>100(96)</v>
       </c>
       <c r="BM18" s="1" t="str">
-        <f>ROUND(K18,0)&amp;"("&amp;ROUND((K18-AM18)/K18*100,0)&amp;")"</f>
+        <f t="shared" si="10"/>
         <v>77(92)</v>
       </c>
       <c r="BN18" s="1" t="str">
-        <f>ROUND(O18,0)&amp;"("&amp;ROUND((O18-AQ18)/O18*100,0)&amp;")"</f>
+        <f t="shared" si="11"/>
         <v>98(93)</v>
       </c>
     </row>
-    <row r="19" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>18</v>
       </c>
@@ -5135,59 +5135,59 @@
         <v>54.895048271566502</v>
       </c>
       <c r="BB19" s="1" t="str">
-        <f>ROUND(M19,0)&amp;"("&amp;ROUND((M19-AA19)/M19*100,0)&amp;")"</f>
+        <f t="shared" si="12"/>
         <v>99(25)</v>
       </c>
       <c r="BC19" s="1" t="str">
-        <f>ROUND(G19,0)&amp;"("&amp;ROUND((G19-U19)/G19*100,0)&amp;")"</f>
+        <f t="shared" si="0"/>
         <v>90(27)</v>
       </c>
       <c r="BD19" s="1" t="str">
-        <f>ROUND(I19,0)&amp;"("&amp;ROUND((I19-W19)/I19*100,0)&amp;")"</f>
+        <f t="shared" si="1"/>
         <v>100(27)</v>
       </c>
       <c r="BE19" s="1" t="str">
-        <f>ROUND(K19,0)&amp;"("&amp;ROUND((K19-Y19)/K19*100,0)&amp;")"</f>
+        <f t="shared" si="2"/>
         <v>93(-8)</v>
       </c>
       <c r="BF19" s="1" t="str">
-        <f>ROUND(O19,0)&amp;"("&amp;ROUND((O19-AC19)/O19*100,0)&amp;")"</f>
+        <f t="shared" si="3"/>
         <v>97(6)</v>
       </c>
       <c r="BG19" s="1" t="str">
-        <f>ROUND(C19,0)&amp;"("&amp;ROUND((C19-AE19)/C19*100,0)&amp;")"</f>
+        <f t="shared" si="4"/>
         <v>70(-27)</v>
       </c>
       <c r="BH19" s="1" t="str">
-        <f>ROUND(E19,0)&amp;"("&amp;ROUND((E19-AG19)/E19*100,1)&amp;")"</f>
+        <f t="shared" si="5"/>
         <v>70(-37.3)</v>
       </c>
       <c r="BI19" s="1" t="str">
-        <f>ROUND(AS19,0)&amp;"("&amp;ROUND((AS19-AU19)/AS19*100,0)&amp;")"</f>
+        <f t="shared" si="6"/>
         <v>53(-13)</v>
       </c>
       <c r="BJ19" s="1" t="str">
-        <f>ROUND(M19,0)&amp;"("&amp;ROUND((M19-AO19)/M19*100,0)&amp;")"</f>
+        <f t="shared" si="7"/>
         <v>99(-1)</v>
       </c>
       <c r="BK19" s="1" t="str">
-        <f>ROUND(G19,0)&amp;"("&amp;ROUND((G19-AI19)/G19*100,0)&amp;")"</f>
+        <f t="shared" si="8"/>
         <v>90(71)</v>
       </c>
       <c r="BL19" s="1" t="str">
-        <f>ROUND(I19,0)&amp;"("&amp;ROUND((I19-AK19)/I19*100,0)&amp;")"</f>
+        <f t="shared" si="9"/>
         <v>100(74)</v>
       </c>
       <c r="BM19" s="1" t="str">
-        <f>ROUND(K19,0)&amp;"("&amp;ROUND((K19-AM19)/K19*100,0)&amp;")"</f>
+        <f t="shared" si="10"/>
         <v>93(63)</v>
       </c>
       <c r="BN19" s="1" t="str">
-        <f>ROUND(O19,0)&amp;"("&amp;ROUND((O19-AQ19)/O19*100,0)&amp;")"</f>
+        <f t="shared" si="11"/>
         <v>97(64)</v>
       </c>
     </row>
-    <row r="20" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>19</v>
       </c>
@@ -5348,59 +5348,59 @@
         <v>49.036442465432401</v>
       </c>
       <c r="BB20" s="1" t="str">
-        <f>ROUND(M20,0)&amp;"("&amp;ROUND((M20-AA20)/M20*100,0)&amp;")"</f>
+        <f t="shared" si="12"/>
         <v>99(24)</v>
       </c>
       <c r="BC20" s="1" t="str">
-        <f>ROUND(G20,0)&amp;"("&amp;ROUND((G20-U20)/G20*100,0)&amp;")"</f>
+        <f t="shared" si="0"/>
         <v>89(36)</v>
       </c>
       <c r="BD20" s="1" t="str">
-        <f>ROUND(I20,0)&amp;"("&amp;ROUND((I20-W20)/I20*100,0)&amp;")"</f>
+        <f t="shared" si="1"/>
         <v>100(30)</v>
       </c>
       <c r="BE20" s="1" t="str">
-        <f>ROUND(K20,0)&amp;"("&amp;ROUND((K20-Y20)/K20*100,0)&amp;")"</f>
+        <f t="shared" si="2"/>
         <v>91(-10)</v>
       </c>
       <c r="BF20" s="1" t="str">
-        <f>ROUND(O20,0)&amp;"("&amp;ROUND((O20-AC20)/O20*100,0)&amp;")"</f>
+        <f t="shared" si="3"/>
         <v>98(5)</v>
       </c>
       <c r="BG20" s="1" t="str">
-        <f>ROUND(C20,0)&amp;"("&amp;ROUND((C20-AE20)/C20*100,0)&amp;")"</f>
+        <f t="shared" si="4"/>
         <v>77(-24)</v>
       </c>
       <c r="BH20" s="1" t="str">
-        <f>ROUND(E20,0)&amp;"("&amp;ROUND((E20-AG20)/E20*100,1)&amp;")"</f>
+        <f t="shared" si="5"/>
         <v>62(-54.3)</v>
       </c>
       <c r="BI20" s="1" t="str">
-        <f>ROUND(AS20,0)&amp;"("&amp;ROUND((AS20-AU20)/AS20*100,0)&amp;")"</f>
+        <f t="shared" si="6"/>
         <v>51(-54)</v>
       </c>
       <c r="BJ20" s="1" t="str">
-        <f>ROUND(M20,0)&amp;"("&amp;ROUND((M20-AO20)/M20*100,0)&amp;")"</f>
+        <f t="shared" si="7"/>
         <v>99(-1)</v>
       </c>
       <c r="BK20" s="1" t="str">
-        <f>ROUND(G20,0)&amp;"("&amp;ROUND((G20-AI20)/G20*100,0)&amp;")"</f>
+        <f t="shared" si="8"/>
         <v>89(79)</v>
       </c>
       <c r="BL20" s="1" t="str">
-        <f>ROUND(I20,0)&amp;"("&amp;ROUND((I20-AK20)/I20*100,0)&amp;")"</f>
+        <f t="shared" si="9"/>
         <v>100(80)</v>
       </c>
       <c r="BM20" s="1" t="str">
-        <f>ROUND(K20,0)&amp;"("&amp;ROUND((K20-AM20)/K20*100,0)&amp;")"</f>
+        <f t="shared" si="10"/>
         <v>91(73)</v>
       </c>
       <c r="BN20" s="1" t="str">
-        <f>ROUND(O20,0)&amp;"("&amp;ROUND((O20-AQ20)/O20*100,0)&amp;")"</f>
+        <f t="shared" si="11"/>
         <v>98(73)</v>
       </c>
     </row>
-    <row r="21" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>20</v>
       </c>
@@ -5561,59 +5561,59 @@
         <v>31.641260555218299</v>
       </c>
       <c r="BB21" s="1" t="str">
-        <f>ROUND(M21,0)&amp;"("&amp;ROUND((M21-AA21)/M21*100,0)&amp;")"</f>
+        <f t="shared" si="12"/>
         <v>96(48)</v>
       </c>
       <c r="BC21" s="1" t="str">
-        <f>ROUND(G21,0)&amp;"("&amp;ROUND((G21-U21)/G21*100,0)&amp;")"</f>
+        <f t="shared" si="0"/>
         <v>56(14)</v>
       </c>
       <c r="BD21" s="1" t="str">
-        <f>ROUND(I21,0)&amp;"("&amp;ROUND((I21-W21)/I21*100,0)&amp;")"</f>
+        <f t="shared" si="1"/>
         <v>100(70)</v>
       </c>
       <c r="BE21" s="1" t="str">
-        <f>ROUND(K21,0)&amp;"("&amp;ROUND((K21-Y21)/K21*100,0)&amp;")"</f>
+        <f t="shared" si="2"/>
         <v>81(-23)</v>
       </c>
       <c r="BF21" s="1" t="str">
-        <f>ROUND(O21,0)&amp;"("&amp;ROUND((O21-AC21)/O21*100,0)&amp;")"</f>
+        <f t="shared" si="3"/>
         <v>98(20)</v>
       </c>
       <c r="BG21" s="1" t="str">
-        <f>ROUND(C21,0)&amp;"("&amp;ROUND((C21-AE21)/C21*100,0)&amp;")"</f>
+        <f t="shared" si="4"/>
         <v>59(-52)</v>
       </c>
       <c r="BH21" s="1" t="str">
-        <f>ROUND(E21,0)&amp;"("&amp;ROUND((E21-AG21)/E21*100,1)&amp;")"</f>
+        <f t="shared" si="5"/>
         <v>54(-40.8)</v>
       </c>
       <c r="BI21" s="1" t="str">
-        <f>ROUND(AS21,0)&amp;"("&amp;ROUND((AS21-AU21)/AS21*100,0)&amp;")"</f>
+        <f t="shared" si="6"/>
         <v>39(-8)</v>
       </c>
       <c r="BJ21" s="1" t="str">
-        <f>ROUND(M21,0)&amp;"("&amp;ROUND((M21-AO21)/M21*100,0)&amp;")"</f>
+        <f t="shared" si="7"/>
         <v>96(-5)</v>
       </c>
       <c r="BK21" s="1" t="str">
-        <f>ROUND(G21,0)&amp;"("&amp;ROUND((G21-AI21)/G21*100,0)&amp;")"</f>
+        <f t="shared" si="8"/>
         <v>56(87)</v>
       </c>
       <c r="BL21" s="1" t="str">
-        <f>ROUND(I21,0)&amp;"("&amp;ROUND((I21-AK21)/I21*100,0)&amp;")"</f>
+        <f t="shared" si="9"/>
         <v>100(91)</v>
       </c>
       <c r="BM21" s="1" t="str">
-        <f>ROUND(K21,0)&amp;"("&amp;ROUND((K21-AM21)/K21*100,0)&amp;")"</f>
+        <f t="shared" si="10"/>
         <v>81(88)</v>
       </c>
       <c r="BN21" s="1" t="str">
-        <f>ROUND(O21,0)&amp;"("&amp;ROUND((O21-AQ21)/O21*100,0)&amp;")"</f>
+        <f t="shared" si="11"/>
         <v>98(85)</v>
       </c>
     </row>
-    <row r="22" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>21</v>
       </c>
@@ -5774,59 +5774,59 @@
         <v>35.121074120602998</v>
       </c>
       <c r="BB22" s="1" t="str">
-        <f>ROUND(M22,0)&amp;"("&amp;ROUND((M22-AA22)/M22*100,0)&amp;")"</f>
+        <f t="shared" si="12"/>
         <v>94(38)</v>
       </c>
       <c r="BC22" s="1" t="str">
-        <f>ROUND(G22,0)&amp;"("&amp;ROUND((G22-U22)/G22*100,0)&amp;")"</f>
+        <f t="shared" si="0"/>
         <v>41(-61)</v>
       </c>
       <c r="BD22" s="1" t="str">
-        <f>ROUND(I22,0)&amp;"("&amp;ROUND((I22-W22)/I22*100,0)&amp;")"</f>
+        <f t="shared" si="1"/>
         <v>100(76)</v>
       </c>
       <c r="BE22" s="1" t="str">
-        <f>ROUND(K22,0)&amp;"("&amp;ROUND((K22-Y22)/K22*100,0)&amp;")"</f>
+        <f t="shared" si="2"/>
         <v>81(-24)</v>
       </c>
       <c r="BF22" s="1" t="str">
-        <f>ROUND(O22,0)&amp;"("&amp;ROUND((O22-AC22)/O22*100,0)&amp;")"</f>
+        <f t="shared" si="3"/>
         <v>99(19)</v>
       </c>
       <c r="BG22" s="1" t="str">
-        <f>ROUND(C22,0)&amp;"("&amp;ROUND((C22-AE22)/C22*100,0)&amp;")"</f>
+        <f t="shared" si="4"/>
         <v>60(-60)</v>
       </c>
       <c r="BH22" s="1" t="str">
-        <f>ROUND(E22,0)&amp;"("&amp;ROUND((E22-AG22)/E22*100,1)&amp;")"</f>
+        <f t="shared" si="5"/>
         <v>69(-5.7)</v>
       </c>
       <c r="BI22" s="1" t="str">
-        <f>ROUND(AS22,0)&amp;"("&amp;ROUND((AS22-AU22)/AS22*100,0)&amp;")"</f>
+        <f t="shared" si="6"/>
         <v>48(-27)</v>
       </c>
       <c r="BJ22" s="1" t="str">
-        <f>ROUND(M22,0)&amp;"("&amp;ROUND((M22-AO22)/M22*100,0)&amp;")"</f>
+        <f t="shared" si="7"/>
         <v>94(-7)</v>
       </c>
       <c r="BK22" s="1" t="str">
-        <f>ROUND(G22,0)&amp;"("&amp;ROUND((G22-AI22)/G22*100,0)&amp;")"</f>
+        <f t="shared" si="8"/>
         <v>41(70)</v>
       </c>
       <c r="BL22" s="1" t="str">
-        <f>ROUND(I22,0)&amp;"("&amp;ROUND((I22-AK22)/I22*100,0)&amp;")"</f>
+        <f t="shared" si="9"/>
         <v>100(79)</v>
       </c>
       <c r="BM22" s="1" t="str">
-        <f>ROUND(K22,0)&amp;"("&amp;ROUND((K22-AM22)/K22*100,0)&amp;")"</f>
+        <f t="shared" si="10"/>
         <v>81(88)</v>
       </c>
       <c r="BN22" s="1" t="str">
-        <f>ROUND(O22,0)&amp;"("&amp;ROUND((O22-AQ22)/O22*100,0)&amp;")"</f>
+        <f t="shared" si="11"/>
         <v>99(78)</v>
       </c>
     </row>
-    <row r="23" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>22</v>
       </c>
@@ -5987,59 +5987,59 @@
         <v>33.631075434352297</v>
       </c>
       <c r="BB23" s="1" t="str">
-        <f>ROUND(M23,0)&amp;"("&amp;ROUND((M23-AA23)/M23*100,0)&amp;")"</f>
+        <f t="shared" si="12"/>
         <v>97(41)</v>
       </c>
       <c r="BC23" s="1" t="str">
-        <f>ROUND(G23,0)&amp;"("&amp;ROUND((G23-U23)/G23*100,0)&amp;")"</f>
+        <f t="shared" si="0"/>
         <v>70(-17)</v>
       </c>
       <c r="BD23" s="1" t="str">
-        <f>ROUND(I23,0)&amp;"("&amp;ROUND((I23-W23)/I23*100,0)&amp;")"</f>
+        <f t="shared" si="1"/>
         <v>100(59)</v>
       </c>
       <c r="BE23" s="1" t="str">
-        <f>ROUND(K23,0)&amp;"("&amp;ROUND((K23-Y23)/K23*100,0)&amp;")"</f>
+        <f t="shared" si="2"/>
         <v>82(-22)</v>
       </c>
       <c r="BF23" s="1" t="str">
-        <f>ROUND(O23,0)&amp;"("&amp;ROUND((O23-AC23)/O23*100,0)&amp;")"</f>
+        <f t="shared" si="3"/>
         <v>98(13)</v>
       </c>
       <c r="BG23" s="1" t="str">
-        <f>ROUND(C23,0)&amp;"("&amp;ROUND((C23-AE23)/C23*100,0)&amp;")"</f>
+        <f t="shared" si="4"/>
         <v>59(-56)</v>
       </c>
       <c r="BH23" s="1" t="str">
-        <f>ROUND(E23,0)&amp;"("&amp;ROUND((E23-AG23)/E23*100,1)&amp;")"</f>
+        <f t="shared" si="5"/>
         <v>84(-0.6)</v>
       </c>
       <c r="BI23" s="1" t="str">
-        <f>ROUND(AS23,0)&amp;"("&amp;ROUND((AS23-AU23)/AS23*100,0)&amp;")"</f>
+        <f t="shared" si="6"/>
         <v>34(-99)</v>
       </c>
       <c r="BJ23" s="1" t="str">
-        <f>ROUND(M23,0)&amp;"("&amp;ROUND((M23-AO23)/M23*100,0)&amp;")"</f>
+        <f t="shared" si="7"/>
         <v>97(-3)</v>
       </c>
       <c r="BK23" s="1" t="str">
-        <f>ROUND(G23,0)&amp;"("&amp;ROUND((G23-AI23)/G23*100,0)&amp;")"</f>
+        <f t="shared" si="8"/>
         <v>70(86)</v>
       </c>
       <c r="BL23" s="1" t="str">
-        <f>ROUND(I23,0)&amp;"("&amp;ROUND((I23-AK23)/I23*100,0)&amp;")"</f>
+        <f t="shared" si="9"/>
         <v>100(69)</v>
       </c>
       <c r="BM23" s="1" t="str">
-        <f>ROUND(K23,0)&amp;"("&amp;ROUND((K23-AM23)/K23*100,0)&amp;")"</f>
+        <f t="shared" si="10"/>
         <v>82(85)</v>
       </c>
       <c r="BN23" s="1" t="str">
-        <f>ROUND(O23,0)&amp;"("&amp;ROUND((O23-AQ23)/O23*100,0)&amp;")"</f>
+        <f t="shared" si="11"/>
         <v>98(82)</v>
       </c>
     </row>
-    <row r="24" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>23</v>
       </c>
@@ -6200,59 +6200,59 @@
         <v>24.586803460068399</v>
       </c>
       <c r="BB24" s="1" t="str">
-        <f>ROUND(M24,0)&amp;"("&amp;ROUND((M24-AA24)/M24*100,0)&amp;")"</f>
+        <f t="shared" si="12"/>
         <v>97(49)</v>
       </c>
       <c r="BC24" s="1" t="str">
-        <f>ROUND(G24,0)&amp;"("&amp;ROUND((G24-U24)/G24*100,0)&amp;")"</f>
+        <f t="shared" si="0"/>
         <v>68(-21)</v>
       </c>
       <c r="BD24" s="1" t="str">
-        <f>ROUND(I24,0)&amp;"("&amp;ROUND((I24-W24)/I24*100,0)&amp;")"</f>
+        <f t="shared" si="1"/>
         <v>100(67)</v>
       </c>
       <c r="BE24" s="1" t="str">
-        <f>ROUND(K24,0)&amp;"("&amp;ROUND((K24-Y24)/K24*100,0)&amp;")"</f>
+        <f t="shared" si="2"/>
         <v>89(-13)</v>
       </c>
       <c r="BF24" s="1" t="str">
-        <f>ROUND(O24,0)&amp;"("&amp;ROUND((O24-AC24)/O24*100,0)&amp;")"</f>
+        <f t="shared" si="3"/>
         <v>98(25)</v>
       </c>
       <c r="BG24" s="1" t="str">
-        <f>ROUND(C24,0)&amp;"("&amp;ROUND((C24-AE24)/C24*100,0)&amp;")"</f>
+        <f t="shared" si="4"/>
         <v>50(-65)</v>
       </c>
       <c r="BH24" s="1" t="str">
-        <f>ROUND(E24,0)&amp;"("&amp;ROUND((E24-AG24)/E24*100,1)&amp;")"</f>
+        <f t="shared" si="5"/>
         <v>86(11.6)</v>
       </c>
       <c r="BI24" s="1" t="str">
-        <f>ROUND(AS24,0)&amp;"("&amp;ROUND((AS24-AU24)/AS24*100,0)&amp;")"</f>
+        <f t="shared" si="6"/>
         <v>22(-42)</v>
       </c>
       <c r="BJ24" s="1" t="str">
-        <f>ROUND(M24,0)&amp;"("&amp;ROUND((M24-AO24)/M24*100,0)&amp;")"</f>
+        <f t="shared" si="7"/>
         <v>97(-3)</v>
       </c>
       <c r="BK24" s="1" t="str">
-        <f>ROUND(G24,0)&amp;"("&amp;ROUND((G24-AI24)/G24*100,0)&amp;")"</f>
+        <f t="shared" si="8"/>
         <v>68(88)</v>
       </c>
       <c r="BL24" s="1" t="str">
-        <f>ROUND(I24,0)&amp;"("&amp;ROUND((I24-AK24)/I24*100,0)&amp;")"</f>
+        <f t="shared" si="9"/>
         <v>100(82)</v>
       </c>
       <c r="BM24" s="1" t="str">
-        <f>ROUND(K24,0)&amp;"("&amp;ROUND((K24-AM24)/K24*100,0)&amp;")"</f>
+        <f t="shared" si="10"/>
         <v>89(87)</v>
       </c>
       <c r="BN24" s="1" t="str">
-        <f>ROUND(O24,0)&amp;"("&amp;ROUND((O24-AQ24)/O24*100,0)&amp;")"</f>
+        <f t="shared" si="11"/>
         <v>98(83)</v>
       </c>
     </row>
-    <row r="25" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>24</v>
       </c>
@@ -6413,59 +6413,59 @@
         <v>28.6344306301215</v>
       </c>
       <c r="BB25" s="1" t="str">
-        <f>ROUND(M25,0)&amp;"("&amp;ROUND((M25-AA25)/M25*100,0)&amp;")"</f>
+        <f t="shared" si="12"/>
         <v>92(31)</v>
       </c>
       <c r="BC25" s="1" t="str">
-        <f>ROUND(G25,0)&amp;"("&amp;ROUND((G25-U25)/G25*100,0)&amp;")"</f>
+        <f t="shared" si="0"/>
         <v>7(-619)</v>
       </c>
       <c r="BD25" s="1" t="str">
-        <f>ROUND(I25,0)&amp;"("&amp;ROUND((I25-W25)/I25*100,0)&amp;")"</f>
+        <f t="shared" si="1"/>
         <v>100(95)</v>
       </c>
       <c r="BE25" s="1" t="str">
-        <f>ROUND(K25,0)&amp;"("&amp;ROUND((K25-Y25)/K25*100,0)&amp;")"</f>
+        <f t="shared" si="2"/>
         <v>87(-16)</v>
       </c>
       <c r="BF25" s="1" t="str">
-        <f>ROUND(O25,0)&amp;"("&amp;ROUND((O25-AC25)/O25*100,0)&amp;")"</f>
+        <f t="shared" si="3"/>
         <v>98(23)</v>
       </c>
       <c r="BG25" s="1" t="str">
-        <f>ROUND(C25,0)&amp;"("&amp;ROUND((C25-AE25)/C25*100,0)&amp;")"</f>
+        <f t="shared" si="4"/>
         <v>31(-211)</v>
       </c>
       <c r="BH25" s="1" t="str">
-        <f>ROUND(E25,0)&amp;"("&amp;ROUND((E25-AG25)/E25*100,1)&amp;")"</f>
+        <f t="shared" si="5"/>
         <v>56(6)</v>
       </c>
       <c r="BI25" s="1" t="str">
-        <f>ROUND(AS25,0)&amp;"("&amp;ROUND((AS25-AU25)/AS25*100,0)&amp;")"</f>
+        <f t="shared" si="6"/>
         <v>58(4)</v>
       </c>
       <c r="BJ25" s="1" t="str">
-        <f>ROUND(M25,0)&amp;"("&amp;ROUND((M25-AO25)/M25*100,0)&amp;")"</f>
+        <f t="shared" si="7"/>
         <v>92(-8)</v>
       </c>
       <c r="BK25" s="1" t="str">
-        <f>ROUND(G25,0)&amp;"("&amp;ROUND((G25-AI25)/G25*100,0)&amp;")"</f>
+        <f t="shared" si="8"/>
         <v>7(-33)</v>
       </c>
       <c r="BL25" s="1" t="str">
-        <f>ROUND(I25,0)&amp;"("&amp;ROUND((I25-AK25)/I25*100,0)&amp;")"</f>
+        <f t="shared" si="9"/>
         <v>100(80)</v>
       </c>
       <c r="BM25" s="1" t="str">
-        <f>ROUND(K25,0)&amp;"("&amp;ROUND((K25-AM25)/K25*100,0)&amp;")"</f>
+        <f t="shared" si="10"/>
         <v>87(96)</v>
       </c>
       <c r="BN25" s="1" t="str">
-        <f>ROUND(O25,0)&amp;"("&amp;ROUND((O25-AQ25)/O25*100,0)&amp;")"</f>
+        <f t="shared" si="11"/>
         <v>98(63)</v>
       </c>
     </row>
-    <row r="26" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>25</v>
       </c>
@@ -6626,59 +6626,59 @@
         <v>41.7235988986588</v>
       </c>
       <c r="BB26" s="1" t="str">
-        <f>ROUND(M26,0)&amp;"("&amp;ROUND((M26-AA26)/M26*100,0)&amp;")"</f>
+        <f t="shared" si="12"/>
         <v>94(10)</v>
       </c>
       <c r="BC26" s="1" t="str">
-        <f>ROUND(G26,0)&amp;"("&amp;ROUND((G26-U26)/G26*100,0)&amp;")"</f>
+        <f t="shared" si="0"/>
         <v>16(-157)</v>
       </c>
       <c r="BD26" s="1" t="str">
-        <f>ROUND(I26,0)&amp;"("&amp;ROUND((I26-W26)/I26*100,0)&amp;")"</f>
+        <f t="shared" si="1"/>
         <v>100(89)</v>
       </c>
       <c r="BE26" s="1" t="str">
-        <f>ROUND(K26,0)&amp;"("&amp;ROUND((K26-Y26)/K26*100,0)&amp;")"</f>
+        <f t="shared" si="2"/>
         <v>94(-6)</v>
       </c>
       <c r="BF26" s="1" t="str">
-        <f>ROUND(O26,0)&amp;"("&amp;ROUND((O26-AC26)/O26*100,0)&amp;")"</f>
+        <f t="shared" si="3"/>
         <v>98(12)</v>
       </c>
       <c r="BG26" s="1" t="str">
-        <f>ROUND(C26,0)&amp;"("&amp;ROUND((C26-AE26)/C26*100,0)&amp;")"</f>
+        <f t="shared" si="4"/>
         <v>38(-153)</v>
       </c>
       <c r="BH26" s="1" t="str">
-        <f>ROUND(E26,0)&amp;"("&amp;ROUND((E26-AG26)/E26*100,1)&amp;")"</f>
+        <f t="shared" si="5"/>
         <v>43(-81.2)</v>
       </c>
       <c r="BI26" s="1" t="str">
-        <f>ROUND(AS26,0)&amp;"("&amp;ROUND((AS26-AU26)/AS26*100,0)&amp;")"</f>
+        <f t="shared" si="6"/>
         <v>74(1)</v>
       </c>
       <c r="BJ26" s="1" t="str">
-        <f>ROUND(M26,0)&amp;"("&amp;ROUND((M26-AO26)/M26*100,0)&amp;")"</f>
+        <f t="shared" si="7"/>
         <v>94(-6)</v>
       </c>
       <c r="BK26" s="1" t="str">
-        <f>ROUND(G26,0)&amp;"("&amp;ROUND((G26-AI26)/G26*100,0)&amp;")"</f>
+        <f t="shared" si="8"/>
         <v>16(-24)</v>
       </c>
       <c r="BL26" s="1" t="str">
-        <f>ROUND(I26,0)&amp;"("&amp;ROUND((I26-AK26)/I26*100,0)&amp;")"</f>
+        <f t="shared" si="9"/>
         <v>100(80)</v>
       </c>
       <c r="BM26" s="1" t="str">
-        <f>ROUND(K26,0)&amp;"("&amp;ROUND((K26-AM26)/K26*100,0)&amp;")"</f>
+        <f t="shared" si="10"/>
         <v>94(91)</v>
       </c>
       <c r="BN26" s="1" t="str">
-        <f>ROUND(O26,0)&amp;"("&amp;ROUND((O26-AQ26)/O26*100,0)&amp;")"</f>
+        <f t="shared" si="11"/>
         <v>98(36)</v>
       </c>
     </row>
-    <row r="27" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>26</v>
       </c>
@@ -6839,59 +6839,59 @@
         <v>52.132440476190503</v>
       </c>
       <c r="BB27" s="1" t="str">
-        <f>ROUND(M27,0)&amp;"("&amp;ROUND((M27-AA27)/M27*100,0)&amp;")"</f>
+        <f t="shared" si="12"/>
         <v>89(12)</v>
       </c>
       <c r="BC27" s="1" t="str">
-        <f>ROUND(G27,0)&amp;"("&amp;ROUND((G27-U27)/G27*100,0)&amp;")"</f>
+        <f t="shared" si="0"/>
         <v>21(-111)</v>
       </c>
       <c r="BD27" s="1" t="str">
-        <f>ROUND(I27,0)&amp;"("&amp;ROUND((I27-W27)/I27*100,0)&amp;")"</f>
+        <f t="shared" si="1"/>
         <v>100(84)</v>
       </c>
       <c r="BE27" s="1" t="str">
-        <f>ROUND(K27,0)&amp;"("&amp;ROUND((K27-Y27)/K27*100,0)&amp;")"</f>
+        <f t="shared" si="2"/>
         <v>80(-24)</v>
       </c>
       <c r="BF27" s="1" t="str">
-        <f>ROUND(O27,0)&amp;"("&amp;ROUND((O27-AC27)/O27*100,0)&amp;")"</f>
+        <f t="shared" si="3"/>
         <v>99(11)</v>
       </c>
       <c r="BG27" s="1" t="str">
-        <f>ROUND(C27,0)&amp;"("&amp;ROUND((C27-AE27)/C27*100,0)&amp;")"</f>
+        <f t="shared" si="4"/>
         <v>34(-188)</v>
       </c>
       <c r="BH27" s="1" t="str">
-        <f>ROUND(E27,0)&amp;"("&amp;ROUND((E27-AG27)/E27*100,1)&amp;")"</f>
+        <f t="shared" si="5"/>
         <v>44(-106.6)</v>
       </c>
       <c r="BI27" s="1" t="str">
-        <f>ROUND(AS27,0)&amp;"("&amp;ROUND((AS27-AU27)/AS27*100,0)&amp;")"</f>
+        <f t="shared" si="6"/>
         <v>82(-13)</v>
       </c>
       <c r="BJ27" s="1" t="str">
-        <f>ROUND(M27,0)&amp;"("&amp;ROUND((M27-AO27)/M27*100,0)&amp;")"</f>
+        <f t="shared" si="7"/>
         <v>89(-13)</v>
       </c>
       <c r="BK27" s="1" t="str">
-        <f>ROUND(G27,0)&amp;"("&amp;ROUND((G27-AI27)/G27*100,0)&amp;")"</f>
+        <f t="shared" si="8"/>
         <v>21(-13)</v>
       </c>
       <c r="BL27" s="1" t="str">
-        <f>ROUND(I27,0)&amp;"("&amp;ROUND((I27-AK27)/I27*100,0)&amp;")"</f>
+        <f t="shared" si="9"/>
         <v>100(65)</v>
       </c>
       <c r="BM27" s="1" t="str">
-        <f>ROUND(K27,0)&amp;"("&amp;ROUND((K27-AM27)/K27*100,0)&amp;")"</f>
+        <f t="shared" si="10"/>
         <v>80(86)</v>
       </c>
       <c r="BN27" s="1" t="str">
-        <f>ROUND(O27,0)&amp;"("&amp;ROUND((O27-AQ27)/O27*100,0)&amp;")"</f>
+        <f t="shared" si="11"/>
         <v>99(30)</v>
       </c>
     </row>
-    <row r="28" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>27</v>
       </c>
@@ -7052,59 +7052,59 @@
         <v>45.9033352425431</v>
       </c>
       <c r="BB28" s="1" t="str">
-        <f>ROUND(M28,0)&amp;"("&amp;ROUND((M28-AA28)/M28*100,0)&amp;")"</f>
+        <f t="shared" si="12"/>
         <v>96(19)</v>
       </c>
       <c r="BC28" s="1" t="str">
-        <f>ROUND(G28,0)&amp;"("&amp;ROUND((G28-U28)/G28*100,0)&amp;")"</f>
+        <f t="shared" si="0"/>
         <v>27(-107)</v>
       </c>
       <c r="BD28" s="1" t="str">
-        <f>ROUND(I28,0)&amp;"("&amp;ROUND((I28-W28)/I28*100,0)&amp;")"</f>
+        <f t="shared" si="1"/>
         <v>100(81)</v>
       </c>
       <c r="BE28" s="1" t="str">
-        <f>ROUND(K28,0)&amp;"("&amp;ROUND((K28-Y28)/K28*100,0)&amp;")"</f>
+        <f t="shared" si="2"/>
         <v>91(-10)</v>
       </c>
       <c r="BF28" s="1" t="str">
-        <f>ROUND(O28,0)&amp;"("&amp;ROUND((O28-AC28)/O28*100,0)&amp;")"</f>
+        <f t="shared" si="3"/>
         <v>98(10)</v>
       </c>
       <c r="BG28" s="1" t="str">
-        <f>ROUND(C28,0)&amp;"("&amp;ROUND((C28-AE28)/C28*100,0)&amp;")"</f>
+        <f t="shared" si="4"/>
         <v>48(-99)</v>
       </c>
       <c r="BH28" s="1" t="str">
-        <f>ROUND(E28,0)&amp;"("&amp;ROUND((E28-AG28)/E28*100,1)&amp;")"</f>
+        <f t="shared" si="5"/>
         <v>59(-38.4)</v>
       </c>
       <c r="BI28" s="1" t="str">
-        <f>ROUND(AS28,0)&amp;"("&amp;ROUND((AS28-AU28)/AS28*100,0)&amp;")"</f>
+        <f t="shared" si="6"/>
         <v>75(11)</v>
       </c>
       <c r="BJ28" s="1" t="str">
-        <f>ROUND(M28,0)&amp;"("&amp;ROUND((M28-AO28)/M28*100,0)&amp;")"</f>
+        <f t="shared" si="7"/>
         <v>96(-4)</v>
       </c>
       <c r="BK28" s="1" t="str">
-        <f>ROUND(G28,0)&amp;"("&amp;ROUND((G28-AI28)/G28*100,0)&amp;")"</f>
+        <f t="shared" si="8"/>
         <v>27(26)</v>
       </c>
       <c r="BL28" s="1" t="str">
-        <f>ROUND(I28,0)&amp;"("&amp;ROUND((I28-AK28)/I28*100,0)&amp;")"</f>
+        <f t="shared" si="9"/>
         <v>100(75)</v>
       </c>
       <c r="BM28" s="1" t="str">
-        <f>ROUND(K28,0)&amp;"("&amp;ROUND((K28-AM28)/K28*100,0)&amp;")"</f>
+        <f t="shared" si="10"/>
         <v>91(85)</v>
       </c>
       <c r="BN28" s="1" t="str">
-        <f>ROUND(O28,0)&amp;"("&amp;ROUND((O28-AQ28)/O28*100,0)&amp;")"</f>
+        <f t="shared" si="11"/>
         <v>98(47)</v>
       </c>
     </row>
-    <row r="29" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>28</v>
       </c>
@@ -7265,59 +7265,59 @@
         <v>36.129824216831999</v>
       </c>
       <c r="BB29" s="1" t="str">
-        <f>ROUND(M29,0)&amp;"("&amp;ROUND((M29-AA29)/M29*100,0)&amp;")"</f>
+        <f t="shared" si="12"/>
         <v>96(38)</v>
       </c>
       <c r="BC29" s="1" t="str">
-        <f>ROUND(G29,0)&amp;"("&amp;ROUND((G29-U29)/G29*100,0)&amp;")"</f>
+        <f t="shared" si="0"/>
         <v>64(53)</v>
       </c>
       <c r="BD29" s="1" t="str">
-        <f>ROUND(I29,0)&amp;"("&amp;ROUND((I29-W29)/I29*100,0)&amp;")"</f>
+        <f t="shared" si="1"/>
         <v>100(64)</v>
       </c>
       <c r="BE29" s="1" t="str">
-        <f>ROUND(K29,0)&amp;"("&amp;ROUND((K29-Y29)/K29*100,0)&amp;")"</f>
+        <f t="shared" si="2"/>
         <v>84(-19)</v>
       </c>
       <c r="BF29" s="1" t="str">
-        <f>ROUND(O29,0)&amp;"("&amp;ROUND((O29-AC29)/O29*100,0)&amp;")"</f>
+        <f t="shared" si="3"/>
         <v>97(16)</v>
       </c>
       <c r="BG29" s="1" t="str">
-        <f>ROUND(C29,0)&amp;"("&amp;ROUND((C29-AE29)/C29*100,0)&amp;")"</f>
+        <f t="shared" si="4"/>
         <v>53(-69)</v>
       </c>
       <c r="BH29" s="1" t="str">
-        <f>ROUND(E29,0)&amp;"("&amp;ROUND((E29-AG29)/E29*100,1)&amp;")"</f>
+        <f t="shared" si="5"/>
         <v>35(-143.2)</v>
       </c>
       <c r="BI29" s="1" t="str">
-        <f>ROUND(AS29,0)&amp;"("&amp;ROUND((AS29-AU29)/AS29*100,0)&amp;")"</f>
+        <f t="shared" si="6"/>
         <v>34(-68)</v>
       </c>
       <c r="BJ29" s="1" t="str">
-        <f>ROUND(M29,0)&amp;"("&amp;ROUND((M29-AO29)/M29*100,0)&amp;")"</f>
+        <f t="shared" si="7"/>
         <v>96(-4)</v>
       </c>
       <c r="BK29" s="1" t="str">
-        <f>ROUND(G29,0)&amp;"("&amp;ROUND((G29-AI29)/G29*100,0)&amp;")"</f>
+        <f t="shared" si="8"/>
         <v>64(86)</v>
       </c>
       <c r="BL29" s="1" t="str">
-        <f>ROUND(I29,0)&amp;"("&amp;ROUND((I29-AK29)/I29*100,0)&amp;")"</f>
+        <f t="shared" si="9"/>
         <v>100(92)</v>
       </c>
       <c r="BM29" s="1" t="str">
-        <f>ROUND(K29,0)&amp;"("&amp;ROUND((K29-AM29)/K29*100,0)&amp;")"</f>
+        <f t="shared" si="10"/>
         <v>84(87)</v>
       </c>
       <c r="BN29" s="1" t="str">
-        <f>ROUND(O29,0)&amp;"("&amp;ROUND((O29-AQ29)/O29*100,0)&amp;")"</f>
+        <f t="shared" si="11"/>
         <v>97(82)</v>
       </c>
     </row>
-    <row r="30" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>29</v>
       </c>
@@ -7478,59 +7478,59 @@
         <v>31.8188899707887</v>
       </c>
       <c r="BB30" s="1" t="str">
-        <f>ROUND(M30,0)&amp;"("&amp;ROUND((M30-AA30)/M30*100,0)&amp;")"</f>
+        <f t="shared" si="12"/>
         <v>93(27)</v>
       </c>
       <c r="BC30" s="1" t="str">
-        <f>ROUND(G30,0)&amp;"("&amp;ROUND((G30-U30)/G30*100,0)&amp;")"</f>
+        <f t="shared" si="0"/>
         <v>42(0)</v>
       </c>
       <c r="BD30" s="1" t="str">
-        <f>ROUND(I30,0)&amp;"("&amp;ROUND((I30-W30)/I30*100,0)&amp;")"</f>
+        <f t="shared" si="1"/>
         <v>100(74)</v>
       </c>
       <c r="BE30" s="1" t="str">
-        <f>ROUND(K30,0)&amp;"("&amp;ROUND((K30-Y30)/K30*100,0)&amp;")"</f>
+        <f t="shared" si="2"/>
         <v>86(-17)</v>
       </c>
       <c r="BF30" s="1" t="str">
-        <f>ROUND(O30,0)&amp;"("&amp;ROUND((O30-AC30)/O30*100,0)&amp;")"</f>
+        <f t="shared" si="3"/>
         <v>96(16)</v>
       </c>
       <c r="BG30" s="1" t="str">
-        <f>ROUND(C30,0)&amp;"("&amp;ROUND((C30-AE30)/C30*100,0)&amp;")"</f>
+        <f t="shared" si="4"/>
         <v>41(-119)</v>
       </c>
       <c r="BH30" s="1" t="str">
-        <f>ROUND(E30,0)&amp;"("&amp;ROUND((E30-AG30)/E30*100,1)&amp;")"</f>
+        <f t="shared" si="5"/>
         <v>47(-65.8)</v>
       </c>
       <c r="BI30" s="1" t="str">
-        <f>ROUND(AS30,0)&amp;"("&amp;ROUND((AS30-AU30)/AS30*100,0)&amp;")"</f>
+        <f t="shared" si="6"/>
         <v>45(-44)</v>
       </c>
       <c r="BJ30" s="1" t="str">
-        <f>ROUND(M30,0)&amp;"("&amp;ROUND((M30-AO30)/M30*100,0)&amp;")"</f>
+        <f t="shared" si="7"/>
         <v>93(-8)</v>
       </c>
       <c r="BK30" s="1" t="str">
-        <f>ROUND(G30,0)&amp;"("&amp;ROUND((G30-AI30)/G30*100,0)&amp;")"</f>
+        <f t="shared" si="8"/>
         <v>42(69)</v>
       </c>
       <c r="BL30" s="1" t="str">
-        <f>ROUND(I30,0)&amp;"("&amp;ROUND((I30-AK30)/I30*100,0)&amp;")"</f>
+        <f t="shared" si="9"/>
         <v>100(84)</v>
       </c>
       <c r="BM30" s="1" t="str">
-        <f>ROUND(K30,0)&amp;"("&amp;ROUND((K30-AM30)/K30*100,0)&amp;")"</f>
+        <f t="shared" si="10"/>
         <v>86(84)</v>
       </c>
       <c r="BN30" s="1" t="str">
-        <f>ROUND(O30,0)&amp;"("&amp;ROUND((O30-AQ30)/O30*100,0)&amp;")"</f>
+        <f t="shared" si="11"/>
         <v>96(68)</v>
       </c>
     </row>
-    <row r="31" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>30</v>
       </c>
@@ -7691,59 +7691,59 @@
         <v>27.518409425625901</v>
       </c>
       <c r="BB31" s="1" t="str">
-        <f>ROUND(M31,0)&amp;"("&amp;ROUND((M31-AA31)/M31*100,0)&amp;")"</f>
+        <f t="shared" si="12"/>
         <v>89(30)</v>
       </c>
       <c r="BC31" s="1" t="str">
-        <f>ROUND(G31,0)&amp;"("&amp;ROUND((G31-U31)/G31*100,0)&amp;")"</f>
+        <f t="shared" si="0"/>
         <v>44(47)</v>
       </c>
       <c r="BD31" s="1" t="str">
-        <f>ROUND(I31,0)&amp;"("&amp;ROUND((I31-W31)/I31*100,0)&amp;")"</f>
+        <f t="shared" si="1"/>
         <v>100(76)</v>
       </c>
       <c r="BE31" s="1" t="str">
-        <f>ROUND(K31,0)&amp;"("&amp;ROUND((K31-Y31)/K31*100,0)&amp;")"</f>
+        <f t="shared" si="2"/>
         <v>85(-18)</v>
       </c>
       <c r="BF31" s="1" t="str">
-        <f>ROUND(O31,0)&amp;"("&amp;ROUND((O31-AC31)/O31*100,0)&amp;")"</f>
+        <f t="shared" si="3"/>
         <v>90(20)</v>
       </c>
       <c r="BG31" s="1" t="str">
-        <f>ROUND(C31,0)&amp;"("&amp;ROUND((C31-AE31)/C31*100,0)&amp;")"</f>
+        <f t="shared" si="4"/>
         <v>25(-229)</v>
       </c>
       <c r="BH31" s="1" t="str">
-        <f>ROUND(E31,0)&amp;"("&amp;ROUND((E31-AG31)/E31*100,1)&amp;")"</f>
+        <f t="shared" si="5"/>
         <v>25(-170.3)</v>
       </c>
       <c r="BI31" s="1" t="str">
-        <f>ROUND(AS31,0)&amp;"("&amp;ROUND((AS31-AU31)/AS31*100,0)&amp;")"</f>
+        <f t="shared" si="6"/>
         <v>40(-41)</v>
       </c>
       <c r="BJ31" s="1" t="str">
-        <f>ROUND(M31,0)&amp;"("&amp;ROUND((M31-AO31)/M31*100,0)&amp;")"</f>
+        <f t="shared" si="7"/>
         <v>89(-12)</v>
       </c>
       <c r="BK31" s="1" t="str">
-        <f>ROUND(G31,0)&amp;"("&amp;ROUND((G31-AI31)/G31*100,0)&amp;")"</f>
+        <f t="shared" si="8"/>
         <v>44(83)</v>
       </c>
       <c r="BL31" s="1" t="str">
-        <f>ROUND(I31,0)&amp;"("&amp;ROUND((I31-AK31)/I31*100,0)&amp;")"</f>
+        <f t="shared" si="9"/>
         <v>100(87)</v>
       </c>
       <c r="BM31" s="1" t="str">
-        <f>ROUND(K31,0)&amp;"("&amp;ROUND((K31-AM31)/K31*100,0)&amp;")"</f>
+        <f t="shared" si="10"/>
         <v>85(88)</v>
       </c>
       <c r="BN31" s="1" t="str">
-        <f>ROUND(O31,0)&amp;"("&amp;ROUND((O31-AQ31)/O31*100,0)&amp;")"</f>
+        <f t="shared" si="11"/>
         <v>90(68)</v>
       </c>
     </row>
-    <row r="32" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>31</v>
       </c>
@@ -7904,59 +7904,59 @@
         <v>22.752883031301501</v>
       </c>
       <c r="BB32" s="1" t="str">
-        <f>ROUND(M32,0)&amp;"("&amp;ROUND((M32-AA32)/M32*100,0)&amp;")"</f>
+        <f t="shared" si="12"/>
         <v>98(21)</v>
       </c>
       <c r="BC32" s="1" t="str">
-        <f>ROUND(G32,0)&amp;"("&amp;ROUND((G32-U32)/G32*100,0)&amp;")"</f>
+        <f t="shared" si="0"/>
         <v>97(58)</v>
       </c>
       <c r="BD32" s="1" t="str">
-        <f>ROUND(I32,0)&amp;"("&amp;ROUND((I32-W32)/I32*100,0)&amp;")"</f>
+        <f t="shared" si="1"/>
         <v>100(26)</v>
       </c>
       <c r="BE32" s="1" t="str">
-        <f>ROUND(K32,0)&amp;"("&amp;ROUND((K32-Y32)/K32*100,0)&amp;")"</f>
+        <f t="shared" si="2"/>
         <v>97(-3)</v>
       </c>
       <c r="BF32" s="1" t="str">
-        <f>ROUND(O32,0)&amp;"("&amp;ROUND((O32-AC32)/O32*100,0)&amp;")"</f>
+        <f t="shared" si="3"/>
         <v>99(11)</v>
       </c>
       <c r="BG32" s="1" t="str">
-        <f>ROUND(C32,0)&amp;"("&amp;ROUND((C32-AE32)/C32*100,0)&amp;")"</f>
+        <f t="shared" si="4"/>
         <v>79(-22)</v>
       </c>
       <c r="BH32" s="1" t="str">
-        <f>ROUND(E32,0)&amp;"("&amp;ROUND((E32-AG32)/E32*100,1)&amp;")"</f>
+        <f t="shared" si="5"/>
         <v>46(-89.5)</v>
       </c>
       <c r="BI32" s="1" t="str">
-        <f>ROUND(AS32,0)&amp;"("&amp;ROUND((AS32-AU32)/AS32*100,0)&amp;")"</f>
+        <f t="shared" si="6"/>
         <v>29(-136)</v>
       </c>
       <c r="BJ32" s="1" t="str">
-        <f>ROUND(M32,0)&amp;"("&amp;ROUND((M32-AO32)/M32*100,0)&amp;")"</f>
+        <f t="shared" si="7"/>
         <v>98(-2)</v>
       </c>
       <c r="BK32" s="1" t="str">
-        <f>ROUND(G32,0)&amp;"("&amp;ROUND((G32-AI32)/G32*100,0)&amp;")"</f>
+        <f t="shared" si="8"/>
         <v>97(87)</v>
       </c>
       <c r="BL32" s="1" t="str">
-        <f>ROUND(I32,0)&amp;"("&amp;ROUND((I32-AK32)/I32*100,0)&amp;")"</f>
+        <f t="shared" si="9"/>
         <v>100(83)</v>
       </c>
       <c r="BM32" s="1" t="str">
-        <f>ROUND(K32,0)&amp;"("&amp;ROUND((K32-AM32)/K32*100,0)&amp;")"</f>
+        <f t="shared" si="10"/>
         <v>97(81)</v>
       </c>
       <c r="BN32" s="1" t="str">
-        <f>ROUND(O32,0)&amp;"("&amp;ROUND((O32-AQ32)/O32*100,0)&amp;")"</f>
+        <f t="shared" si="11"/>
         <v>99(82)</v>
       </c>
     </row>
-    <row r="33" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>32</v>
       </c>
@@ -8117,59 +8117,59 @@
         <v>45.906657608695703</v>
       </c>
       <c r="BB33" s="1" t="str">
-        <f>ROUND(M33,0)&amp;"("&amp;ROUND((M33-AA33)/M33*100,0)&amp;")"</f>
+        <f t="shared" si="12"/>
         <v>97(11)</v>
       </c>
       <c r="BC33" s="1" t="str">
-        <f>ROUND(G33,0)&amp;"("&amp;ROUND((G33-U33)/G33*100,0)&amp;")"</f>
+        <f t="shared" si="0"/>
         <v>84(68)</v>
       </c>
       <c r="BD33" s="1" t="str">
-        <f>ROUND(I33,0)&amp;"("&amp;ROUND((I33-W33)/I33*100,0)&amp;")"</f>
+        <f t="shared" si="1"/>
         <v>100(28)</v>
       </c>
       <c r="BE33" s="1" t="str">
-        <f>ROUND(K33,0)&amp;"("&amp;ROUND((K33-Y33)/K33*100,0)&amp;")"</f>
+        <f t="shared" si="2"/>
         <v>95(-5)</v>
       </c>
       <c r="BF33" s="1" t="str">
-        <f>ROUND(O33,0)&amp;"("&amp;ROUND((O33-AC33)/O33*100,0)&amp;")"</f>
+        <f t="shared" si="3"/>
         <v>97(8)</v>
       </c>
       <c r="BG33" s="1" t="str">
-        <f>ROUND(C33,0)&amp;"("&amp;ROUND((C33-AE33)/C33*100,0)&amp;")"</f>
+        <f t="shared" si="4"/>
         <v>65(-45)</v>
       </c>
       <c r="BH33" s="1" t="str">
-        <f>ROUND(E33,0)&amp;"("&amp;ROUND((E33-AG33)/E33*100,1)&amp;")"</f>
+        <f t="shared" si="5"/>
         <v>29(-214)</v>
       </c>
       <c r="BI33" s="1" t="str">
-        <f>ROUND(AS33,0)&amp;"("&amp;ROUND((AS33-AU33)/AS33*100,0)&amp;")"</f>
+        <f t="shared" si="6"/>
         <v>66(-17)</v>
       </c>
       <c r="BJ33" s="1" t="str">
-        <f>ROUND(M33,0)&amp;"("&amp;ROUND((M33-AO33)/M33*100,0)&amp;")"</f>
+        <f t="shared" si="7"/>
         <v>97(-3)</v>
       </c>
       <c r="BK33" s="1" t="str">
-        <f>ROUND(G33,0)&amp;"("&amp;ROUND((G33-AI33)/G33*100,0)&amp;")"</f>
+        <f t="shared" si="8"/>
         <v>84(76)</v>
       </c>
       <c r="BL33" s="1" t="str">
-        <f>ROUND(I33,0)&amp;"("&amp;ROUND((I33-AK33)/I33*100,0)&amp;")"</f>
+        <f t="shared" si="9"/>
         <v>100(88)</v>
       </c>
       <c r="BM33" s="1" t="str">
-        <f>ROUND(K33,0)&amp;"("&amp;ROUND((K33-AM33)/K33*100,0)&amp;")"</f>
+        <f t="shared" si="10"/>
         <v>95(61)</v>
       </c>
       <c r="BN33" s="1" t="str">
-        <f>ROUND(O33,0)&amp;"("&amp;ROUND((O33-AQ33)/O33*100,0)&amp;")"</f>
+        <f t="shared" si="11"/>
         <v>97(55)</v>
       </c>
     </row>
-    <row r="34" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>33</v>
       </c>
@@ -8330,59 +8330,59 @@
         <v>40.370571827057198</v>
       </c>
       <c r="BB34" s="1" t="str">
-        <f>ROUND(M34,0)&amp;"("&amp;ROUND((M34-AA34)/M34*100,0)&amp;")"</f>
+        <f t="shared" ref="BB34:BB55" si="13">ROUND(M34,0)&amp;"("&amp;ROUND((M34-AA34)/M34*100,0)&amp;")"</f>
         <v>94(15)</v>
       </c>
       <c r="BC34" s="1" t="str">
-        <f>ROUND(G34,0)&amp;"("&amp;ROUND((G34-U34)/G34*100,0)&amp;")"</f>
+        <f t="shared" ref="BC34:BC55" si="14">ROUND(G34,0)&amp;"("&amp;ROUND((G34-U34)/G34*100,0)&amp;")"</f>
         <v>73(57)</v>
       </c>
       <c r="BD34" s="1" t="str">
-        <f>ROUND(I34,0)&amp;"("&amp;ROUND((I34-W34)/I34*100,0)&amp;")"</f>
+        <f t="shared" ref="BD34:BD55" si="15">ROUND(I34,0)&amp;"("&amp;ROUND((I34-W34)/I34*100,0)&amp;")"</f>
         <v>100(46)</v>
       </c>
       <c r="BE34" s="1" t="str">
-        <f>ROUND(K34,0)&amp;"("&amp;ROUND((K34-Y34)/K34*100,0)&amp;")"</f>
+        <f t="shared" ref="BE34:BE55" si="16">ROUND(K34,0)&amp;"("&amp;ROUND((K34-Y34)/K34*100,0)&amp;")"</f>
         <v>93(-8)</v>
       </c>
       <c r="BF34" s="1" t="str">
-        <f>ROUND(O34,0)&amp;"("&amp;ROUND((O34-AC34)/O34*100,0)&amp;")"</f>
+        <f t="shared" ref="BF34:BF55" si="17">ROUND(O34,0)&amp;"("&amp;ROUND((O34-AC34)/O34*100,0)&amp;")"</f>
         <v>96(11)</v>
       </c>
       <c r="BG34" s="1" t="str">
-        <f>ROUND(C34,0)&amp;"("&amp;ROUND((C34-AE34)/C34*100,0)&amp;")"</f>
+        <f t="shared" ref="BG34:BG55" si="18">ROUND(C34,0)&amp;"("&amp;ROUND((C34-AE34)/C34*100,0)&amp;")"</f>
         <v>45(-100)</v>
       </c>
       <c r="BH34" s="1" t="str">
-        <f>ROUND(E34,0)&amp;"("&amp;ROUND((E34-AG34)/E34*100,1)&amp;")"</f>
+        <f t="shared" ref="BH34:BH55" si="19">ROUND(E34,0)&amp;"("&amp;ROUND((E34-AG34)/E34*100,1)&amp;")"</f>
         <v>35(-145.8)</v>
       </c>
       <c r="BI34" s="1" t="str">
-        <f>ROUND(AS34,0)&amp;"("&amp;ROUND((AS34-AU34)/AS34*100,0)&amp;")"</f>
+        <f t="shared" ref="BI34:BI55" si="20">ROUND(AS34,0)&amp;"("&amp;ROUND((AS34-AU34)/AS34*100,0)&amp;")"</f>
         <v>55(-18)</v>
       </c>
       <c r="BJ34" s="1" t="str">
-        <f>ROUND(M34,0)&amp;"("&amp;ROUND((M34-AO34)/M34*100,0)&amp;")"</f>
+        <f t="shared" ref="BJ34:BJ55" si="21">ROUND(M34,0)&amp;"("&amp;ROUND((M34-AO34)/M34*100,0)&amp;")"</f>
         <v>94(-6)</v>
       </c>
       <c r="BK34" s="1" t="str">
-        <f>ROUND(G34,0)&amp;"("&amp;ROUND((G34-AI34)/G34*100,0)&amp;")"</f>
+        <f t="shared" ref="BK34:BK55" si="22">ROUND(G34,0)&amp;"("&amp;ROUND((G34-AI34)/G34*100,0)&amp;")"</f>
         <v>73(85)</v>
       </c>
       <c r="BL34" s="1" t="str">
-        <f>ROUND(I34,0)&amp;"("&amp;ROUND((I34-AK34)/I34*100,0)&amp;")"</f>
+        <f t="shared" ref="BL34:BL55" si="23">ROUND(I34,0)&amp;"("&amp;ROUND((I34-AK34)/I34*100,0)&amp;")"</f>
         <v>100(88)</v>
       </c>
       <c r="BM34" s="1" t="str">
-        <f>ROUND(K34,0)&amp;"("&amp;ROUND((K34-AM34)/K34*100,0)&amp;")"</f>
+        <f t="shared" ref="BM34:BM55" si="24">ROUND(K34,0)&amp;"("&amp;ROUND((K34-AM34)/K34*100,0)&amp;")"</f>
         <v>93(77)</v>
       </c>
       <c r="BN34" s="1" t="str">
-        <f>ROUND(O34,0)&amp;"("&amp;ROUND((O34-AQ34)/O34*100,0)&amp;")"</f>
+        <f t="shared" ref="BN34:BN55" si="25">ROUND(O34,0)&amp;"("&amp;ROUND((O34-AQ34)/O34*100,0)&amp;")"</f>
         <v>96(65)</v>
       </c>
     </row>
-    <row r="35" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>34</v>
       </c>
@@ -8543,59 +8543,59 @@
         <v>71.779549718574103</v>
       </c>
       <c r="BB35" s="1" t="str">
-        <f>ROUND(M35,0)&amp;"("&amp;ROUND((M35-AA35)/M35*100,0)&amp;")"</f>
+        <f t="shared" si="13"/>
         <v>96(10)</v>
       </c>
       <c r="BC35" s="1" t="str">
-        <f>ROUND(G35,0)&amp;"("&amp;ROUND((G35-U35)/G35*100,0)&amp;")"</f>
+        <f t="shared" si="14"/>
         <v>72(83)</v>
       </c>
       <c r="BD35" s="1" t="str">
-        <f>ROUND(I35,0)&amp;"("&amp;ROUND((I35-W35)/I35*100,0)&amp;")"</f>
+        <f t="shared" si="15"/>
         <v>100(35)</v>
       </c>
       <c r="BE35" s="1" t="str">
-        <f>ROUND(K35,0)&amp;"("&amp;ROUND((K35-Y35)/K35*100,0)&amp;")"</f>
+        <f t="shared" si="16"/>
         <v>92(-9)</v>
       </c>
       <c r="BF35" s="1" t="str">
-        <f>ROUND(O35,0)&amp;"("&amp;ROUND((O35-AC35)/O35*100,0)&amp;")"</f>
+        <f t="shared" si="17"/>
         <v>95(0)</v>
       </c>
       <c r="BG35" s="1" t="str">
-        <f>ROUND(C35,0)&amp;"("&amp;ROUND((C35-AE35)/C35*100,0)&amp;")"</f>
+        <f t="shared" si="18"/>
         <v>50(-83)</v>
       </c>
       <c r="BH35" s="1" t="str">
-        <f>ROUND(E35,0)&amp;"("&amp;ROUND((E35-AG35)/E35*100,1)&amp;")"</f>
+        <f t="shared" si="19"/>
         <v>13(-632.8)</v>
       </c>
       <c r="BI35" s="1" t="str">
-        <f>ROUND(AS35,0)&amp;"("&amp;ROUND((AS35-AU35)/AS35*100,0)&amp;")"</f>
+        <f t="shared" si="20"/>
         <v>85(0)</v>
       </c>
       <c r="BJ35" s="1" t="str">
-        <f>ROUND(M35,0)&amp;"("&amp;ROUND((M35-AO35)/M35*100,0)&amp;")"</f>
+        <f t="shared" si="21"/>
         <v>96(-4)</v>
       </c>
       <c r="BK35" s="1" t="str">
-        <f>ROUND(G35,0)&amp;"("&amp;ROUND((G35-AI35)/G35*100,0)&amp;")"</f>
+        <f t="shared" si="22"/>
         <v>72(50)</v>
       </c>
       <c r="BL35" s="1" t="str">
-        <f>ROUND(I35,0)&amp;"("&amp;ROUND((I35-AK35)/I35*100,0)&amp;")"</f>
+        <f t="shared" si="23"/>
         <v>100(90)</v>
       </c>
       <c r="BM35" s="1" t="str">
-        <f>ROUND(K35,0)&amp;"("&amp;ROUND((K35-AM35)/K35*100,0)&amp;")"</f>
+        <f t="shared" si="24"/>
         <v>92(40)</v>
       </c>
       <c r="BN35" s="1" t="str">
-        <f>ROUND(O35,0)&amp;"("&amp;ROUND((O35-AQ35)/O35*100,0)&amp;")"</f>
+        <f t="shared" si="25"/>
         <v>95(23)</v>
       </c>
     </row>
-    <row r="36" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>35</v>
       </c>
@@ -8756,59 +8756,59 @@
         <v>48.2822580645161</v>
       </c>
       <c r="BB36" s="1" t="str">
-        <f>ROUND(M36,0)&amp;"("&amp;ROUND((M36-AA36)/M36*100,0)&amp;")"</f>
+        <f t="shared" si="13"/>
         <v>96(24)</v>
       </c>
       <c r="BC36" s="1" t="str">
-        <f>ROUND(G36,0)&amp;"("&amp;ROUND((G36-U36)/G36*100,0)&amp;")"</f>
+        <f t="shared" si="14"/>
         <v>71(67)</v>
       </c>
       <c r="BD36" s="1" t="str">
-        <f>ROUND(I36,0)&amp;"("&amp;ROUND((I36-W36)/I36*100,0)&amp;")"</f>
+        <f t="shared" si="15"/>
         <v>100(44)</v>
       </c>
       <c r="BE36" s="1" t="str">
-        <f>ROUND(K36,0)&amp;"("&amp;ROUND((K36-Y36)/K36*100,0)&amp;")"</f>
+        <f t="shared" si="16"/>
         <v>87(-15)</v>
       </c>
       <c r="BF36" s="1" t="str">
-        <f>ROUND(O36,0)&amp;"("&amp;ROUND((O36-AC36)/O36*100,0)&amp;")"</f>
+        <f t="shared" si="17"/>
         <v>99(12)</v>
       </c>
       <c r="BG36" s="1" t="str">
-        <f>ROUND(C36,0)&amp;"("&amp;ROUND((C36-AE36)/C36*100,0)&amp;")"</f>
+        <f t="shared" si="18"/>
         <v>62(-55)</v>
       </c>
       <c r="BH36" s="1" t="str">
-        <f>ROUND(E36,0)&amp;"("&amp;ROUND((E36-AG36)/E36*100,1)&amp;")"</f>
+        <f t="shared" si="19"/>
         <v>26(-237.3)</v>
       </c>
       <c r="BI36" s="1" t="str">
-        <f>ROUND(AS36,0)&amp;"("&amp;ROUND((AS36-AU36)/AS36*100,0)&amp;")"</f>
+        <f t="shared" si="20"/>
         <v>61(-20)</v>
       </c>
       <c r="BJ36" s="1" t="str">
-        <f>ROUND(M36,0)&amp;"("&amp;ROUND((M36-AO36)/M36*100,0)&amp;")"</f>
+        <f t="shared" si="21"/>
         <v>96(-4)</v>
       </c>
       <c r="BK36" s="1" t="str">
-        <f>ROUND(G36,0)&amp;"("&amp;ROUND((G36-AI36)/G36*100,0)&amp;")"</f>
+        <f t="shared" si="22"/>
         <v>71(67)</v>
       </c>
       <c r="BL36" s="1" t="str">
-        <f>ROUND(I36,0)&amp;"("&amp;ROUND((I36-AK36)/I36*100,0)&amp;")"</f>
+        <f t="shared" si="23"/>
         <v>100(90)</v>
       </c>
       <c r="BM36" s="1" t="str">
-        <f>ROUND(K36,0)&amp;"("&amp;ROUND((K36-AM36)/K36*100,0)&amp;")"</f>
+        <f t="shared" si="24"/>
         <v>87(63)</v>
       </c>
       <c r="BN36" s="1" t="str">
-        <f>ROUND(O36,0)&amp;"("&amp;ROUND((O36-AQ36)/O36*100,0)&amp;")"</f>
+        <f t="shared" si="25"/>
         <v>99(61)</v>
       </c>
     </row>
-    <row r="37" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>36</v>
       </c>
@@ -8969,59 +8969,59 @@
         <v>46.781713100177797</v>
       </c>
       <c r="BB37" s="1" t="str">
-        <f>ROUND(M37,0)&amp;"("&amp;ROUND((M37-AA37)/M37*100,0)&amp;")"</f>
+        <f t="shared" si="13"/>
         <v>96(32)</v>
       </c>
       <c r="BC37" s="1" t="str">
-        <f>ROUND(G37,0)&amp;"("&amp;ROUND((G37-U37)/G37*100,0)&amp;")"</f>
+        <f t="shared" si="14"/>
         <v>70(44)</v>
       </c>
       <c r="BD37" s="1" t="str">
-        <f>ROUND(I37,0)&amp;"("&amp;ROUND((I37-W37)/I37*100,0)&amp;")"</f>
+        <f t="shared" si="15"/>
         <v>100(53)</v>
       </c>
       <c r="BE37" s="1" t="str">
-        <f>ROUND(K37,0)&amp;"("&amp;ROUND((K37-Y37)/K37*100,0)&amp;")"</f>
+        <f t="shared" si="16"/>
         <v>86(-16)</v>
       </c>
       <c r="BF37" s="1" t="str">
-        <f>ROUND(O37,0)&amp;"("&amp;ROUND((O37-AC37)/O37*100,0)&amp;")"</f>
+        <f t="shared" si="17"/>
         <v>97(11)</v>
       </c>
       <c r="BG37" s="1" t="str">
-        <f>ROUND(C37,0)&amp;"("&amp;ROUND((C37-AE37)/C37*100,0)&amp;")"</f>
+        <f t="shared" si="18"/>
         <v>66(-38)</v>
       </c>
       <c r="BH37" s="1" t="str">
-        <f>ROUND(E37,0)&amp;"("&amp;ROUND((E37-AG37)/E37*100,1)&amp;")"</f>
+        <f t="shared" si="19"/>
         <v>44(-101)</v>
       </c>
       <c r="BI37" s="1" t="str">
-        <f>ROUND(AS37,0)&amp;"("&amp;ROUND((AS37-AU37)/AS37*100,0)&amp;")"</f>
+        <f t="shared" si="20"/>
         <v>50(-31)</v>
       </c>
       <c r="BJ37" s="1" t="str">
-        <f>ROUND(M37,0)&amp;"("&amp;ROUND((M37-AO37)/M37*100,0)&amp;")"</f>
+        <f t="shared" si="21"/>
         <v>96(-4)</v>
       </c>
       <c r="BK37" s="1" t="str">
-        <f>ROUND(G37,0)&amp;"("&amp;ROUND((G37-AI37)/G37*100,0)&amp;")"</f>
+        <f t="shared" si="22"/>
         <v>70(66)</v>
       </c>
       <c r="BL37" s="1" t="str">
-        <f>ROUND(I37,0)&amp;"("&amp;ROUND((I37-AK37)/I37*100,0)&amp;")"</f>
+        <f t="shared" si="23"/>
         <v>100(83)</v>
       </c>
       <c r="BM37" s="1" t="str">
-        <f>ROUND(K37,0)&amp;"("&amp;ROUND((K37-AM37)/K37*100,0)&amp;")"</f>
+        <f t="shared" si="24"/>
         <v>86(70)</v>
       </c>
       <c r="BN37" s="1" t="str">
-        <f>ROUND(O37,0)&amp;"("&amp;ROUND((O37-AQ37)/O37*100,0)&amp;")"</f>
+        <f t="shared" si="25"/>
         <v>97(64)</v>
       </c>
     </row>
-    <row r="38" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>37</v>
       </c>
@@ -9182,59 +9182,59 @@
         <v>26.1766342141864</v>
       </c>
       <c r="BB38" s="1" t="str">
-        <f>ROUND(M38,0)&amp;"("&amp;ROUND((M38-AA38)/M38*100,0)&amp;")"</f>
+        <f t="shared" si="13"/>
         <v>94(34)</v>
       </c>
       <c r="BC38" s="1" t="str">
-        <f>ROUND(G38,0)&amp;"("&amp;ROUND((G38-U38)/G38*100,0)&amp;")"</f>
+        <f t="shared" si="14"/>
         <v>25(83)</v>
       </c>
       <c r="BD38" s="1" t="str">
-        <f>ROUND(I38,0)&amp;"("&amp;ROUND((I38-W38)/I38*100,0)&amp;")"</f>
+        <f t="shared" si="15"/>
         <v>100(96)</v>
       </c>
       <c r="BE38" s="1" t="str">
-        <f>ROUND(K38,0)&amp;"("&amp;ROUND((K38-Y38)/K38*100,0)&amp;")"</f>
+        <f t="shared" si="16"/>
         <v>89(-12)</v>
       </c>
       <c r="BF38" s="1" t="str">
-        <f>ROUND(O38,0)&amp;"("&amp;ROUND((O38-AC38)/O38*100,0)&amp;")"</f>
+        <f t="shared" si="17"/>
         <v>93(21)</v>
       </c>
       <c r="BG38" s="1" t="str">
-        <f>ROUND(C38,0)&amp;"("&amp;ROUND((C38-AE38)/C38*100,0)&amp;")"</f>
+        <f t="shared" si="18"/>
         <v>53(-46)</v>
       </c>
       <c r="BH38" s="1" t="str">
-        <f>ROUND(E38,0)&amp;"("&amp;ROUND((E38-AG38)/E38*100,1)&amp;")"</f>
+        <f t="shared" si="19"/>
         <v>7(-891)</v>
       </c>
       <c r="BI38" s="1" t="str">
-        <f>ROUND(AS38,0)&amp;"("&amp;ROUND((AS38-AU38)/AS38*100,0)&amp;")"</f>
+        <f t="shared" si="20"/>
         <v>36(51)</v>
       </c>
       <c r="BJ38" s="1" t="str">
-        <f>ROUND(M38,0)&amp;"("&amp;ROUND((M38-AO38)/M38*100,0)&amp;")"</f>
+        <f t="shared" si="21"/>
         <v>94(-6)</v>
       </c>
       <c r="BK38" s="1" t="str">
-        <f>ROUND(G38,0)&amp;"("&amp;ROUND((G38-AI38)/G38*100,0)&amp;")"</f>
+        <f t="shared" si="22"/>
         <v>25(92)</v>
       </c>
       <c r="BL38" s="1" t="str">
-        <f>ROUND(I38,0)&amp;"("&amp;ROUND((I38-AK38)/I38*100,0)&amp;")"</f>
+        <f t="shared" si="23"/>
         <v>100(99)</v>
       </c>
       <c r="BM38" s="1" t="str">
-        <f>ROUND(K38,0)&amp;"("&amp;ROUND((K38-AM38)/K38*100,0)&amp;")"</f>
+        <f t="shared" si="24"/>
         <v>89(99)</v>
       </c>
       <c r="BN38" s="1" t="str">
-        <f>ROUND(O38,0)&amp;"("&amp;ROUND((O38-AQ38)/O38*100,0)&amp;")"</f>
+        <f t="shared" si="25"/>
         <v>93(94)</v>
       </c>
     </row>
-    <row r="39" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>38</v>
       </c>
@@ -9395,59 +9395,59 @@
         <v>32.414640222286103</v>
       </c>
       <c r="BB39" s="1" t="str">
-        <f>ROUND(M39,0)&amp;"("&amp;ROUND((M39-AA39)/M39*100,0)&amp;")"</f>
+        <f t="shared" si="13"/>
         <v>96(33)</v>
       </c>
       <c r="BC39" s="1" t="str">
-        <f>ROUND(G39,0)&amp;"("&amp;ROUND((G39-U39)/G39*100,0)&amp;")"</f>
+        <f t="shared" si="14"/>
         <v>35(-65)</v>
       </c>
       <c r="BD39" s="1" t="str">
-        <f>ROUND(I39,0)&amp;"("&amp;ROUND((I39-W39)/I39*100,0)&amp;")"</f>
+        <f t="shared" si="15"/>
         <v>100(78)</v>
       </c>
       <c r="BE39" s="1" t="str">
-        <f>ROUND(K39,0)&amp;"("&amp;ROUND((K39-Y39)/K39*100,0)&amp;")"</f>
+        <f t="shared" si="16"/>
         <v>87(-15)</v>
       </c>
       <c r="BF39" s="1" t="str">
-        <f>ROUND(O39,0)&amp;"("&amp;ROUND((O39-AC39)/O39*100,0)&amp;")"</f>
+        <f t="shared" si="17"/>
         <v>99(18)</v>
       </c>
       <c r="BG39" s="1" t="str">
-        <f>ROUND(C39,0)&amp;"("&amp;ROUND((C39-AE39)/C39*100,0)&amp;")"</f>
+        <f t="shared" si="18"/>
         <v>59(-62)</v>
       </c>
       <c r="BH39" s="1" t="str">
-        <f>ROUND(E39,0)&amp;"("&amp;ROUND((E39-AG39)/E39*100,1)&amp;")"</f>
+        <f t="shared" si="19"/>
         <v>63(-12.6)</v>
       </c>
       <c r="BI39" s="1" t="str">
-        <f>ROUND(AS39,0)&amp;"("&amp;ROUND((AS39-AU39)/AS39*100,0)&amp;")"</f>
+        <f t="shared" si="20"/>
         <v>50(-17)</v>
       </c>
       <c r="BJ39" s="1" t="str">
-        <f>ROUND(M39,0)&amp;"("&amp;ROUND((M39-AO39)/M39*100,0)&amp;")"</f>
+        <f t="shared" si="21"/>
         <v>96(-5)</v>
       </c>
       <c r="BK39" s="1" t="str">
-        <f>ROUND(G39,0)&amp;"("&amp;ROUND((G39-AI39)/G39*100,0)&amp;")"</f>
+        <f t="shared" si="22"/>
         <v>35(69)</v>
       </c>
       <c r="BL39" s="1" t="str">
-        <f>ROUND(I39,0)&amp;"("&amp;ROUND((I39-AK39)/I39*100,0)&amp;")"</f>
+        <f t="shared" si="23"/>
         <v>100(84)</v>
       </c>
       <c r="BM39" s="1" t="str">
-        <f>ROUND(K39,0)&amp;"("&amp;ROUND((K39-AM39)/K39*100,0)&amp;")"</f>
+        <f t="shared" si="24"/>
         <v>87(91)</v>
       </c>
       <c r="BN39" s="1" t="str">
-        <f>ROUND(O39,0)&amp;"("&amp;ROUND((O39-AQ39)/O39*100,0)&amp;")"</f>
+        <f t="shared" si="25"/>
         <v>99(76)</v>
       </c>
     </row>
-    <row r="40" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>39</v>
       </c>
@@ -9608,59 +9608,59 @@
         <v>31.702362543796099</v>
       </c>
       <c r="BB40" s="1" t="str">
-        <f>ROUND(M40,0)&amp;"("&amp;ROUND((M40-AA40)/M40*100,0)&amp;")"</f>
+        <f t="shared" si="13"/>
         <v>94(36)</v>
       </c>
       <c r="BC40" s="1" t="str">
-        <f>ROUND(G40,0)&amp;"("&amp;ROUND((G40-U40)/G40*100,0)&amp;")"</f>
+        <f t="shared" si="14"/>
         <v>35(-41)</v>
       </c>
       <c r="BD40" s="1" t="str">
-        <f>ROUND(I40,0)&amp;"("&amp;ROUND((I40-W40)/I40*100,0)&amp;")"</f>
+        <f t="shared" si="15"/>
         <v>100(79)</v>
       </c>
       <c r="BE40" s="1" t="str">
-        <f>ROUND(K40,0)&amp;"("&amp;ROUND((K40-Y40)/K40*100,0)&amp;")"</f>
+        <f t="shared" si="16"/>
         <v>85(-18)</v>
       </c>
       <c r="BF40" s="1" t="str">
-        <f>ROUND(O40,0)&amp;"("&amp;ROUND((O40-AC40)/O40*100,0)&amp;")"</f>
+        <f t="shared" si="17"/>
         <v>98(21)</v>
       </c>
       <c r="BG40" s="1" t="str">
-        <f>ROUND(C40,0)&amp;"("&amp;ROUND((C40-AE40)/C40*100,0)&amp;")"</f>
+        <f t="shared" si="18"/>
         <v>49(-89)</v>
       </c>
       <c r="BH40" s="1" t="str">
-        <f>ROUND(E40,0)&amp;"("&amp;ROUND((E40-AG40)/E40*100,1)&amp;")"</f>
+        <f t="shared" si="19"/>
         <v>54(-26.4)</v>
       </c>
       <c r="BI40" s="1" t="str">
-        <f>ROUND(AS40,0)&amp;"("&amp;ROUND((AS40-AU40)/AS40*100,0)&amp;")"</f>
+        <f t="shared" si="20"/>
         <v>48(-13)</v>
       </c>
       <c r="BJ40" s="1" t="str">
-        <f>ROUND(M40,0)&amp;"("&amp;ROUND((M40-AO40)/M40*100,0)&amp;")"</f>
+        <f t="shared" si="21"/>
         <v>94(-6)</v>
       </c>
       <c r="BK40" s="1" t="str">
-        <f>ROUND(G40,0)&amp;"("&amp;ROUND((G40-AI40)/G40*100,0)&amp;")"</f>
+        <f t="shared" si="22"/>
         <v>35(72)</v>
       </c>
       <c r="BL40" s="1" t="str">
-        <f>ROUND(I40,0)&amp;"("&amp;ROUND((I40-AK40)/I40*100,0)&amp;")"</f>
+        <f t="shared" si="23"/>
         <v>100(87)</v>
       </c>
       <c r="BM40" s="1" t="str">
-        <f>ROUND(K40,0)&amp;"("&amp;ROUND((K40-AM40)/K40*100,0)&amp;")"</f>
+        <f t="shared" si="24"/>
         <v>85(92)</v>
       </c>
       <c r="BN40" s="1" t="str">
-        <f>ROUND(O40,0)&amp;"("&amp;ROUND((O40-AQ40)/O40*100,0)&amp;")"</f>
+        <f t="shared" si="25"/>
         <v>98(75)</v>
       </c>
     </row>
-    <row r="41" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>40</v>
       </c>
@@ -9821,59 +9821,59 @@
         <v>34.023203807412202</v>
       </c>
       <c r="BB41" s="1" t="str">
-        <f>ROUND(M41,0)&amp;"("&amp;ROUND((M41-AA41)/M41*100,0)&amp;")"</f>
+        <f t="shared" si="13"/>
         <v>94(32)</v>
       </c>
       <c r="BC41" s="1" t="str">
-        <f>ROUND(G41,0)&amp;"("&amp;ROUND((G41-U41)/G41*100,0)&amp;")"</f>
+        <f t="shared" si="14"/>
         <v>37(-8)</v>
       </c>
       <c r="BD41" s="1" t="str">
-        <f>ROUND(I41,0)&amp;"("&amp;ROUND((I41-W41)/I41*100,0)&amp;")"</f>
+        <f t="shared" si="15"/>
         <v>100(77)</v>
       </c>
       <c r="BE41" s="1" t="str">
-        <f>ROUND(K41,0)&amp;"("&amp;ROUND((K41-Y41)/K41*100,0)&amp;")"</f>
+        <f t="shared" si="16"/>
         <v>85(-17)</v>
       </c>
       <c r="BF41" s="1" t="str">
-        <f>ROUND(O41,0)&amp;"("&amp;ROUND((O41-AC41)/O41*100,0)&amp;")"</f>
+        <f t="shared" si="17"/>
         <v>98(20)</v>
       </c>
       <c r="BG41" s="1" t="str">
-        <f>ROUND(C41,0)&amp;"("&amp;ROUND((C41-AE41)/C41*100,0)&amp;")"</f>
+        <f t="shared" si="18"/>
         <v>45(-106)</v>
       </c>
       <c r="BH41" s="1" t="str">
-        <f>ROUND(E41,0)&amp;"("&amp;ROUND((E41-AG41)/E41*100,1)&amp;")"</f>
+        <f t="shared" si="19"/>
         <v>45(-56.8)</v>
       </c>
       <c r="BI41" s="1" t="str">
-        <f>ROUND(AS41,0)&amp;"("&amp;ROUND((AS41-AU41)/AS41*100,0)&amp;")"</f>
+        <f t="shared" si="20"/>
         <v>50(-13)</v>
       </c>
       <c r="BJ41" s="1" t="str">
-        <f>ROUND(M41,0)&amp;"("&amp;ROUND((M41-AO41)/M41*100,0)&amp;")"</f>
+        <f t="shared" si="21"/>
         <v>94(-7)</v>
       </c>
       <c r="BK41" s="1" t="str">
-        <f>ROUND(G41,0)&amp;"("&amp;ROUND((G41-AI41)/G41*100,0)&amp;")"</f>
+        <f t="shared" si="22"/>
         <v>37(70)</v>
       </c>
       <c r="BL41" s="1" t="str">
-        <f>ROUND(I41,0)&amp;"("&amp;ROUND((I41-AK41)/I41*100,0)&amp;")"</f>
+        <f t="shared" si="23"/>
         <v>100(87)</v>
       </c>
       <c r="BM41" s="1" t="str">
-        <f>ROUND(K41,0)&amp;"("&amp;ROUND((K41-AM41)/K41*100,0)&amp;")"</f>
+        <f t="shared" si="24"/>
         <v>85(89)</v>
       </c>
       <c r="BN41" s="1" t="str">
-        <f>ROUND(O41,0)&amp;"("&amp;ROUND((O41-AQ41)/O41*100,0)&amp;")"</f>
+        <f t="shared" si="25"/>
         <v>98(70)</v>
       </c>
     </row>
-    <row r="42" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>41</v>
       </c>
@@ -10034,59 +10034,59 @@
         <v>37.761603176103598</v>
       </c>
       <c r="BB42" s="1" t="str">
-        <f>ROUND(M42,0)&amp;"("&amp;ROUND((M42-AA42)/M42*100,0)&amp;")"</f>
+        <f t="shared" si="13"/>
         <v>92(28)</v>
       </c>
       <c r="BC42" s="1" t="str">
-        <f>ROUND(G42,0)&amp;"("&amp;ROUND((G42-U42)/G42*100,0)&amp;")"</f>
+        <f t="shared" si="14"/>
         <v>38(13)</v>
       </c>
       <c r="BD42" s="1" t="str">
-        <f>ROUND(I42,0)&amp;"("&amp;ROUND((I42-W42)/I42*100,0)&amp;")"</f>
+        <f t="shared" si="15"/>
         <v>100(75)</v>
       </c>
       <c r="BE42" s="1" t="str">
-        <f>ROUND(K42,0)&amp;"("&amp;ROUND((K42-Y42)/K42*100,0)&amp;")"</f>
+        <f t="shared" si="16"/>
         <v>85(-17)</v>
       </c>
       <c r="BF42" s="1" t="str">
-        <f>ROUND(O42,0)&amp;"("&amp;ROUND((O42-AC42)/O42*100,0)&amp;")"</f>
+        <f t="shared" si="17"/>
         <v>97(19)</v>
       </c>
       <c r="BG42" s="1" t="str">
-        <f>ROUND(C42,0)&amp;"("&amp;ROUND((C42-AE42)/C42*100,0)&amp;")"</f>
+        <f t="shared" si="18"/>
         <v>39(-133)</v>
       </c>
       <c r="BH42" s="1" t="str">
-        <f>ROUND(E42,0)&amp;"("&amp;ROUND((E42-AG42)/E42*100,1)&amp;")"</f>
+        <f t="shared" si="19"/>
         <v>36(-101.8)</v>
       </c>
       <c r="BI42" s="1" t="str">
-        <f>ROUND(AS42,0)&amp;"("&amp;ROUND((AS42-AU42)/AS42*100,0)&amp;")"</f>
+        <f t="shared" si="20"/>
         <v>53(-16)</v>
       </c>
       <c r="BJ42" s="1" t="str">
-        <f>ROUND(M42,0)&amp;"("&amp;ROUND((M42-AO42)/M42*100,0)&amp;")"</f>
+        <f t="shared" si="21"/>
         <v>92(-8)</v>
       </c>
       <c r="BK42" s="1" t="str">
-        <f>ROUND(G42,0)&amp;"("&amp;ROUND((G42-AI42)/G42*100,0)&amp;")"</f>
+        <f t="shared" si="22"/>
         <v>38(64)</v>
       </c>
       <c r="BL42" s="1" t="str">
-        <f>ROUND(I42,0)&amp;"("&amp;ROUND((I42-AK42)/I42*100,0)&amp;")"</f>
+        <f t="shared" si="23"/>
         <v>100(87)</v>
       </c>
       <c r="BM42" s="1" t="str">
-        <f>ROUND(K42,0)&amp;"("&amp;ROUND((K42-AM42)/K42*100,0)&amp;")"</f>
+        <f t="shared" si="24"/>
         <v>85(86)</v>
       </c>
       <c r="BN42" s="1" t="str">
-        <f>ROUND(O42,0)&amp;"("&amp;ROUND((O42-AQ42)/O42*100,0)&amp;")"</f>
+        <f t="shared" si="25"/>
         <v>97(62)</v>
       </c>
     </row>
-    <row r="43" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>42</v>
       </c>
@@ -10247,59 +10247,59 @@
         <v>46.183595086891998</v>
       </c>
       <c r="BB43" s="1" t="str">
-        <f>ROUND(M43,0)&amp;"("&amp;ROUND((M43-AA43)/M43*100,0)&amp;")"</f>
+        <f t="shared" si="13"/>
         <v>88(16)</v>
       </c>
       <c r="BC43" s="1" t="str">
-        <f>ROUND(G43,0)&amp;"("&amp;ROUND((G43-U43)/G43*100,0)&amp;")"</f>
+        <f t="shared" si="14"/>
         <v>36(20)</v>
       </c>
       <c r="BD43" s="1" t="str">
-        <f>ROUND(I43,0)&amp;"("&amp;ROUND((I43-W43)/I43*100,0)&amp;")"</f>
+        <f t="shared" si="15"/>
         <v>100(72)</v>
       </c>
       <c r="BE43" s="1" t="str">
-        <f>ROUND(K43,0)&amp;"("&amp;ROUND((K43-Y43)/K43*100,0)&amp;")"</f>
+        <f t="shared" si="16"/>
         <v>85(-18)</v>
       </c>
       <c r="BF43" s="1" t="str">
-        <f>ROUND(O43,0)&amp;"("&amp;ROUND((O43-AC43)/O43*100,0)&amp;")"</f>
+        <f t="shared" si="17"/>
         <v>94(15)</v>
       </c>
       <c r="BG43" s="1" t="str">
-        <f>ROUND(C43,0)&amp;"("&amp;ROUND((C43-AE43)/C43*100,0)&amp;")"</f>
+        <f t="shared" si="18"/>
         <v>33(-169)</v>
       </c>
       <c r="BH43" s="1" t="str">
-        <f>ROUND(E43,0)&amp;"("&amp;ROUND((E43-AG43)/E43*100,1)&amp;")"</f>
+        <f t="shared" si="19"/>
         <v>30(-156.1)</v>
       </c>
       <c r="BI43" s="1" t="str">
-        <f>ROUND(AS43,0)&amp;"("&amp;ROUND((AS43-AU43)/AS43*100,0)&amp;")"</f>
+        <f t="shared" si="20"/>
         <v>66(-13)</v>
       </c>
       <c r="BJ43" s="1" t="str">
-        <f>ROUND(M43,0)&amp;"("&amp;ROUND((M43-AO43)/M43*100,0)&amp;")"</f>
+        <f t="shared" si="21"/>
         <v>88(-13)</v>
       </c>
       <c r="BK43" s="1" t="str">
-        <f>ROUND(G43,0)&amp;"("&amp;ROUND((G43-AI43)/G43*100,0)&amp;")"</f>
+        <f t="shared" si="22"/>
         <v>36(37)</v>
       </c>
       <c r="BL43" s="1" t="str">
-        <f>ROUND(I43,0)&amp;"("&amp;ROUND((I43-AK43)/I43*100,0)&amp;")"</f>
+        <f t="shared" si="23"/>
         <v>100(79)</v>
       </c>
       <c r="BM43" s="1" t="str">
-        <f>ROUND(K43,0)&amp;"("&amp;ROUND((K43-AM43)/K43*100,0)&amp;")"</f>
+        <f t="shared" si="24"/>
         <v>85(74)</v>
       </c>
       <c r="BN43" s="1" t="str">
-        <f>ROUND(O43,0)&amp;"("&amp;ROUND((O43-AQ43)/O43*100,0)&amp;")"</f>
+        <f t="shared" si="25"/>
         <v>94(38)</v>
       </c>
     </row>
-    <row r="44" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>43</v>
       </c>
@@ -10460,59 +10460,59 @@
         <v>29.945751211631698</v>
       </c>
       <c r="BB44" s="1" t="str">
-        <f>ROUND(M44,0)&amp;"("&amp;ROUND((M44-AA44)/M44*100,0)&amp;")"</f>
+        <f t="shared" si="13"/>
         <v>93(36)</v>
       </c>
       <c r="BC44" s="1" t="str">
-        <f>ROUND(G44,0)&amp;"("&amp;ROUND((G44-U44)/G44*100,0)&amp;")"</f>
+        <f t="shared" si="14"/>
         <v>35(-30)</v>
       </c>
       <c r="BD44" s="1" t="str">
-        <f>ROUND(I44,0)&amp;"("&amp;ROUND((I44-W44)/I44*100,0)&amp;")"</f>
+        <f t="shared" si="15"/>
         <v>100(79)</v>
       </c>
       <c r="BE44" s="1" t="str">
-        <f>ROUND(K44,0)&amp;"("&amp;ROUND((K44-Y44)/K44*100,0)&amp;")"</f>
+        <f t="shared" si="16"/>
         <v>84(-19)</v>
       </c>
       <c r="BF44" s="1" t="str">
-        <f>ROUND(O44,0)&amp;"("&amp;ROUND((O44-AC44)/O44*100,0)&amp;")"</f>
+        <f t="shared" si="17"/>
         <v>98(22)</v>
       </c>
       <c r="BG44" s="1" t="str">
-        <f>ROUND(C44,0)&amp;"("&amp;ROUND((C44-AE44)/C44*100,0)&amp;")"</f>
+        <f t="shared" si="18"/>
         <v>47(-97)</v>
       </c>
       <c r="BH44" s="1" t="str">
-        <f>ROUND(E44,0)&amp;"("&amp;ROUND((E44-AG44)/E44*100,1)&amp;")"</f>
+        <f t="shared" si="19"/>
         <v>51(-32.9)</v>
       </c>
       <c r="BI44" s="1" t="str">
-        <f>ROUND(AS44,0)&amp;"("&amp;ROUND((AS44-AU44)/AS44*100,0)&amp;")"</f>
+        <f t="shared" si="20"/>
         <v>45(-20)</v>
       </c>
       <c r="BJ44" s="1" t="str">
-        <f>ROUND(M44,0)&amp;"("&amp;ROUND((M44-AO44)/M44*100,0)&amp;")"</f>
+        <f t="shared" si="21"/>
         <v>93(-7)</v>
       </c>
       <c r="BK44" s="1" t="str">
-        <f>ROUND(G44,0)&amp;"("&amp;ROUND((G44-AI44)/G44*100,0)&amp;")"</f>
+        <f t="shared" si="22"/>
         <v>35(74)</v>
       </c>
       <c r="BL44" s="1" t="str">
-        <f>ROUND(I44,0)&amp;"("&amp;ROUND((I44-AK44)/I44*100,0)&amp;")"</f>
+        <f t="shared" si="23"/>
         <v>100(87)</v>
       </c>
       <c r="BM44" s="1" t="str">
-        <f>ROUND(K44,0)&amp;"("&amp;ROUND((K44-AM44)/K44*100,0)&amp;")"</f>
+        <f t="shared" si="24"/>
         <v>84(91)</v>
       </c>
       <c r="BN44" s="1" t="str">
-        <f>ROUND(O44,0)&amp;"("&amp;ROUND((O44-AQ44)/O44*100,0)&amp;")"</f>
+        <f t="shared" si="25"/>
         <v>98(75)</v>
       </c>
     </row>
-    <row r="45" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>44</v>
       </c>
@@ -10673,59 +10673,59 @@
         <v>45.9272373321296</v>
       </c>
       <c r="BB45" s="1" t="str">
-        <f>ROUND(M45,0)&amp;"("&amp;ROUND((M45-AA45)/M45*100,0)&amp;")"</f>
+        <f t="shared" si="13"/>
         <v>93(16)</v>
       </c>
       <c r="BC45" s="1" t="str">
-        <f>ROUND(G45,0)&amp;"("&amp;ROUND((G45-U45)/G45*100,0)&amp;")"</f>
+        <f t="shared" si="14"/>
         <v>37(8)</v>
       </c>
       <c r="BD45" s="1" t="str">
-        <f>ROUND(I45,0)&amp;"("&amp;ROUND((I45-W45)/I45*100,0)&amp;")"</f>
+        <f t="shared" si="15"/>
         <v>100(71)</v>
       </c>
       <c r="BE45" s="1" t="str">
-        <f>ROUND(K45,0)&amp;"("&amp;ROUND((K45-Y45)/K45*100,0)&amp;")"</f>
+        <f t="shared" si="16"/>
         <v>89(-12)</v>
       </c>
       <c r="BF45" s="1" t="str">
-        <f>ROUND(O45,0)&amp;"("&amp;ROUND((O45-AC45)/O45*100,0)&amp;")"</f>
+        <f t="shared" si="17"/>
         <v>96(11)</v>
       </c>
       <c r="BG45" s="1" t="str">
-        <f>ROUND(C45,0)&amp;"("&amp;ROUND((C45-AE45)/C45*100,0)&amp;")"</f>
+        <f t="shared" si="18"/>
         <v>43(-115)</v>
       </c>
       <c r="BH45" s="1" t="str">
-        <f>ROUND(E45,0)&amp;"("&amp;ROUND((E45-AG45)/E45*100,1)&amp;")"</f>
+        <f t="shared" si="19"/>
         <v>37(-117.9)</v>
       </c>
       <c r="BI45" s="1" t="str">
-        <f>ROUND(AS45,0)&amp;"("&amp;ROUND((AS45-AU45)/AS45*100,0)&amp;")"</f>
+        <f t="shared" si="20"/>
         <v>69(-7)</v>
       </c>
       <c r="BJ45" s="1" t="str">
-        <f>ROUND(M45,0)&amp;"("&amp;ROUND((M45-AO45)/M45*100,0)&amp;")"</f>
+        <f t="shared" si="21"/>
         <v>93(-8)</v>
       </c>
       <c r="BK45" s="1" t="str">
-        <f>ROUND(G45,0)&amp;"("&amp;ROUND((G45-AI45)/G45*100,0)&amp;")"</f>
+        <f t="shared" si="22"/>
         <v>37(40)</v>
       </c>
       <c r="BL45" s="1" t="str">
-        <f>ROUND(I45,0)&amp;"("&amp;ROUND((I45-AK45)/I45*100,0)&amp;")"</f>
+        <f t="shared" si="23"/>
         <v>100(80)</v>
       </c>
       <c r="BM45" s="1" t="str">
-        <f>ROUND(K45,0)&amp;"("&amp;ROUND((K45-AM45)/K45*100,0)&amp;")"</f>
+        <f t="shared" si="24"/>
         <v>89(78)</v>
       </c>
       <c r="BN45" s="1" t="str">
-        <f>ROUND(O45,0)&amp;"("&amp;ROUND((O45-AQ45)/O45*100,0)&amp;")"</f>
+        <f t="shared" si="25"/>
         <v>96(42)</v>
       </c>
     </row>
-    <row r="46" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>45</v>
       </c>
@@ -10886,59 +10886,59 @@
         <v>31.131503736097201</v>
       </c>
       <c r="BB46" s="1" t="str">
-        <f>ROUND(M46,0)&amp;"("&amp;ROUND((M46-AA46)/M46*100,0)&amp;")"</f>
+        <f t="shared" si="13"/>
         <v>96(34)</v>
       </c>
       <c r="BC46" s="1" t="str">
-        <f>ROUND(G46,0)&amp;"("&amp;ROUND((G46-U46)/G46*100,0)&amp;")"</f>
+        <f t="shared" si="14"/>
         <v>36(-68)</v>
       </c>
       <c r="BD46" s="1" t="str">
-        <f>ROUND(I46,0)&amp;"("&amp;ROUND((I46-W46)/I46*100,0)&amp;")"</f>
+        <f t="shared" si="15"/>
         <v>100(78)</v>
       </c>
       <c r="BE46" s="1" t="str">
-        <f>ROUND(K46,0)&amp;"("&amp;ROUND((K46-Y46)/K46*100,0)&amp;")"</f>
+        <f t="shared" si="16"/>
         <v>87(-15)</v>
       </c>
       <c r="BF46" s="1" t="str">
-        <f>ROUND(O46,0)&amp;"("&amp;ROUND((O46-AC46)/O46*100,0)&amp;")"</f>
+        <f t="shared" si="17"/>
         <v>99(18)</v>
       </c>
       <c r="BG46" s="1" t="str">
-        <f>ROUND(C46,0)&amp;"("&amp;ROUND((C46-AE46)/C46*100,0)&amp;")"</f>
+        <f t="shared" si="18"/>
         <v>62(-56)</v>
       </c>
       <c r="BH46" s="1" t="str">
-        <f>ROUND(E46,0)&amp;"("&amp;ROUND((E46-AG46)/E46*100,1)&amp;")"</f>
+        <f t="shared" si="19"/>
         <v>65(-9.4)</v>
       </c>
       <c r="BI46" s="1" t="str">
-        <f>ROUND(AS46,0)&amp;"("&amp;ROUND((AS46-AU46)/AS46*100,0)&amp;")"</f>
+        <f t="shared" si="20"/>
         <v>49(-20)</v>
       </c>
       <c r="BJ46" s="1" t="str">
-        <f>ROUND(M46,0)&amp;"("&amp;ROUND((M46-AO46)/M46*100,0)&amp;")"</f>
+        <f t="shared" si="21"/>
         <v>96(-4)</v>
       </c>
       <c r="BK46" s="1" t="str">
-        <f>ROUND(G46,0)&amp;"("&amp;ROUND((G46-AI46)/G46*100,0)&amp;")"</f>
+        <f t="shared" si="22"/>
         <v>36(71)</v>
       </c>
       <c r="BL46" s="1" t="str">
-        <f>ROUND(I46,0)&amp;"("&amp;ROUND((I46-AK46)/I46*100,0)&amp;")"</f>
+        <f t="shared" si="23"/>
         <v>100(84)</v>
       </c>
       <c r="BM46" s="1" t="str">
-        <f>ROUND(K46,0)&amp;"("&amp;ROUND((K46-AM46)/K46*100,0)&amp;")"</f>
+        <f t="shared" si="24"/>
         <v>87(92)</v>
       </c>
       <c r="BN46" s="1" t="str">
-        <f>ROUND(O46,0)&amp;"("&amp;ROUND((O46-AQ46)/O46*100,0)&amp;")"</f>
+        <f t="shared" si="25"/>
         <v>99(77)</v>
       </c>
     </row>
-    <row r="47" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>46</v>
       </c>
@@ -11099,59 +11099,59 @@
         <v>29.219135802469101</v>
       </c>
       <c r="BB47" s="1" t="str">
-        <f>ROUND(M47,0)&amp;"("&amp;ROUND((M47-AA47)/M47*100,0)&amp;")"</f>
+        <f t="shared" si="13"/>
         <v>95(38)</v>
       </c>
       <c r="BC47" s="1" t="str">
-        <f>ROUND(G47,0)&amp;"("&amp;ROUND((G47-U47)/G47*100,0)&amp;")"</f>
+        <f t="shared" si="14"/>
         <v>33(-59)</v>
       </c>
       <c r="BD47" s="1" t="str">
-        <f>ROUND(I47,0)&amp;"("&amp;ROUND((I47-W47)/I47*100,0)&amp;")"</f>
+        <f t="shared" si="15"/>
         <v>100(81)</v>
       </c>
       <c r="BE47" s="1" t="str">
-        <f>ROUND(K47,0)&amp;"("&amp;ROUND((K47-Y47)/K47*100,0)&amp;")"</f>
+        <f t="shared" si="16"/>
         <v>85(-18)</v>
       </c>
       <c r="BF47" s="1" t="str">
-        <f>ROUND(O47,0)&amp;"("&amp;ROUND((O47-AC47)/O47*100,0)&amp;")"</f>
+        <f t="shared" si="17"/>
         <v>99(21)</v>
       </c>
       <c r="BG47" s="1" t="str">
-        <f>ROUND(C47,0)&amp;"("&amp;ROUND((C47-AE47)/C47*100,0)&amp;")"</f>
+        <f t="shared" si="18"/>
         <v>51(-84)</v>
       </c>
       <c r="BH47" s="1" t="str">
-        <f>ROUND(E47,0)&amp;"("&amp;ROUND((E47-AG47)/E47*100,1)&amp;")"</f>
+        <f t="shared" si="19"/>
         <v>58(-14.4)</v>
       </c>
       <c r="BI47" s="1" t="str">
-        <f>ROUND(AS47,0)&amp;"("&amp;ROUND((AS47-AU47)/AS47*100,0)&amp;")"</f>
+        <f t="shared" si="20"/>
         <v>45(-16)</v>
       </c>
       <c r="BJ47" s="1" t="str">
-        <f>ROUND(M47,0)&amp;"("&amp;ROUND((M47-AO47)/M47*100,0)&amp;")"</f>
+        <f t="shared" si="21"/>
         <v>95(-6)</v>
       </c>
       <c r="BK47" s="1" t="str">
-        <f>ROUND(G47,0)&amp;"("&amp;ROUND((G47-AI47)/G47*100,0)&amp;")"</f>
+        <f t="shared" si="22"/>
         <v>33(76)</v>
       </c>
       <c r="BL47" s="1" t="str">
-        <f>ROUND(I47,0)&amp;"("&amp;ROUND((I47-AK47)/I47*100,0)&amp;")"</f>
+        <f t="shared" si="23"/>
         <v>100(87)</v>
       </c>
       <c r="BM47" s="1" t="str">
-        <f>ROUND(K47,0)&amp;"("&amp;ROUND((K47-AM47)/K47*100,0)&amp;")"</f>
+        <f t="shared" si="24"/>
         <v>85(93)</v>
       </c>
       <c r="BN47" s="1" t="str">
-        <f>ROUND(O47,0)&amp;"("&amp;ROUND((O47-AQ47)/O47*100,0)&amp;")"</f>
+        <f t="shared" si="25"/>
         <v>99(79)</v>
       </c>
     </row>
-    <row r="48" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>47</v>
       </c>
@@ -11312,59 +11312,59 @@
         <v>28.595991428211299</v>
       </c>
       <c r="BB48" s="1" t="str">
-        <f>ROUND(M48,0)&amp;"("&amp;ROUND((M48-AA48)/M48*100,0)&amp;")"</f>
+        <f t="shared" si="13"/>
         <v>93(38)</v>
       </c>
       <c r="BC48" s="1" t="str">
-        <f>ROUND(G48,0)&amp;"("&amp;ROUND((G48-U48)/G48*100,0)&amp;")"</f>
+        <f t="shared" si="14"/>
         <v>35(-32)</v>
       </c>
       <c r="BD48" s="1" t="str">
-        <f>ROUND(I48,0)&amp;"("&amp;ROUND((I48-W48)/I48*100,0)&amp;")"</f>
+        <f t="shared" si="15"/>
         <v>100(80)</v>
       </c>
       <c r="BE48" s="1" t="str">
-        <f>ROUND(K48,0)&amp;"("&amp;ROUND((K48-Y48)/K48*100,0)&amp;")"</f>
+        <f t="shared" si="16"/>
         <v>83(-20)</v>
       </c>
       <c r="BF48" s="1" t="str">
-        <f>ROUND(O48,0)&amp;"("&amp;ROUND((O48-AC48)/O48*100,0)&amp;")"</f>
+        <f t="shared" si="17"/>
         <v>98(23)</v>
       </c>
       <c r="BG48" s="1" t="str">
-        <f>ROUND(C48,0)&amp;"("&amp;ROUND((C48-AE48)/C48*100,0)&amp;")"</f>
+        <f t="shared" si="18"/>
         <v>46(-102)</v>
       </c>
       <c r="BH48" s="1" t="str">
-        <f>ROUND(E48,0)&amp;"("&amp;ROUND((E48-AG48)/E48*100,1)&amp;")"</f>
+        <f t="shared" si="19"/>
         <v>51(-28.6)</v>
       </c>
       <c r="BI48" s="1" t="str">
-        <f>ROUND(AS48,0)&amp;"("&amp;ROUND((AS48-AU48)/AS48*100,0)&amp;")"</f>
+        <f t="shared" si="20"/>
         <v>43(-18)</v>
       </c>
       <c r="BJ48" s="1" t="str">
-        <f>ROUND(M48,0)&amp;"("&amp;ROUND((M48-AO48)/M48*100,0)&amp;")"</f>
+        <f t="shared" si="21"/>
         <v>93(-7)</v>
       </c>
       <c r="BK48" s="1" t="str">
-        <f>ROUND(G48,0)&amp;"("&amp;ROUND((G48-AI48)/G48*100,0)&amp;")"</f>
+        <f t="shared" si="22"/>
         <v>35(78)</v>
       </c>
       <c r="BL48" s="1" t="str">
-        <f>ROUND(I48,0)&amp;"("&amp;ROUND((I48-AK48)/I48*100,0)&amp;")"</f>
+        <f t="shared" si="23"/>
         <v>100(89)</v>
       </c>
       <c r="BM48" s="1" t="str">
-        <f>ROUND(K48,0)&amp;"("&amp;ROUND((K48-AM48)/K48*100,0)&amp;")"</f>
+        <f t="shared" si="24"/>
         <v>83(93)</v>
       </c>
       <c r="BN48" s="1" t="str">
-        <f>ROUND(O48,0)&amp;"("&amp;ROUND((O48-AQ48)/O48*100,0)&amp;")"</f>
+        <f t="shared" si="25"/>
         <v>98(78)</v>
       </c>
     </row>
-    <row r="49" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>48</v>
       </c>
@@ -11525,59 +11525,59 @@
         <v>29.007696554411702</v>
       </c>
       <c r="BB49" s="1" t="str">
-        <f>ROUND(M49,0)&amp;"("&amp;ROUND((M49-AA49)/M49*100,0)&amp;")"</f>
+        <f t="shared" si="13"/>
         <v>92(36)</v>
       </c>
       <c r="BC49" s="1" t="str">
-        <f>ROUND(G49,0)&amp;"("&amp;ROUND((G49-U49)/G49*100,0)&amp;")"</f>
+        <f t="shared" si="14"/>
         <v>37(-7)</v>
       </c>
       <c r="BD49" s="1" t="str">
-        <f>ROUND(I49,0)&amp;"("&amp;ROUND((I49-W49)/I49*100,0)&amp;")"</f>
+        <f t="shared" si="15"/>
         <v>100(79)</v>
       </c>
       <c r="BE49" s="1" t="str">
-        <f>ROUND(K49,0)&amp;"("&amp;ROUND((K49-Y49)/K49*100,0)&amp;")"</f>
+        <f t="shared" si="16"/>
         <v>83(-20)</v>
       </c>
       <c r="BF49" s="1" t="str">
-        <f>ROUND(O49,0)&amp;"("&amp;ROUND((O49-AC49)/O49*100,0)&amp;")"</f>
+        <f t="shared" si="17"/>
         <v>98(23)</v>
       </c>
       <c r="BG49" s="1" t="str">
-        <f>ROUND(C49,0)&amp;"("&amp;ROUND((C49-AE49)/C49*100,0)&amp;")"</f>
+        <f t="shared" si="18"/>
         <v>41(-120)</v>
       </c>
       <c r="BH49" s="1" t="str">
-        <f>ROUND(E49,0)&amp;"("&amp;ROUND((E49-AG49)/E49*100,1)&amp;")"</f>
+        <f t="shared" si="19"/>
         <v>44(-52.6)</v>
       </c>
       <c r="BI49" s="1" t="str">
-        <f>ROUND(AS49,0)&amp;"("&amp;ROUND((AS49-AU49)/AS49*100,0)&amp;")"</f>
+        <f t="shared" si="20"/>
         <v>44(-20)</v>
       </c>
       <c r="BJ49" s="1" t="str">
-        <f>ROUND(M49,0)&amp;"("&amp;ROUND((M49-AO49)/M49*100,0)&amp;")"</f>
+        <f t="shared" si="21"/>
         <v>92(-8)</v>
       </c>
       <c r="BK49" s="1" t="str">
-        <f>ROUND(G49,0)&amp;"("&amp;ROUND((G49-AI49)/G49*100,0)&amp;")"</f>
+        <f t="shared" si="22"/>
         <v>37(78)</v>
       </c>
       <c r="BL49" s="1" t="str">
-        <f>ROUND(I49,0)&amp;"("&amp;ROUND((I49-AK49)/I49*100,0)&amp;")"</f>
+        <f t="shared" si="23"/>
         <v>100(89)</v>
       </c>
       <c r="BM49" s="1" t="str">
-        <f>ROUND(K49,0)&amp;"("&amp;ROUND((K49-AM49)/K49*100,0)&amp;")"</f>
+        <f t="shared" si="24"/>
         <v>83(92)</v>
       </c>
       <c r="BN49" s="1" t="str">
-        <f>ROUND(O49,0)&amp;"("&amp;ROUND((O49-AQ49)/O49*100,0)&amp;")"</f>
+        <f t="shared" si="25"/>
         <v>98(76)</v>
       </c>
     </row>
-    <row r="50" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>49</v>
       </c>
@@ -11738,59 +11738,59 @@
         <v>31.8658373631967</v>
       </c>
       <c r="BB50" s="1" t="str">
-        <f>ROUND(M50,0)&amp;"("&amp;ROUND((M50-AA50)/M50*100,0)&amp;")"</f>
+        <f t="shared" si="13"/>
         <v>89(33)</v>
       </c>
       <c r="BC50" s="1" t="str">
-        <f>ROUND(G50,0)&amp;"("&amp;ROUND((G50-U50)/G50*100,0)&amp;")"</f>
+        <f t="shared" si="14"/>
         <v>36(15)</v>
       </c>
       <c r="BD50" s="1" t="str">
-        <f>ROUND(I50,0)&amp;"("&amp;ROUND((I50-W50)/I50*100,0)&amp;")"</f>
+        <f t="shared" si="15"/>
         <v>100(76)</v>
       </c>
       <c r="BE50" s="1" t="str">
-        <f>ROUND(K50,0)&amp;"("&amp;ROUND((K50-Y50)/K50*100,0)&amp;")"</f>
+        <f t="shared" si="16"/>
         <v>80(-24)</v>
       </c>
       <c r="BF50" s="1" t="str">
-        <f>ROUND(O50,0)&amp;"("&amp;ROUND((O50-AC50)/O50*100,0)&amp;")"</f>
+        <f t="shared" si="17"/>
         <v>96(25)</v>
       </c>
       <c r="BG50" s="1" t="str">
-        <f>ROUND(C50,0)&amp;"("&amp;ROUND((C50-AE50)/C50*100,0)&amp;")"</f>
+        <f t="shared" si="18"/>
         <v>34(-160)</v>
       </c>
       <c r="BH50" s="1" t="str">
-        <f>ROUND(E50,0)&amp;"("&amp;ROUND((E50-AG50)/E50*100,1)&amp;")"</f>
+        <f t="shared" si="19"/>
         <v>34(-95.8)</v>
       </c>
       <c r="BI50" s="1" t="str">
-        <f>ROUND(AS50,0)&amp;"("&amp;ROUND((AS50-AU50)/AS50*100,0)&amp;")"</f>
+        <f t="shared" si="20"/>
         <v>46(-24)</v>
       </c>
       <c r="BJ50" s="1" t="str">
-        <f>ROUND(M50,0)&amp;"("&amp;ROUND((M50-AO50)/M50*100,0)&amp;")"</f>
+        <f t="shared" si="21"/>
         <v>89(-11)</v>
       </c>
       <c r="BK50" s="1" t="str">
-        <f>ROUND(G50,0)&amp;"("&amp;ROUND((G50-AI50)/G50*100,0)&amp;")"</f>
+        <f t="shared" si="22"/>
         <v>36(68)</v>
       </c>
       <c r="BL50" s="1" t="str">
-        <f>ROUND(I50,0)&amp;"("&amp;ROUND((I50-AK50)/I50*100,0)&amp;")"</f>
+        <f t="shared" si="23"/>
         <v>100(86)</v>
       </c>
       <c r="BM50" s="1" t="str">
-        <f>ROUND(K50,0)&amp;"("&amp;ROUND((K50-AM50)/K50*100,0)&amp;")"</f>
+        <f t="shared" si="24"/>
         <v>80(85)</v>
       </c>
       <c r="BN50" s="1" t="str">
-        <f>ROUND(O50,0)&amp;"("&amp;ROUND((O50-AQ50)/O50*100,0)&amp;")"</f>
+        <f t="shared" si="25"/>
         <v>96(66)</v>
       </c>
     </row>
-    <row r="51" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>50</v>
       </c>
@@ -11951,59 +11951,59 @@
         <v>40.554530836170997</v>
       </c>
       <c r="BB51" s="1" t="str">
-        <f>ROUND(M51,0)&amp;"("&amp;ROUND((M51-AA51)/M51*100,0)&amp;")"</f>
+        <f t="shared" si="13"/>
         <v>97(23)</v>
       </c>
       <c r="BC51" s="1" t="str">
-        <f>ROUND(G51,0)&amp;"("&amp;ROUND((G51-U51)/G51*100,0)&amp;")"</f>
+        <f t="shared" si="14"/>
         <v>38(-32)</v>
       </c>
       <c r="BD51" s="1" t="str">
-        <f>ROUND(I51,0)&amp;"("&amp;ROUND((I51-W51)/I51*100,0)&amp;")"</f>
+        <f t="shared" si="15"/>
         <v>100(73)</v>
       </c>
       <c r="BE51" s="1" t="str">
-        <f>ROUND(K51,0)&amp;"("&amp;ROUND((K51-Y51)/K51*100,0)&amp;")"</f>
+        <f t="shared" si="16"/>
         <v>91(-10)</v>
       </c>
       <c r="BF51" s="1" t="str">
-        <f>ROUND(O51,0)&amp;"("&amp;ROUND((O51-AC51)/O51*100,0)&amp;")"</f>
+        <f t="shared" si="17"/>
         <v>99(12)</v>
       </c>
       <c r="BG51" s="1" t="str">
-        <f>ROUND(C51,0)&amp;"("&amp;ROUND((C51-AE51)/C51*100,0)&amp;")"</f>
+        <f t="shared" si="18"/>
         <v>57(-66)</v>
       </c>
       <c r="BH51" s="1" t="str">
-        <f>ROUND(E51,0)&amp;"("&amp;ROUND((E51-AG51)/E51*100,1)&amp;")"</f>
+        <f t="shared" si="19"/>
         <v>54(-45.5)</v>
       </c>
       <c r="BI51" s="1" t="str">
-        <f>ROUND(AS51,0)&amp;"("&amp;ROUND((AS51-AU51)/AS51*100,0)&amp;")"</f>
+        <f t="shared" si="20"/>
         <v>65(-2)</v>
       </c>
       <c r="BJ51" s="1" t="str">
-        <f>ROUND(M51,0)&amp;"("&amp;ROUND((M51-AO51)/M51*100,0)&amp;")"</f>
+        <f t="shared" si="21"/>
         <v>97(-3)</v>
       </c>
       <c r="BK51" s="1" t="str">
-        <f>ROUND(G51,0)&amp;"("&amp;ROUND((G51-AI51)/G51*100,0)&amp;")"</f>
+        <f t="shared" si="22"/>
         <v>38(48)</v>
       </c>
       <c r="BL51" s="1" t="str">
-        <f>ROUND(I51,0)&amp;"("&amp;ROUND((I51-AK51)/I51*100,0)&amp;")"</f>
+        <f t="shared" si="23"/>
         <v>100(80)</v>
       </c>
       <c r="BM51" s="1" t="str">
-        <f>ROUND(K51,0)&amp;"("&amp;ROUND((K51-AM51)/K51*100,0)&amp;")"</f>
+        <f t="shared" si="24"/>
         <v>91(85)</v>
       </c>
       <c r="BN51" s="1" t="str">
-        <f>ROUND(O51,0)&amp;"("&amp;ROUND((O51-AQ51)/O51*100,0)&amp;")"</f>
+        <f t="shared" si="25"/>
         <v>99(58)</v>
       </c>
     </row>
-    <row r="52" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>51</v>
       </c>
@@ -12164,59 +12164,59 @@
         <v>43.021138869222199</v>
       </c>
       <c r="BB52" s="1" t="str">
-        <f>ROUND(M52,0)&amp;"("&amp;ROUND((M52-AA52)/M52*100,0)&amp;")"</f>
+        <f t="shared" si="13"/>
         <v>96(20)</v>
       </c>
       <c r="BC52" s="1" t="str">
-        <f>ROUND(G52,0)&amp;"("&amp;ROUND((G52-U52)/G52*100,0)&amp;")"</f>
+        <f t="shared" si="14"/>
         <v>40(4)</v>
       </c>
       <c r="BD52" s="1" t="str">
-        <f>ROUND(I52,0)&amp;"("&amp;ROUND((I52-W52)/I52*100,0)&amp;")"</f>
+        <f t="shared" si="15"/>
         <v>100(71)</v>
       </c>
       <c r="BE52" s="1" t="str">
-        <f>ROUND(K52,0)&amp;"("&amp;ROUND((K52-Y52)/K52*100,0)&amp;")"</f>
+        <f t="shared" si="16"/>
         <v>90(-10)</v>
       </c>
       <c r="BF52" s="1" t="str">
-        <f>ROUND(O52,0)&amp;"("&amp;ROUND((O52-AC52)/O52*100,0)&amp;")"</f>
+        <f t="shared" si="17"/>
         <v>98(12)</v>
       </c>
       <c r="BG52" s="1" t="str">
-        <f>ROUND(C52,0)&amp;"("&amp;ROUND((C52-AE52)/C52*100,0)&amp;")"</f>
+        <f t="shared" si="18"/>
         <v>50(-89)</v>
       </c>
       <c r="BH52" s="1" t="str">
-        <f>ROUND(E52,0)&amp;"("&amp;ROUND((E52-AG52)/E52*100,1)&amp;")"</f>
+        <f t="shared" si="19"/>
         <v>41(-92.8)</v>
       </c>
       <c r="BI52" s="1" t="str">
-        <f>ROUND(AS52,0)&amp;"("&amp;ROUND((AS52-AU52)/AS52*100,0)&amp;")"</f>
+        <f t="shared" si="20"/>
         <v>66(-3)</v>
       </c>
       <c r="BJ52" s="1" t="str">
-        <f>ROUND(M52,0)&amp;"("&amp;ROUND((M52-AO52)/M52*100,0)&amp;")"</f>
+        <f t="shared" si="21"/>
         <v>96(-5)</v>
       </c>
       <c r="BK52" s="1" t="str">
-        <f>ROUND(G52,0)&amp;"("&amp;ROUND((G52-AI52)/G52*100,0)&amp;")"</f>
+        <f t="shared" si="22"/>
         <v>40(49)</v>
       </c>
       <c r="BL52" s="1" t="str">
-        <f>ROUND(I52,0)&amp;"("&amp;ROUND((I52-AK52)/I52*100,0)&amp;")"</f>
+        <f t="shared" si="23"/>
         <v>100(83)</v>
       </c>
       <c r="BM52" s="1" t="str">
-        <f>ROUND(K52,0)&amp;"("&amp;ROUND((K52-AM52)/K52*100,0)&amp;")"</f>
+        <f t="shared" si="24"/>
         <v>90(82)</v>
       </c>
       <c r="BN52" s="1" t="str">
-        <f>ROUND(O52,0)&amp;"("&amp;ROUND((O52-AQ52)/O52*100,0)&amp;")"</f>
+        <f t="shared" si="25"/>
         <v>98(52)</v>
       </c>
     </row>
-    <row r="53" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>52</v>
       </c>
@@ -12377,59 +12377,59 @@
         <v>45.415283405219398</v>
       </c>
       <c r="BB53" s="1" t="str">
-        <f>ROUND(M53,0)&amp;"("&amp;ROUND((M53-AA53)/M53*100,0)&amp;")"</f>
+        <f t="shared" si="13"/>
         <v>94(17)</v>
       </c>
       <c r="BC53" s="1" t="str">
-        <f>ROUND(G53,0)&amp;"("&amp;ROUND((G53-U53)/G53*100,0)&amp;")"</f>
+        <f t="shared" si="14"/>
         <v>39(18)</v>
       </c>
       <c r="BD53" s="1" t="str">
-        <f>ROUND(I53,0)&amp;"("&amp;ROUND((I53-W53)/I53*100,0)&amp;")"</f>
+        <f t="shared" si="15"/>
         <v>100(71)</v>
       </c>
       <c r="BE53" s="1" t="str">
-        <f>ROUND(K53,0)&amp;"("&amp;ROUND((K53-Y53)/K53*100,0)&amp;")"</f>
+        <f t="shared" si="16"/>
         <v>90(-11)</v>
       </c>
       <c r="BF53" s="1" t="str">
-        <f>ROUND(O53,0)&amp;"("&amp;ROUND((O53-AC53)/O53*100,0)&amp;")"</f>
+        <f t="shared" si="17"/>
         <v>97(11)</v>
       </c>
       <c r="BG53" s="1" t="str">
-        <f>ROUND(C53,0)&amp;"("&amp;ROUND((C53-AE53)/C53*100,0)&amp;")"</f>
+        <f t="shared" si="18"/>
         <v>43(-118)</v>
       </c>
       <c r="BH53" s="1" t="str">
-        <f>ROUND(E53,0)&amp;"("&amp;ROUND((E53-AG53)/E53*100,1)&amp;")"</f>
+        <f t="shared" si="19"/>
         <v>34(-136.4)</v>
       </c>
       <c r="BI53" s="1" t="str">
-        <f>ROUND(AS53,0)&amp;"("&amp;ROUND((AS53-AU53)/AS53*100,0)&amp;")"</f>
+        <f t="shared" si="20"/>
         <v>67(-7)</v>
       </c>
       <c r="BJ53" s="1" t="str">
-        <f>ROUND(M53,0)&amp;"("&amp;ROUND((M53-AO53)/M53*100,0)&amp;")"</f>
+        <f t="shared" si="21"/>
         <v>94(-6)</v>
       </c>
       <c r="BK53" s="1" t="str">
-        <f>ROUND(G53,0)&amp;"("&amp;ROUND((G53-AI53)/G53*100,0)&amp;")"</f>
+        <f t="shared" si="22"/>
         <v>39(47)</v>
       </c>
       <c r="BL53" s="1" t="str">
-        <f>ROUND(I53,0)&amp;"("&amp;ROUND((I53-AK53)/I53*100,0)&amp;")"</f>
+        <f t="shared" si="23"/>
         <v>100(82)</v>
       </c>
       <c r="BM53" s="1" t="str">
-        <f>ROUND(K53,0)&amp;"("&amp;ROUND((K53-AM53)/K53*100,0)&amp;")"</f>
+        <f t="shared" si="24"/>
         <v>90(81)</v>
       </c>
       <c r="BN53" s="1" t="str">
-        <f>ROUND(O53,0)&amp;"("&amp;ROUND((O53-AQ53)/O53*100,0)&amp;")"</f>
+        <f t="shared" si="25"/>
         <v>97(46)</v>
       </c>
     </row>
-    <row r="54" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>53</v>
       </c>
@@ -12590,59 +12590,59 @@
         <v>47.826512968299703</v>
       </c>
       <c r="BB54" s="1" t="str">
-        <f>ROUND(M54,0)&amp;"("&amp;ROUND((M54-AA54)/M54*100,0)&amp;")"</f>
+        <f t="shared" si="13"/>
         <v>92(15)</v>
       </c>
       <c r="BC54" s="1" t="str">
-        <f>ROUND(G54,0)&amp;"("&amp;ROUND((G54-U54)/G54*100,0)&amp;")"</f>
+        <f t="shared" si="14"/>
         <v>36(24)</v>
       </c>
       <c r="BD54" s="1" t="str">
-        <f>ROUND(I54,0)&amp;"("&amp;ROUND((I54-W54)/I54*100,0)&amp;")"</f>
+        <f t="shared" si="15"/>
         <v>100(72)</v>
       </c>
       <c r="BE54" s="1" t="str">
-        <f>ROUND(K54,0)&amp;"("&amp;ROUND((K54-Y54)/K54*100,0)&amp;")"</f>
+        <f t="shared" si="16"/>
         <v>88(-13)</v>
       </c>
       <c r="BF54" s="1" t="str">
-        <f>ROUND(O54,0)&amp;"("&amp;ROUND((O54-AC54)/O54*100,0)&amp;")"</f>
+        <f t="shared" si="17"/>
         <v>96(11)</v>
       </c>
       <c r="BG54" s="1" t="str">
-        <f>ROUND(C54,0)&amp;"("&amp;ROUND((C54-AE54)/C54*100,0)&amp;")"</f>
+        <f t="shared" si="18"/>
         <v>35(-161)</v>
       </c>
       <c r="BH54" s="1" t="str">
-        <f>ROUND(E54,0)&amp;"("&amp;ROUND((E54-AG54)/E54*100,1)&amp;")"</f>
+        <f t="shared" si="19"/>
         <v>29(-182.2)</v>
       </c>
       <c r="BI54" s="1" t="str">
-        <f>ROUND(AS54,0)&amp;"("&amp;ROUND((AS54-AU54)/AS54*100,0)&amp;")"</f>
+        <f t="shared" si="20"/>
         <v>70(-10)</v>
       </c>
       <c r="BJ54" s="1" t="str">
-        <f>ROUND(M54,0)&amp;"("&amp;ROUND((M54-AO54)/M54*100,0)&amp;")"</f>
+        <f t="shared" si="21"/>
         <v>92(-8)</v>
       </c>
       <c r="BK54" s="1" t="str">
-        <f>ROUND(G54,0)&amp;"("&amp;ROUND((G54-AI54)/G54*100,0)&amp;")"</f>
+        <f t="shared" si="22"/>
         <v>36(40)</v>
       </c>
       <c r="BL54" s="1" t="str">
-        <f>ROUND(I54,0)&amp;"("&amp;ROUND((I54-AK54)/I54*100,0)&amp;")"</f>
+        <f t="shared" si="23"/>
         <v>100(81)</v>
       </c>
       <c r="BM54" s="1" t="str">
-        <f>ROUND(K54,0)&amp;"("&amp;ROUND((K54-AM54)/K54*100,0)&amp;")"</f>
+        <f t="shared" si="24"/>
         <v>88(78)</v>
       </c>
       <c r="BN54" s="1" t="str">
-        <f>ROUND(O54,0)&amp;"("&amp;ROUND((O54-AQ54)/O54*100,0)&amp;")"</f>
+        <f t="shared" si="25"/>
         <v>96(38)</v>
       </c>
     </row>
-    <row r="55" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>54</v>
       </c>
@@ -12803,55 +12803,55 @@
         <v>52.547710364585697</v>
       </c>
       <c r="BB55" s="1" t="str">
-        <f>ROUND(M55,0)&amp;"("&amp;ROUND((M55-AA55)/M55*100,0)&amp;")"</f>
+        <f t="shared" si="13"/>
         <v>87(5)</v>
       </c>
       <c r="BC55" s="1" t="str">
-        <f>ROUND(G55,0)&amp;"("&amp;ROUND((G55-U55)/G55*100,0)&amp;")"</f>
+        <f t="shared" si="14"/>
         <v>35(20)</v>
       </c>
       <c r="BD55" s="1" t="str">
-        <f>ROUND(I55,0)&amp;"("&amp;ROUND((I55-W55)/I55*100,0)&amp;")"</f>
+        <f t="shared" si="15"/>
         <v>100(68)</v>
       </c>
       <c r="BE55" s="1" t="str">
-        <f>ROUND(K55,0)&amp;"("&amp;ROUND((K55-Y55)/K55*100,0)&amp;")"</f>
+        <f t="shared" si="16"/>
         <v>86(-16)</v>
       </c>
       <c r="BF55" s="1" t="str">
-        <f>ROUND(O55,0)&amp;"("&amp;ROUND((O55-AC55)/O55*100,0)&amp;")"</f>
+        <f t="shared" si="17"/>
         <v>93(11)</v>
       </c>
       <c r="BG55" s="1" t="str">
-        <f>ROUND(C55,0)&amp;"("&amp;ROUND((C55-AE55)/C55*100,0)&amp;")"</f>
+        <f t="shared" si="18"/>
         <v>34(-168)</v>
       </c>
       <c r="BH55" s="1" t="str">
-        <f>ROUND(E55,0)&amp;"("&amp;ROUND((E55-AG55)/E55*100,1)&amp;")"</f>
+        <f t="shared" si="19"/>
         <v>29(-178.1)</v>
       </c>
       <c r="BI55" s="1" t="str">
-        <f>ROUND(AS55,0)&amp;"("&amp;ROUND((AS55-AU55)/AS55*100,0)&amp;")"</f>
+        <f t="shared" si="20"/>
         <v>77(-9)</v>
       </c>
       <c r="BJ55" s="1" t="str">
-        <f>ROUND(M55,0)&amp;"("&amp;ROUND((M55-AO55)/M55*100,0)&amp;")"</f>
+        <f t="shared" si="21"/>
         <v>87(-15)</v>
       </c>
       <c r="BK55" s="1" t="str">
-        <f>ROUND(G55,0)&amp;"("&amp;ROUND((G55-AI55)/G55*100,0)&amp;")"</f>
+        <f t="shared" si="22"/>
         <v>35(18)</v>
       </c>
       <c r="BL55" s="1" t="str">
-        <f>ROUND(I55,0)&amp;"("&amp;ROUND((I55-AK55)/I55*100,0)&amp;")"</f>
+        <f t="shared" si="23"/>
         <v>100(74)</v>
       </c>
       <c r="BM55" s="1" t="str">
-        <f>ROUND(K55,0)&amp;"("&amp;ROUND((K55-AM55)/K55*100,0)&amp;")"</f>
+        <f t="shared" si="24"/>
         <v>86(67)</v>
       </c>
       <c r="BN55" s="1" t="str">
-        <f>ROUND(O55,0)&amp;"("&amp;ROUND((O55-AQ55)/O55*100,0)&amp;")"</f>
+        <f t="shared" si="25"/>
         <v>93(21)</v>
       </c>
     </row>
@@ -12863,12 +12863,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{829C5016-5CDE-4C2B-8E44-9A0CEC325587}">
   <dimension ref="A1:X55"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="16384" width="8.7265625" style="2"/>
+    <col min="1" max="16384" width="8.7109375" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>1</v>
       </c>
@@ -12942,7 +12942,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>45.865506961097502</v>
       </c>
@@ -13016,7 +13016,7 @@
         <v>32.948576223238298</v>
       </c>
     </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>27.099296678326699</v>
       </c>
@@ -13090,7 +13090,7 @@
         <v>24.143361741586599</v>
       </c>
     </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>17.049636337717001</v>
       </c>
@@ -13164,7 +13164,7 @@
         <v>25.448854071778701</v>
       </c>
     </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>23.9903784814251</v>
       </c>
@@ -13238,7 +13238,7 @@
         <v>51.2991808920588</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>30.480872526915402</v>
       </c>
@@ -13312,7 +13312,7 @@
         <v>86.355227297612203</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>18.0519533296088</v>
       </c>
@@ -13386,7 +13386,7 @@
         <v>39.703509821210403</v>
       </c>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>30.488153297890499</v>
       </c>
@@ -13460,7 +13460,7 @@
         <v>47.032600815144797</v>
       </c>
     </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>29.417522860738099</v>
       </c>
@@ -13534,7 +13534,7 @@
         <v>75.697226562859498</v>
       </c>
     </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>36.589333896154002</v>
       </c>
@@ -13608,7 +13608,7 @@
         <v>25.571467713561301</v>
       </c>
     </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>42.824769906492499</v>
       </c>
@@ -13682,7 +13682,7 @@
         <v>23.907161956899898</v>
       </c>
     </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>35.023951334694502</v>
       </c>
@@ -13756,7 +13756,7 @@
         <v>23.696243106115499</v>
       </c>
     </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>45.108726634025302</v>
       </c>
@@ -13830,7 +13830,7 @@
         <v>36.8878743494666</v>
       </c>
     </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>67.942329839569098</v>
       </c>
@@ -13904,7 +13904,7 @@
         <v>47.695158363979601</v>
       </c>
     </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>74.4191271935548</v>
       </c>
@@ -13978,7 +13978,7 @@
         <v>38.090419866474697</v>
       </c>
     </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>83.888097020798497</v>
       </c>
@@ -14052,7 +14052,7 @@
         <v>34.698657265820202</v>
       </c>
     </row>
-    <row r="17" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>81.495878856592697</v>
       </c>
@@ -14126,7 +14126,7 @@
         <v>11.7242933692908</v>
       </c>
     </row>
-    <row r="18" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>54.184976237581502</v>
       </c>
@@ -14200,7 +14200,7 @@
         <v>8.4418912534566104</v>
       </c>
     </row>
-    <row r="19" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>69.685616582645096</v>
       </c>
@@ -14274,7 +14274,7 @@
         <v>41.3567514915594</v>
       </c>
     </row>
-    <row r="20" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>77.056591975510699</v>
       </c>
@@ -14348,7 +14348,7 @@
         <v>33.941435032451501</v>
       </c>
     </row>
-    <row r="21" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <v>58.559846869254201</v>
       </c>
@@ -14422,7 +14422,7 @@
         <v>20.769247468417699</v>
       </c>
     </row>
-    <row r="22" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <v>59.847300879612803</v>
       </c>
@@ -14496,7 +14496,7 @@
         <v>24.267386792951299</v>
       </c>
     </row>
-    <row r="23" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
         <v>59.062063896912001</v>
       </c>
@@ -14570,7 +14570,7 @@
         <v>20.342022890406199</v>
       </c>
     </row>
-    <row r="24" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
         <v>49.735156015734503</v>
       </c>
@@ -14644,7 +14644,7 @@
         <v>18.3567059464342</v>
       </c>
     </row>
-    <row r="25" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
         <v>30.5635144364702</v>
       </c>
@@ -14718,7 +14718,7 @@
         <v>28.1988201924962</v>
       </c>
     </row>
-    <row r="26" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
         <v>38.150452170686997</v>
       </c>
@@ -14792,7 +14792,7 @@
         <v>52.182075681052602</v>
       </c>
     </row>
-    <row r="27" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
         <v>34.232747334843097</v>
       </c>
@@ -14866,7 +14866,7 @@
         <v>79.952423680645097</v>
       </c>
     </row>
-    <row r="28" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
         <v>47.973012218272501</v>
       </c>
@@ -14940,7 +14940,7 @@
         <v>50.085219712942397</v>
       </c>
     </row>
-    <row r="29" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
         <v>52.515054308301004</v>
       </c>
@@ -15014,7 +15014,7 @@
         <v>23.9585307334773</v>
       </c>
     </row>
-    <row r="30" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
         <v>41.476911815801699</v>
       </c>
@@ -15088,7 +15088,7 @@
         <v>33.568944511786697</v>
       </c>
     </row>
-    <row r="31" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
         <v>24.895570601435502</v>
       </c>
@@ -15162,7 +15162,7 @@
         <v>29.300669455867901</v>
       </c>
     </row>
-    <row r="32" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
         <v>79.387088434965094</v>
       </c>
@@ -15236,7 +15236,7 @@
         <v>18.089915631157002</v>
       </c>
     </row>
-    <row r="33" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A33" s="2">
         <v>65.114671344893907</v>
       </c>
@@ -15310,7 +15310,7 @@
         <v>50.615961980600602</v>
       </c>
     </row>
-    <row r="34" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
         <v>44.922591014458597</v>
       </c>
@@ -15384,7 +15384,7 @@
         <v>38.518862373373899</v>
       </c>
     </row>
-    <row r="35" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
         <v>50.368073926776297</v>
       </c>
@@ -15458,7 +15458,7 @@
         <v>81.033943970601399</v>
       </c>
     </row>
-    <row r="36" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A36" s="2">
         <v>61.515128103959</v>
       </c>
@@ -15532,7 +15532,7 @@
         <v>49.309881521772198</v>
       </c>
     </row>
-    <row r="37" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A37" s="2">
         <v>66.446882062849099</v>
       </c>
@@ -15606,7 +15606,7 @@
         <v>42.206836097034703</v>
       </c>
     </row>
-    <row r="38" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A38" s="2">
         <v>53.105433072572303</v>
       </c>
@@ -15680,7 +15680,7 @@
         <v>5.0140727295788601</v>
       </c>
     </row>
-    <row r="39" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A39" s="2">
         <v>59.217514992679902</v>
       </c>
@@ -15754,7 +15754,7 @@
         <v>23.346574246422101</v>
       </c>
     </row>
-    <row r="40" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A40" s="2">
         <v>49.464948603291099</v>
       </c>
@@ -15828,7 +15828,7 @@
         <v>23.451892388853299</v>
       </c>
     </row>
-    <row r="41" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A41" s="2">
         <v>44.7229735569978</v>
       </c>
@@ -15902,7 +15902,7 @@
         <v>28.655703471531101</v>
       </c>
     </row>
-    <row r="42" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A42" s="2">
         <v>39.093923732180002</v>
       </c>
@@ -15976,7 +15976,7 @@
         <v>36.507484237500599</v>
       </c>
     </row>
-    <row r="43" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A43" s="2">
         <v>33.481690118397204</v>
       </c>
@@ -16050,7 +16050,7 @@
         <v>56.6078196169981</v>
       </c>
     </row>
-    <row r="44" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A44" s="2">
         <v>47.098018188697601</v>
       </c>
@@ -16124,7 +16124,7 @@
         <v>23.197317184334</v>
       </c>
     </row>
-    <row r="45" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A45" s="2">
         <v>43.179013973835502</v>
       </c>
@@ -16198,7 +16198,7 @@
         <v>54.2033017560994</v>
       </c>
     </row>
-    <row r="46" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A46" s="2">
         <v>61.9790813912104</v>
       </c>
@@ -16272,7 +16272,7 @@
         <v>22.023612772035101</v>
       </c>
     </row>
-    <row r="47" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A47" s="2">
         <v>51.201884065619197</v>
       </c>
@@ -16346,7 +16346,7 @@
         <v>19.8395882139428</v>
       </c>
     </row>
-    <row r="48" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A48" s="2">
         <v>45.833605648748097</v>
       </c>
@@ -16420,7 +16420,7 @@
         <v>20.647267498012301</v>
       </c>
     </row>
-    <row r="49" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A49" s="2">
         <v>41.487557947701603</v>
       </c>
@@ -16494,7 +16494,7 @@
         <v>22.813878344544602</v>
       </c>
     </row>
-    <row r="50" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A50" s="2">
         <v>34.014088196321197</v>
       </c>
@@ -16568,7 +16568,7 @@
         <v>31.052237501763901</v>
       </c>
     </row>
-    <row r="51" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A51" s="2">
         <v>57.4287393220986</v>
       </c>
@@ -16642,7 +16642,7 @@
         <v>39.901356441820298</v>
       </c>
     </row>
-    <row r="52" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A52" s="2">
         <v>49.642715902573798</v>
       </c>
@@ -16716,7 +16716,7 @@
         <v>45.889629639253002</v>
       </c>
     </row>
-    <row r="53" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A53" s="2">
         <v>42.831439510559697</v>
       </c>
@@ -16790,7 +16790,7 @@
         <v>51.817747510565198</v>
       </c>
     </row>
-    <row r="54" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A54" s="2">
         <v>35.356159325651298</v>
       </c>
@@ -16864,7 +16864,7 @@
         <v>58.777386226454702</v>
       </c>
     </row>
-    <row r="55" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A55" s="2">
         <v>33.766356008074801</v>
       </c>
